--- a/myprojects/RVNL/RVNL_Business_Performance.xlsx
+++ b/myprojects/RVNL/RVNL_Business_Performance.xlsx
@@ -5,11 +5,11 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dell\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dell\Documents\GitHub\inakm.github.io\myprojects\RVNL\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="450" windowWidth="28800" windowHeight="13860" tabRatio="500" activeTab="5"/>
+    <workbookView xWindow="0" yWindow="450" windowWidth="28800" windowHeight="13860" tabRatio="500" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="HOME" sheetId="1" r:id="rId1"/>
@@ -969,45 +969,6 @@
   </cellStyleXfs>
   <cellXfs count="67">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -1143,23 +1104,62 @@
     <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="10" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="10" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="10" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="16" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="10" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="10" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="10" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1428,162 +1428,167 @@
   <dimension ref="A1:E23"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="2" style="14" customWidth="1"/>
-    <col min="2" max="2" width="42" style="14" customWidth="1"/>
-    <col min="3" max="3" width="57.85546875" style="14" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="64.5703125" style="14" customWidth="1"/>
-    <col min="5" max="5" width="2" style="14" customWidth="1"/>
+    <col min="1" max="1" width="2" style="1" customWidth="1"/>
+    <col min="2" max="2" width="42" style="1" customWidth="1"/>
+    <col min="3" max="3" width="57.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="64.5703125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="2" style="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:4" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B1" s="13" t="s">
+      <c r="B1" s="53" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="13"/>
-      <c r="D1" s="13"/>
+      <c r="C1" s="53"/>
+      <c r="D1" s="53"/>
     </row>
     <row r="2" spans="2:4" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="12" t="s">
+      <c r="B2" s="54" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="12"/>
-      <c r="D2" s="12"/>
+      <c r="C2" s="54"/>
+      <c r="D2" s="54"/>
     </row>
     <row r="3" spans="2:4" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="11" t="s">
+      <c r="B3" s="55" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="11"/>
-      <c r="D3" s="11"/>
+      <c r="C3" s="55"/>
+      <c r="D3" s="55"/>
     </row>
     <row r="5" spans="2:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="10" t="s">
+      <c r="B5" s="48" t="s">
         <v>3</v>
       </c>
-      <c r="C5" s="10"/>
-      <c r="D5" s="10"/>
+      <c r="C5" s="48"/>
+      <c r="D5" s="48"/>
     </row>
     <row r="6" spans="2:4" ht="54.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="9" t="s">
+      <c r="B6" s="56" t="s">
         <v>4</v>
       </c>
-      <c r="C6" s="9"/>
-      <c r="D6" s="9"/>
+      <c r="C6" s="56"/>
+      <c r="D6" s="56"/>
     </row>
     <row r="8" spans="2:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B8" s="10" t="s">
+      <c r="B8" s="48" t="s">
         <v>5</v>
       </c>
-      <c r="C8" s="10"/>
-      <c r="D8" s="10"/>
+      <c r="C8" s="48"/>
+      <c r="D8" s="48"/>
     </row>
     <row r="9" spans="2:4" ht="48" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B9" s="8" t="s">
+      <c r="B9" s="51" t="s">
         <v>6</v>
       </c>
-      <c r="C9" s="8"/>
-      <c r="D9" s="8"/>
+      <c r="C9" s="51"/>
+      <c r="D9" s="51"/>
     </row>
     <row r="10" spans="2:4" ht="48" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B10" s="7" t="s">
+      <c r="B10" s="52" t="s">
         <v>7</v>
       </c>
-      <c r="C10" s="7"/>
-      <c r="D10" s="7"/>
+      <c r="C10" s="52"/>
+      <c r="D10" s="52"/>
     </row>
     <row r="11" spans="2:4" ht="48" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B11" s="8" t="s">
+      <c r="B11" s="51" t="s">
         <v>8</v>
       </c>
-      <c r="C11" s="8"/>
-      <c r="D11" s="8"/>
+      <c r="C11" s="51"/>
+      <c r="D11" s="51"/>
     </row>
     <row r="12" spans="2:4" ht="48" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B12" s="7" t="s">
+      <c r="B12" s="52" t="s">
         <v>9</v>
       </c>
-      <c r="C12" s="7"/>
-      <c r="D12" s="7"/>
+      <c r="C12" s="52"/>
+      <c r="D12" s="52"/>
     </row>
     <row r="13" spans="2:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B13" s="10" t="s">
+      <c r="B13" s="48" t="s">
         <v>10</v>
       </c>
-      <c r="C13" s="10"/>
-      <c r="D13" s="10"/>
+      <c r="C13" s="48"/>
+      <c r="D13" s="48"/>
     </row>
     <row r="14" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B14" s="15" t="s">
+      <c r="B14" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C14" s="15" t="s">
+      <c r="C14" s="2" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="15" spans="2:4" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B15" s="16" t="s">
+      <c r="B15" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="C15" s="17" t="s">
+      <c r="C15" s="4" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="16" spans="2:4" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B16" s="18" t="s">
+      <c r="B16" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="C16" s="19" t="s">
+      <c r="C16" s="6" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="17" spans="2:4" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B17" s="16" t="s">
+      <c r="B17" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="C17" s="17" t="s">
+      <c r="C17" s="4" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="18" spans="2:4" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B18" s="18" t="s">
+      <c r="B18" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="C18" s="19" t="s">
+      <c r="C18" s="6" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="19" spans="2:4" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B19" s="16" t="s">
+      <c r="B19" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="C19" s="17" t="s">
+      <c r="C19" s="4" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="20" spans="2:4" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B20" s="18" t="s">
+      <c r="B20" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="C20" s="19" t="s">
+      <c r="C20" s="6" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="21" spans="2:4" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B21" s="6" t="s">
+      <c r="B21" s="49" t="s">
         <v>25</v>
       </c>
-      <c r="C21" s="6"/>
-      <c r="D21" s="6"/>
+      <c r="C21" s="49"/>
+      <c r="D21" s="49"/>
     </row>
     <row r="23" spans="2:4" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B23" s="5" t="s">
+      <c r="B23" s="50" t="s">
         <v>2</v>
       </c>
-      <c r="C23" s="5"/>
-      <c r="D23" s="5"/>
+      <c r="C23" s="50"/>
+      <c r="D23" s="50"/>
     </row>
   </sheetData>
   <mergeCells count="13">
+    <mergeCell ref="B1:D1"/>
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="B3:D3"/>
+    <mergeCell ref="B5:D5"/>
+    <mergeCell ref="B6:D6"/>
     <mergeCell ref="B13:D13"/>
     <mergeCell ref="B21:D21"/>
     <mergeCell ref="B23:D23"/>
@@ -1592,11 +1597,6 @@
     <mergeCell ref="B10:D10"/>
     <mergeCell ref="B11:D11"/>
     <mergeCell ref="B12:D12"/>
-    <mergeCell ref="B1:D1"/>
-    <mergeCell ref="B2:D2"/>
-    <mergeCell ref="B3:D3"/>
-    <mergeCell ref="B5:D5"/>
-    <mergeCell ref="B6:D6"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -1608,370 +1608,392 @@
   <dimension ref="A1:J84"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="2" style="14" customWidth="1"/>
-    <col min="2" max="2" width="32" style="14" customWidth="1"/>
-    <col min="3" max="6" width="13" style="14" customWidth="1"/>
-    <col min="7" max="9" width="14" style="14" customWidth="1"/>
-    <col min="10" max="10" width="2" style="14" customWidth="1"/>
+    <col min="1" max="1" width="2" style="1" customWidth="1"/>
+    <col min="2" max="2" width="41" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="6" width="13" style="1" customWidth="1"/>
+    <col min="7" max="9" width="14" style="1" customWidth="1"/>
+    <col min="10" max="10" width="9.42578125" style="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B1" s="4" t="s">
+      <c r="B1" s="63" t="s">
         <v>198</v>
       </c>
-      <c r="C1" s="4"/>
-      <c r="D1" s="4"/>
-      <c r="E1" s="4"/>
-      <c r="F1" s="4"/>
-      <c r="G1" s="4"/>
-      <c r="H1" s="4"/>
-      <c r="I1" s="4"/>
+      <c r="C1" s="63"/>
+      <c r="D1" s="63"/>
+      <c r="E1" s="63"/>
+      <c r="F1" s="63"/>
+      <c r="G1" s="63"/>
+      <c r="H1" s="63"/>
+      <c r="I1" s="63"/>
     </row>
     <row r="3" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="58" t="s">
         <v>26</v>
       </c>
-      <c r="C3" s="3"/>
-      <c r="D3" s="3"/>
-      <c r="E3" s="3"/>
-      <c r="F3" s="3"/>
+      <c r="C3" s="58"/>
+      <c r="D3" s="58"/>
+      <c r="E3" s="58"/>
+      <c r="F3" s="58"/>
     </row>
     <row r="4" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B4" s="20" t="s">
+      <c r="B4" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="C4" s="21" t="s">
+      <c r="C4" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="D4" s="21" t="s">
+      <c r="D4" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="E4" s="21" t="s">
+      <c r="E4" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="F4" s="21" t="s">
+      <c r="F4" s="8" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="5" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="17" t="s">
+      <c r="B5" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="C5" s="22">
+      <c r="C5" s="9">
         <v>19381.71</v>
       </c>
-      <c r="D5" s="22">
+      <c r="D5" s="9">
         <v>20281.57</v>
       </c>
-      <c r="E5" s="22">
+      <c r="E5" s="9">
         <v>21732.58</v>
       </c>
-      <c r="F5" s="22">
+      <c r="F5" s="9">
         <v>19869.349999999999</v>
       </c>
     </row>
     <row r="6" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="17" t="s">
+      <c r="B6" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="C6" s="22">
+      <c r="C6" s="9">
         <v>809.26</v>
       </c>
-      <c r="D6" s="22">
+      <c r="D6" s="9">
         <v>1003.94</v>
       </c>
-      <c r="E6" s="22">
+      <c r="E6" s="9">
         <v>1182.55</v>
       </c>
-      <c r="F6" s="22">
+      <c r="F6" s="9">
         <v>1018.89</v>
       </c>
     </row>
     <row r="7" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B7" s="23" t="s">
+      <c r="B7" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="C7" s="24">
-        <v>20190.97</v>
-      </c>
-      <c r="D7" s="24">
+      <c r="C7" s="11">
+        <f>SUM(C5:C6)</f>
+        <v>20190.969999999998</v>
+      </c>
+      <c r="D7" s="11">
+        <f t="shared" ref="D7:F7" si="0">SUM(D5:D6)</f>
         <v>21285.51</v>
       </c>
-      <c r="E7" s="24">
+      <c r="E7" s="11">
+        <f t="shared" si="0"/>
         <v>22915.13</v>
       </c>
-      <c r="F7" s="24">
-        <v>20888.240000000002</v>
+      <c r="F7" s="11">
+        <f t="shared" si="0"/>
+        <v>20888.239999999998</v>
       </c>
     </row>
     <row r="8" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B8" s="2" t="s">
+      <c r="B8" s="64" t="s">
         <v>35</v>
       </c>
-      <c r="C8" s="2"/>
-      <c r="D8" s="2"/>
-      <c r="E8" s="2"/>
-      <c r="F8" s="2"/>
+      <c r="C8" s="64"/>
+      <c r="D8" s="64"/>
+      <c r="E8" s="64"/>
+      <c r="F8" s="64"/>
     </row>
     <row r="9" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B9" s="17" t="s">
+      <c r="B9" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="C9" s="22">
+      <c r="C9" s="9">
         <v>17905.57</v>
       </c>
-      <c r="D9" s="22">
+      <c r="D9" s="9">
         <v>18727.599999999999</v>
       </c>
-      <c r="E9" s="22">
+      <c r="E9" s="9">
         <v>20041.240000000002</v>
       </c>
-      <c r="F9" s="22">
+      <c r="F9" s="9">
         <v>18385.2</v>
       </c>
     </row>
     <row r="10" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B10" s="25" t="s">
+      <c r="B10" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="C10" s="26">
+      <c r="C10" s="13">
         <v>203.05</v>
       </c>
-      <c r="D10" s="26">
+      <c r="D10" s="13">
         <v>187.16</v>
       </c>
-      <c r="E10" s="26">
+      <c r="E10" s="13">
         <v>184.18</v>
       </c>
-      <c r="F10" s="26">
+      <c r="F10" s="13">
         <v>182.98</v>
       </c>
     </row>
     <row r="11" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B11" s="17" t="s">
+      <c r="B11" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="C11" s="22">
+      <c r="C11" s="9">
         <v>563.71</v>
       </c>
-      <c r="D11" s="22">
+      <c r="D11" s="9">
         <v>581.37</v>
       </c>
-      <c r="E11" s="22">
+      <c r="E11" s="9">
         <v>568.49</v>
       </c>
-      <c r="F11" s="22">
+      <c r="F11" s="9">
         <v>539.51</v>
       </c>
     </row>
     <row r="12" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B12" s="25" t="s">
+      <c r="B12" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="C12" s="26">
+      <c r="C12" s="13">
         <v>20.9</v>
       </c>
-      <c r="D12" s="26">
+      <c r="D12" s="13">
         <v>22.27</v>
       </c>
-      <c r="E12" s="26">
+      <c r="E12" s="13">
         <v>20.82</v>
       </c>
-      <c r="F12" s="26">
+      <c r="F12" s="13">
         <v>30.6</v>
       </c>
     </row>
     <row r="13" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B13" s="17" t="s">
+      <c r="B13" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="C13" s="22">
+      <c r="C13" s="9">
         <v>91.5</v>
       </c>
-      <c r="D13" s="22">
+      <c r="D13" s="9">
         <v>122.73</v>
       </c>
-      <c r="E13" s="22">
+      <c r="E13" s="9">
         <v>161</v>
       </c>
-      <c r="F13" s="22">
+      <c r="F13" s="9">
         <v>199.78</v>
       </c>
     </row>
     <row r="14" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B14" s="23" t="s">
+      <c r="B14" s="10" t="s">
         <v>41</v>
       </c>
-      <c r="C14" s="24">
+      <c r="C14" s="11">
+        <f>SUM(C9:C13)</f>
         <v>18784.73</v>
       </c>
-      <c r="D14" s="24">
-        <v>19641.13</v>
-      </c>
-      <c r="E14" s="24">
-        <v>20975.73</v>
-      </c>
-      <c r="F14" s="24">
-        <v>19338.07</v>
+      <c r="D14" s="11">
+        <f t="shared" ref="D14:F14" si="1">SUM(D9:D13)</f>
+        <v>19641.129999999997</v>
+      </c>
+      <c r="E14" s="11">
+        <f t="shared" si="1"/>
+        <v>20975.730000000003</v>
+      </c>
+      <c r="F14" s="11">
+        <f t="shared" si="1"/>
+        <v>19338.069999999996</v>
       </c>
     </row>
     <row r="15" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B15" s="2" t="s">
+      <c r="B15" s="64" t="s">
         <v>42</v>
       </c>
-      <c r="C15" s="2"/>
-      <c r="D15" s="2"/>
-      <c r="E15" s="2"/>
-      <c r="F15" s="2"/>
+      <c r="C15" s="64"/>
+      <c r="D15" s="64"/>
+      <c r="E15" s="64"/>
+      <c r="F15" s="64"/>
     </row>
     <row r="16" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B16" s="27" t="s">
+      <c r="B16" s="14" t="s">
         <v>43</v>
       </c>
-      <c r="C16" s="28">
-        <v>1406.24</v>
-      </c>
-      <c r="D16" s="28">
-        <v>1644.38</v>
-      </c>
-      <c r="E16" s="28">
-        <v>1939.4</v>
-      </c>
-      <c r="F16" s="28">
-        <v>1550.17</v>
+      <c r="C16" s="15">
+        <f>C7-C14</f>
+        <v>1406.239999999998</v>
+      </c>
+      <c r="D16" s="15">
+        <f t="shared" ref="D16:F16" si="2">D7-D14</f>
+        <v>1644.380000000001</v>
+      </c>
+      <c r="E16" s="15">
+        <f t="shared" si="2"/>
+        <v>1939.3999999999978</v>
+      </c>
+      <c r="F16" s="15">
+        <f t="shared" si="2"/>
+        <v>1550.1700000000019</v>
       </c>
     </row>
     <row r="17" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B17" s="17" t="s">
+      <c r="B17" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="C17" s="22">
+      <c r="C17" s="9">
         <v>318.89</v>
       </c>
-      <c r="D17" s="22">
+      <c r="D17" s="9">
         <v>376.42</v>
       </c>
-      <c r="E17" s="22">
+      <c r="E17" s="9">
         <v>476.45</v>
       </c>
-      <c r="F17" s="22">
+      <c r="F17" s="9">
         <v>361.55</v>
       </c>
     </row>
     <row r="18" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B18" s="27" t="s">
+      <c r="B18" s="14" t="s">
         <v>45</v>
       </c>
-      <c r="C18" s="28">
-        <v>1087.3499999999999</v>
-      </c>
-      <c r="D18" s="28">
-        <v>1267.97</v>
-      </c>
-      <c r="E18" s="28">
-        <v>1462.95</v>
-      </c>
-      <c r="F18" s="28">
-        <v>1188.6199999999999</v>
+      <c r="C18" s="15">
+        <f>C16-C17</f>
+        <v>1087.3499999999981</v>
+      </c>
+      <c r="D18" s="15">
+        <f t="shared" ref="D18:F18" si="3">D16-D17</f>
+        <v>1267.9600000000009</v>
+      </c>
+      <c r="E18" s="15">
+        <f t="shared" si="3"/>
+        <v>1462.9499999999978</v>
+      </c>
+      <c r="F18" s="15">
+        <f t="shared" si="3"/>
+        <v>1188.6200000000019</v>
       </c>
     </row>
     <row r="20" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B20" s="3" t="s">
+      <c r="B20" s="58" t="s">
         <v>46</v>
       </c>
-      <c r="C20" s="3"/>
-      <c r="D20" s="3"/>
-      <c r="E20" s="3"/>
-      <c r="F20" s="3"/>
-      <c r="G20" s="3"/>
-      <c r="H20" s="3"/>
-      <c r="I20" s="3"/>
+      <c r="C20" s="58"/>
+      <c r="D20" s="58"/>
+      <c r="E20" s="58"/>
+      <c r="F20" s="58"/>
+      <c r="G20" s="58"/>
+      <c r="H20" s="58"/>
+      <c r="I20" s="58"/>
     </row>
     <row r="21" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B21" s="20" t="s">
+      <c r="B21" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="C21" s="21" t="s">
+      <c r="C21" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="D21" s="21" t="s">
+      <c r="D21" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="E21" s="21" t="s">
+      <c r="E21" s="8" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="22" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B22" s="17" t="s">
+      <c r="B22" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="C22" s="22">
+      <c r="C22" s="9">
+        <f>D5</f>
         <v>20281.57</v>
       </c>
-      <c r="D22" s="22">
+      <c r="D22" s="9">
+        <f>E5</f>
         <v>21732.58</v>
       </c>
-      <c r="E22" s="22">
+      <c r="E22" s="9">
+        <f>F5</f>
         <v>19869.349999999999</v>
       </c>
     </row>
     <row r="23" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B23" s="25" t="s">
+      <c r="B23" s="12" t="s">
         <v>49</v>
       </c>
-      <c r="C23" s="26">
+      <c r="C23" s="13">
+        <f>C5</f>
         <v>19381.71</v>
       </c>
-      <c r="D23" s="26">
+      <c r="D23" s="13">
+        <f>D5</f>
         <v>20281.57</v>
       </c>
-      <c r="E23" s="26">
+      <c r="E23" s="13">
+        <f>E5</f>
         <v>21732.58</v>
       </c>
     </row>
     <row r="24" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B24" s="23" t="s">
+      <c r="B24" s="10" t="s">
         <v>50</v>
       </c>
-      <c r="C24" s="29">
+      <c r="C24" s="16">
         <f>C22-C23</f>
         <v>899.86000000000058</v>
       </c>
-      <c r="D24" s="29">
-        <f>D22-D23</f>
+      <c r="D24" s="16">
+        <f t="shared" ref="D24:E24" si="4">D22-D23</f>
         <v>1451.010000000002</v>
       </c>
-      <c r="E24" s="29">
-        <f>E22-E23</f>
+      <c r="E24" s="16">
+        <f t="shared" si="4"/>
         <v>-1863.2300000000032</v>
       </c>
     </row>
     <row r="25" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B25" s="17" t="s">
+      <c r="B25" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="C25" s="30">
+      <c r="C25" s="17">
         <f>C24/C23</f>
         <v>4.6428307925358528E-2</v>
       </c>
-      <c r="D25" s="30">
+      <c r="D25" s="17">
         <f>D24/D23</f>
         <v>7.154327796122302E-2</v>
       </c>
-      <c r="E25" s="30">
+      <c r="E25" s="17">
         <f>E24/E23</f>
         <v>-8.5734413493473993E-2</v>
       </c>
     </row>
     <row r="26" spans="2:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="27" spans="2:9" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B27" s="63" t="s">
+      <c r="B27" s="59" t="s">
         <v>52</v>
       </c>
-      <c r="C27" s="64"/>
-      <c r="D27" s="64"/>
-      <c r="E27" s="64"/>
-      <c r="F27" s="65"/>
+      <c r="C27" s="60"/>
+      <c r="D27" s="60"/>
+      <c r="E27" s="60"/>
+      <c r="F27" s="61"/>
     </row>
     <row r="28" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B28" s="62" t="s">
@@ -1983,163 +2005,169 @@
       <c r="F28" s="62"/>
     </row>
     <row r="29" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B29" s="8" t="s">
+      <c r="B29" s="51" t="s">
         <v>54</v>
       </c>
-      <c r="C29" s="8"/>
-      <c r="D29" s="8"/>
-      <c r="E29" s="8"/>
-      <c r="F29" s="8"/>
+      <c r="C29" s="51"/>
+      <c r="D29" s="51"/>
+      <c r="E29" s="51"/>
+      <c r="F29" s="51"/>
     </row>
     <row r="30" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B30" s="7" t="s">
+      <c r="B30" s="52" t="s">
         <v>55</v>
       </c>
-      <c r="C30" s="7"/>
-      <c r="D30" s="7"/>
-      <c r="E30" s="7"/>
-      <c r="F30" s="7"/>
+      <c r="C30" s="52"/>
+      <c r="D30" s="52"/>
+      <c r="E30" s="52"/>
+      <c r="F30" s="52"/>
     </row>
     <row r="31" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B31" s="8" t="s">
+      <c r="B31" s="51" t="s">
         <v>56</v>
       </c>
-      <c r="C31" s="8"/>
-      <c r="D31" s="8"/>
-      <c r="E31" s="8"/>
-      <c r="F31" s="8"/>
+      <c r="C31" s="51"/>
+      <c r="D31" s="51"/>
+      <c r="E31" s="51"/>
+      <c r="F31" s="51"/>
     </row>
     <row r="32" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B32" s="3" t="s">
+      <c r="B32" s="58" t="s">
         <v>57</v>
       </c>
-      <c r="C32" s="3"/>
-      <c r="D32" s="3"/>
-      <c r="E32" s="3"/>
-      <c r="F32" s="3"/>
-      <c r="G32" s="3"/>
-      <c r="H32" s="3"/>
-      <c r="I32" s="3"/>
+      <c r="C32" s="58"/>
+      <c r="D32" s="58"/>
+      <c r="E32" s="58"/>
+      <c r="F32" s="58"/>
+      <c r="G32" s="58"/>
+      <c r="H32" s="58"/>
+      <c r="I32" s="58"/>
     </row>
     <row r="33" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B33" s="20" t="s">
+      <c r="B33" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="C33" s="21" t="s">
+      <c r="C33" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="D33" s="21" t="s">
+      <c r="D33" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="E33" s="21" t="s">
+      <c r="E33" s="8" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="34" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B34" s="17" t="s">
+      <c r="B34" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="C34" s="22">
-        <v>1644.38</v>
-      </c>
-      <c r="D34" s="22">
-        <v>1939.4</v>
-      </c>
-      <c r="E34" s="22">
-        <v>1550.17</v>
+      <c r="C34" s="9">
+        <f>D16</f>
+        <v>1644.380000000001</v>
+      </c>
+      <c r="D34" s="9">
+        <f>E16</f>
+        <v>1939.3999999999978</v>
+      </c>
+      <c r="E34" s="9">
+        <f>F16</f>
+        <v>1550.1700000000019</v>
       </c>
     </row>
     <row r="35" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B35" s="25" t="s">
+      <c r="B35" s="12" t="s">
         <v>59</v>
       </c>
-      <c r="C35" s="26">
-        <v>1267.97</v>
-      </c>
-      <c r="D35" s="26">
-        <v>1462.95</v>
-      </c>
-      <c r="E35" s="26">
-        <v>1188.6199999999999</v>
+      <c r="C35" s="13">
+        <f>D18</f>
+        <v>1267.9600000000009</v>
+      </c>
+      <c r="D35" s="13">
+        <f>E18</f>
+        <v>1462.9499999999978</v>
+      </c>
+      <c r="E35" s="13">
+        <f>F18</f>
+        <v>1188.6200000000019</v>
       </c>
     </row>
     <row r="36" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B36" s="17" t="s">
+      <c r="B36" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="C36" s="30">
-        <f>(1644.38-1406.24)/1406.24</f>
-        <v>0.1693452042325635</v>
-      </c>
-      <c r="D36" s="30">
-        <f>(1939.4-1644.38)/1644.38</f>
-        <v>0.17941108502900788</v>
-      </c>
-      <c r="E36" s="30">
-        <f>(1550.17-1939.4)/1939.4</f>
-        <v>-0.20069609157471383</v>
+      <c r="C36" s="17">
+        <f>(D16-C16)/C16</f>
+        <v>0.16934520423256585</v>
+      </c>
+      <c r="D36" s="17">
+        <f t="shared" ref="D36:E36" si="5">(E16-D16)/D16</f>
+        <v>0.17941108502900582</v>
+      </c>
+      <c r="E36" s="17">
+        <f>(F16-E16)/E16</f>
+        <v>-0.20069609157471197</v>
       </c>
     </row>
     <row r="37" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B37" s="25" t="s">
+      <c r="B37" s="12" t="s">
         <v>61</v>
       </c>
-      <c r="C37" s="31">
-        <f>(1267.97-1087.35)/1087.35</f>
-        <v>0.16611026808295409</v>
-      </c>
-      <c r="D37" s="31">
-        <f>(1462.95-1267.97)/1267.97</f>
-        <v>0.15377335425917019</v>
-      </c>
-      <c r="E37" s="31">
-        <f>(1188.62-1462.95)/1462.95</f>
-        <v>-0.18751837041594049</v>
+      <c r="C37" s="18">
+        <f>(D18-C18)/C18</f>
+        <v>0.16610107141215172</v>
+      </c>
+      <c r="D37" s="18">
+        <f t="shared" ref="D37:E37" si="6">(E18-D18)/D18</f>
+        <v>0.15378245370516158</v>
+      </c>
+      <c r="E37" s="18">
+        <f t="shared" si="6"/>
+        <v>-0.18751837041593783</v>
       </c>
     </row>
     <row r="38" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B38" s="23" t="s">
+      <c r="B38" s="10" t="s">
         <v>62</v>
       </c>
-      <c r="C38" s="32">
-        <f>1267.97/20281.57</f>
-        <v>6.2518335612085266E-2</v>
-      </c>
-      <c r="D38" s="32">
-        <f>1462.95/21732.58</f>
-        <v>6.7315983652194072E-2</v>
-      </c>
-      <c r="E38" s="32">
-        <f>1188.62/19869.35</f>
-        <v>5.9821785815841987E-2</v>
+      <c r="C38" s="19">
+        <f>D18/D5</f>
+        <v>6.2517842553609065E-2</v>
+      </c>
+      <c r="D38" s="19">
+        <f>E18/E5</f>
+        <v>6.7315983652193975E-2</v>
+      </c>
+      <c r="E38" s="19">
+        <f>F18/F5</f>
+        <v>5.9821785815842091E-2</v>
       </c>
     </row>
     <row r="39" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B39" s="17" t="s">
+      <c r="B39" s="4" t="s">
         <v>63</v>
       </c>
-      <c r="C39" s="30">
-        <f>1644.38/20281.57</f>
-        <v>8.1077549716318809E-2</v>
-      </c>
-      <c r="D39" s="30">
-        <f>1939.4/21732.58</f>
-        <v>8.9239289582737066E-2</v>
-      </c>
-      <c r="E39" s="30">
-        <f>1550.17/19869.35</f>
-        <v>7.8018153588315681E-2</v>
+      <c r="C39" s="17">
+        <f>D16/D5</f>
+        <v>8.107754971631885E-2</v>
+      </c>
+      <c r="D39" s="17">
+        <f>E16/E5</f>
+        <v>8.9239289582736969E-2</v>
+      </c>
+      <c r="E39" s="17">
+        <f>F16/F5</f>
+        <v>7.8018153588315778E-2</v>
       </c>
     </row>
     <row r="40" spans="2:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="41" spans="2:9" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B41" s="63" t="s">
+      <c r="B41" s="59" t="s">
         <v>64</v>
       </c>
-      <c r="C41" s="64"/>
-      <c r="D41" s="64"/>
-      <c r="E41" s="64"/>
-      <c r="F41" s="65"/>
+      <c r="C41" s="60"/>
+      <c r="D41" s="60"/>
+      <c r="E41" s="60"/>
+      <c r="F41" s="61"/>
     </row>
     <row r="42" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B42" s="62" t="s">
@@ -2151,196 +2179,196 @@
       <c r="F42" s="62"/>
     </row>
     <row r="43" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B43" s="8" t="s">
+      <c r="B43" s="51" t="s">
         <v>66</v>
       </c>
-      <c r="C43" s="8"/>
-      <c r="D43" s="8"/>
-      <c r="E43" s="8"/>
-      <c r="F43" s="8"/>
+      <c r="C43" s="51"/>
+      <c r="D43" s="51"/>
+      <c r="E43" s="51"/>
+      <c r="F43" s="51"/>
     </row>
     <row r="44" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B44" s="7" t="s">
+      <c r="B44" s="52" t="s">
         <v>67</v>
       </c>
-      <c r="C44" s="7"/>
-      <c r="D44" s="7"/>
-      <c r="E44" s="7"/>
-      <c r="F44" s="7"/>
+      <c r="C44" s="52"/>
+      <c r="D44" s="52"/>
+      <c r="E44" s="52"/>
+      <c r="F44" s="52"/>
     </row>
     <row r="45" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B45" s="8" t="s">
+      <c r="B45" s="51" t="s">
         <v>68</v>
       </c>
-      <c r="C45" s="8"/>
-      <c r="D45" s="8"/>
-      <c r="E45" s="8"/>
-      <c r="F45" s="8"/>
+      <c r="C45" s="51"/>
+      <c r="D45" s="51"/>
+      <c r="E45" s="51"/>
+      <c r="F45" s="51"/>
     </row>
     <row r="46" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B46" s="3" t="s">
+      <c r="B46" s="58" t="s">
         <v>69</v>
       </c>
-      <c r="C46" s="3"/>
-      <c r="D46" s="3"/>
-      <c r="E46" s="3"/>
-      <c r="F46" s="3"/>
-      <c r="G46" s="3"/>
-      <c r="H46" s="3"/>
-      <c r="I46" s="3"/>
+      <c r="C46" s="58"/>
+      <c r="D46" s="58"/>
+      <c r="E46" s="58"/>
+      <c r="F46" s="58"/>
+      <c r="G46" s="58"/>
+      <c r="H46" s="58"/>
+      <c r="I46" s="58"/>
     </row>
     <row r="47" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B47" s="20" t="s">
+      <c r="B47" s="7" t="s">
         <v>70</v>
       </c>
-      <c r="C47" s="21" t="s">
+      <c r="C47" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="D47" s="21" t="s">
+      <c r="D47" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="E47" s="21" t="s">
+      <c r="E47" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="F47" s="21" t="s">
+      <c r="F47" s="8" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="48" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B48" s="25" t="s">
+      <c r="B48" s="12" t="s">
         <v>36</v>
       </c>
-      <c r="C48" s="31">
-        <f>17905.57/19381.71</f>
+      <c r="C48" s="18">
+        <f>C9/C5</f>
         <v>0.92383850547758684</v>
       </c>
-      <c r="D48" s="31">
-        <f>18727.6/20281.57</f>
+      <c r="D48" s="18">
+        <f t="shared" ref="D48:F48" si="7">D9/D5</f>
         <v>0.92338019196738708</v>
       </c>
-      <c r="E48" s="31">
-        <f>20041.24/21732.58</f>
+      <c r="E48" s="18">
+        <f>E9/E5</f>
         <v>0.92217490974380401</v>
       </c>
-      <c r="F48" s="31">
-        <f>18385.2/19869.35</f>
+      <c r="F48" s="18">
+        <f t="shared" si="7"/>
         <v>0.9253045519858476</v>
       </c>
     </row>
     <row r="49" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B49" s="17" t="s">
+      <c r="B49" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="C49" s="30">
-        <f>203.05/19381.71</f>
+      <c r="C49" s="17">
+        <f>C10/C5</f>
         <v>1.0476371795883852E-2</v>
       </c>
-      <c r="D49" s="30">
-        <f>187.16/20281.57</f>
+      <c r="D49" s="17">
+        <f t="shared" ref="D49:F49" si="8">D10/D5</f>
         <v>9.2280824413494607E-3</v>
       </c>
-      <c r="E49" s="30">
-        <f>184.18/21732.58</f>
+      <c r="E49" s="17">
+        <f t="shared" si="8"/>
         <v>8.4748336368714611E-3</v>
       </c>
-      <c r="F49" s="30">
-        <f>182.98/19869.35</f>
+      <c r="F49" s="17">
+        <f t="shared" si="8"/>
         <v>9.2091588300573495E-3</v>
       </c>
     </row>
     <row r="50" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B50" s="25" t="s">
+      <c r="B50" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="C50" s="31">
-        <f>563.71/19381.71</f>
+      <c r="C50" s="18">
+        <f>C11/C5</f>
         <v>2.9084637010872626E-2</v>
       </c>
-      <c r="D50" s="31">
-        <f>581.37/20281.57</f>
+      <c r="D50" s="18">
+        <f t="shared" ref="D50:F50" si="9">D11/D5</f>
         <v>2.8664940633294167E-2</v>
       </c>
-      <c r="E50" s="31">
-        <f>568.49/21732.58</f>
+      <c r="E50" s="18">
+        <f t="shared" si="9"/>
         <v>2.6158422055733831E-2</v>
       </c>
-      <c r="F50" s="31">
-        <f>539.51/19869.35</f>
+      <c r="F50" s="18">
+        <f t="shared" si="9"/>
         <v>2.7152876163538314E-2</v>
       </c>
     </row>
     <row r="51" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B51" s="17" t="s">
+      <c r="B51" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="C51" s="30">
-        <f>20.9/19381.71</f>
+      <c r="C51" s="17">
+        <f>C12/C5</f>
         <v>1.0783362252350282E-3</v>
       </c>
-      <c r="D51" s="30">
-        <f>22.27/20281.57</f>
+      <c r="D51" s="17">
+        <f t="shared" ref="D51:F51" si="10">D12/D5</f>
         <v>1.0980412265914326E-3</v>
       </c>
-      <c r="E51" s="30">
-        <f>20.82/21732.58</f>
+      <c r="E51" s="17">
+        <f t="shared" si="10"/>
         <v>9.5800866717159205E-4</v>
       </c>
-      <c r="F51" s="30">
-        <f>30.6/19869.35</f>
+      <c r="F51" s="17">
+        <f t="shared" si="10"/>
         <v>1.5400604448560222E-3</v>
       </c>
     </row>
     <row r="52" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B52" s="25" t="s">
+      <c r="B52" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="C52" s="31">
-        <f>91.5/19381.71</f>
+      <c r="C52" s="18">
+        <f>C13/C5</f>
         <v>4.7209456750720137E-3</v>
       </c>
-      <c r="D52" s="31">
-        <f>122.73/20281.57</f>
+      <c r="D52" s="18">
+        <f t="shared" ref="D52:F52" si="11">D13/D5</f>
         <v>6.0513066789208139E-3</v>
       </c>
-      <c r="E52" s="31">
-        <f>161/21732.58</f>
+      <c r="E52" s="18">
+        <f t="shared" si="11"/>
         <v>7.4082322485411302E-3</v>
       </c>
-      <c r="F52" s="31">
-        <f>199.78/19869.35</f>
+      <c r="F52" s="18">
+        <f t="shared" si="11"/>
         <v>1.0054682211546932E-2</v>
       </c>
     </row>
     <row r="53" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B53" s="23" t="s">
+      <c r="B53" s="10" t="s">
         <v>41</v>
       </c>
-      <c r="C53" s="32">
-        <f>18784.73/19381.71</f>
+      <c r="C53" s="19">
+        <f>C14/C5</f>
         <v>0.96919879618465044</v>
       </c>
-      <c r="D53" s="32">
-        <f>19641.13/20281.57</f>
-        <v>0.96842256294754303</v>
-      </c>
-      <c r="E53" s="32">
-        <f>20975.73/21732.58</f>
-        <v>0.96517440635212193</v>
-      </c>
-      <c r="F53" s="32">
-        <f>19338.07/19869.35</f>
-        <v>0.97326132963584622</v>
+      <c r="D53" s="19">
+        <f t="shared" ref="D53:F53" si="12">D14/D5</f>
+        <v>0.96842256294754292</v>
+      </c>
+      <c r="E53" s="19">
+        <f t="shared" si="12"/>
+        <v>0.96517440635212204</v>
+      </c>
+      <c r="F53" s="19">
+        <f t="shared" si="12"/>
+        <v>0.973261329635846</v>
       </c>
     </row>
     <row r="54" spans="2:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="55" spans="2:9" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B55" s="63" t="s">
+      <c r="B55" s="59" t="s">
         <v>71</v>
       </c>
-      <c r="C55" s="64"/>
-      <c r="D55" s="64"/>
-      <c r="E55" s="64"/>
-      <c r="F55" s="65"/>
+      <c r="C55" s="60"/>
+      <c r="D55" s="60"/>
+      <c r="E55" s="60"/>
+      <c r="F55" s="61"/>
     </row>
     <row r="56" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B56" s="62" t="s">
@@ -2352,398 +2380,398 @@
       <c r="F56" s="62"/>
     </row>
     <row r="57" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B57" s="8" t="s">
+      <c r="B57" s="51" t="s">
         <v>73</v>
       </c>
-      <c r="C57" s="8"/>
-      <c r="D57" s="8"/>
-      <c r="E57" s="8"/>
-      <c r="F57" s="8"/>
+      <c r="C57" s="51"/>
+      <c r="D57" s="51"/>
+      <c r="E57" s="51"/>
+      <c r="F57" s="51"/>
     </row>
     <row r="58" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B58" s="7" t="s">
+      <c r="B58" s="52" t="s">
         <v>74</v>
       </c>
-      <c r="C58" s="7"/>
-      <c r="D58" s="7"/>
-      <c r="E58" s="7"/>
-      <c r="F58" s="7"/>
+      <c r="C58" s="52"/>
+      <c r="D58" s="52"/>
+      <c r="E58" s="52"/>
+      <c r="F58" s="52"/>
     </row>
     <row r="59" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B59" s="8" t="s">
+      <c r="B59" s="51" t="s">
         <v>75</v>
       </c>
-      <c r="C59" s="8"/>
-      <c r="D59" s="8"/>
-      <c r="E59" s="8"/>
-      <c r="F59" s="8"/>
+      <c r="C59" s="51"/>
+      <c r="D59" s="51"/>
+      <c r="E59" s="51"/>
+      <c r="F59" s="51"/>
     </row>
     <row r="60" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B60" s="3" t="s">
+      <c r="B60" s="58" t="s">
         <v>201</v>
       </c>
-      <c r="C60" s="3"/>
-      <c r="D60" s="3"/>
-      <c r="E60" s="3"/>
-      <c r="F60" s="3"/>
-      <c r="G60" s="3"/>
-      <c r="H60" s="3"/>
-      <c r="I60" s="3"/>
+      <c r="C60" s="58"/>
+      <c r="D60" s="58"/>
+      <c r="E60" s="58"/>
+      <c r="F60" s="58"/>
+      <c r="G60" s="58"/>
+      <c r="H60" s="58"/>
+      <c r="I60" s="58"/>
     </row>
     <row r="61" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B61" s="20" t="s">
+      <c r="B61" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="C61" s="21" t="s">
+      <c r="C61" s="8" t="s">
         <v>77</v>
       </c>
-      <c r="D61" s="21" t="s">
+      <c r="D61" s="8" t="s">
         <v>78</v>
       </c>
-      <c r="E61" s="21" t="s">
+      <c r="E61" s="8" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="62" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B62" s="33" t="s">
+      <c r="B62" s="20" t="s">
         <v>80</v>
       </c>
-      <c r="C62" s="34">
+      <c r="C62" s="21">
         <v>0.08</v>
       </c>
-      <c r="D62" s="34">
+      <c r="D62" s="21">
         <v>0.1</v>
       </c>
-      <c r="E62" s="34">
+      <c r="E62" s="21">
         <v>0.12</v>
       </c>
     </row>
     <row r="63" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B63" s="33" t="s">
+      <c r="B63" s="20" t="s">
         <v>81</v>
       </c>
-      <c r="C63" s="34">
+      <c r="C63" s="21">
         <v>0.06</v>
       </c>
-      <c r="D63" s="34">
+      <c r="D63" s="21">
         <v>6.2E-2</v>
       </c>
-      <c r="E63" s="34">
+      <c r="E63" s="21">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
     <row r="64" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B64" s="33" t="s">
+      <c r="B64" s="20" t="s">
         <v>82</v>
       </c>
-      <c r="C64" s="34">
+      <c r="C64" s="21">
         <v>0.05</v>
       </c>
-      <c r="D64" s="34">
+      <c r="D64" s="21">
         <v>0.05</v>
       </c>
-      <c r="E64" s="34">
+      <c r="E64" s="21">
         <v>0.05</v>
       </c>
     </row>
     <row r="65" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B65" s="3" t="s">
+      <c r="B65" s="58" t="s">
         <v>202</v>
       </c>
-      <c r="C65" s="3"/>
-      <c r="D65" s="3"/>
-      <c r="E65" s="3"/>
-      <c r="F65" s="3"/>
-      <c r="G65" s="3"/>
-      <c r="H65" s="3"/>
-      <c r="I65" s="3"/>
-    </row>
-    <row r="66" spans="2:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B66" s="20" t="s">
+      <c r="C65" s="58"/>
+      <c r="D65" s="58"/>
+      <c r="E65" s="58"/>
+      <c r="F65" s="58"/>
+      <c r="G65" s="58"/>
+      <c r="H65" s="58"/>
+      <c r="I65" s="58"/>
+    </row>
+    <row r="66" spans="2:9" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B66" s="7" t="s">
         <v>83</v>
       </c>
-      <c r="C66" s="35" t="s">
+      <c r="C66" s="22" t="s">
         <v>84</v>
       </c>
-      <c r="D66" s="35" t="s">
+      <c r="D66" s="22" t="s">
         <v>85</v>
       </c>
-      <c r="E66" s="35" t="s">
+      <c r="E66" s="22" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="67" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B67" s="36">
-        <f>19869.35</f>
+      <c r="B67" s="23">
+        <f>F5</f>
         <v>19869.349999999999</v>
       </c>
-      <c r="C67" s="36">
+      <c r="C67" s="23">
         <f>B67*(1+C62)</f>
         <v>21458.898000000001</v>
       </c>
-      <c r="D67" s="36">
+      <c r="D67" s="23">
         <f>C67*(1+D62)</f>
         <v>23604.787800000002</v>
       </c>
-      <c r="E67" s="36">
+      <c r="E67" s="23">
         <f>D67*(1+E62)</f>
         <v>26437.362336000006</v>
       </c>
     </row>
     <row r="68" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B68" s="37">
-        <f>1018.89</f>
+      <c r="B68" s="24">
+        <f>F6</f>
         <v>1018.89</v>
       </c>
-      <c r="C68" s="37">
+      <c r="C68" s="24">
         <f>B68*(1+C64)</f>
         <v>1069.8344999999999</v>
       </c>
-      <c r="D68" s="37">
+      <c r="D68" s="24">
         <f>C68*(1+D64)</f>
         <v>1123.326225</v>
       </c>
-      <c r="E68" s="37">
+      <c r="E68" s="24">
         <f>D68*(1+E64)</f>
         <v>1179.4925362500001</v>
       </c>
     </row>
     <row r="69" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B69" s="29">
-        <f>B67+B68</f>
+      <c r="B69" s="16">
+        <f>F7</f>
         <v>20888.239999999998</v>
       </c>
-      <c r="C69" s="29">
+      <c r="C69" s="16">
         <f>C67+C68</f>
         <v>22528.732500000002</v>
       </c>
-      <c r="D69" s="29">
+      <c r="D69" s="16">
         <f>D67+D68</f>
         <v>24728.114025000003</v>
       </c>
-      <c r="E69" s="29">
+      <c r="E69" s="16">
         <f>E67+E68</f>
         <v>27616.854872250005</v>
       </c>
     </row>
     <row r="70" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B70" s="38">
-        <f>1188.62</f>
-        <v>1188.6199999999999</v>
-      </c>
-      <c r="C70" s="38">
+      <c r="B70" s="25">
+        <f>F18</f>
+        <v>1188.6200000000019</v>
+      </c>
+      <c r="C70" s="25">
         <f>C67*C63</f>
         <v>1287.53388</v>
       </c>
-      <c r="D70" s="38">
+      <c r="D70" s="25">
         <f>D67*D63</f>
         <v>1463.4968436000001</v>
       </c>
-      <c r="E70" s="38">
+      <c r="E70" s="25">
         <f>E67*E63</f>
         <v>1718.4285518400004</v>
       </c>
     </row>
     <row r="71" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B71" s="30">
-        <f>1188.62/19869.35</f>
-        <v>5.9821785815841987E-2</v>
-      </c>
-      <c r="C71" s="30">
+      <c r="B71" s="17">
+        <f>E38</f>
+        <v>5.9821785815842091E-2</v>
+      </c>
+      <c r="C71" s="17">
         <f>C63</f>
         <v>0.06</v>
       </c>
-      <c r="D71" s="30">
+      <c r="D71" s="17">
         <f>D63</f>
         <v>6.2E-2</v>
       </c>
-      <c r="E71" s="30">
+      <c r="E71" s="17">
         <f>E63</f>
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
     <row r="72" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B72" s="3" t="s">
+      <c r="B72" s="58" t="s">
         <v>199</v>
       </c>
-      <c r="C72" s="3"/>
-      <c r="D72" s="3"/>
-      <c r="E72" s="3"/>
-      <c r="F72" s="3"/>
-      <c r="G72" s="3"/>
-      <c r="H72" s="3"/>
-      <c r="I72" s="3"/>
+      <c r="C72" s="58"/>
+      <c r="D72" s="58"/>
+      <c r="E72" s="58"/>
+      <c r="F72" s="58"/>
+      <c r="G72" s="58"/>
+      <c r="H72" s="58"/>
+      <c r="I72" s="58"/>
     </row>
     <row r="73" spans="2:9" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B73" s="8" t="s">
+      <c r="B73" s="51" t="s">
         <v>87</v>
       </c>
-      <c r="C73" s="8"/>
-      <c r="D73" s="8"/>
-      <c r="E73" s="8"/>
-      <c r="F73" s="8"/>
-      <c r="G73" s="8"/>
-      <c r="H73" s="8"/>
-      <c r="I73" s="8"/>
+      <c r="C73" s="51"/>
+      <c r="D73" s="51"/>
+      <c r="E73" s="51"/>
+      <c r="F73" s="51"/>
+      <c r="G73" s="51"/>
+      <c r="H73" s="51"/>
+      <c r="I73" s="51"/>
     </row>
     <row r="74" spans="2:9" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B74" s="7" t="s">
+      <c r="B74" s="52" t="s">
         <v>88</v>
       </c>
-      <c r="C74" s="7"/>
-      <c r="D74" s="7"/>
-      <c r="E74" s="7"/>
-      <c r="F74" s="7"/>
-      <c r="G74" s="7"/>
-      <c r="H74" s="7"/>
-      <c r="I74" s="7"/>
+      <c r="C74" s="52"/>
+      <c r="D74" s="52"/>
+      <c r="E74" s="52"/>
+      <c r="F74" s="52"/>
+      <c r="G74" s="52"/>
+      <c r="H74" s="52"/>
+      <c r="I74" s="52"/>
     </row>
     <row r="75" spans="2:9" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B75" s="8" t="s">
+      <c r="B75" s="51" t="s">
         <v>89</v>
       </c>
-      <c r="C75" s="8"/>
-      <c r="D75" s="8"/>
-      <c r="E75" s="8"/>
-      <c r="F75" s="8"/>
-      <c r="G75" s="8"/>
-      <c r="H75" s="8"/>
-      <c r="I75" s="8"/>
+      <c r="C75" s="51"/>
+      <c r="D75" s="51"/>
+      <c r="E75" s="51"/>
+      <c r="F75" s="51"/>
+      <c r="G75" s="51"/>
+      <c r="H75" s="51"/>
+      <c r="I75" s="51"/>
     </row>
     <row r="76" spans="2:9" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B76" s="7" t="s">
+      <c r="B76" s="52" t="s">
         <v>90</v>
       </c>
-      <c r="C76" s="7"/>
-      <c r="D76" s="7"/>
-      <c r="E76" s="7"/>
-      <c r="F76" s="7"/>
-      <c r="G76" s="7"/>
-      <c r="H76" s="7"/>
-      <c r="I76" s="7"/>
+      <c r="C76" s="52"/>
+      <c r="D76" s="52"/>
+      <c r="E76" s="52"/>
+      <c r="F76" s="52"/>
+      <c r="G76" s="52"/>
+      <c r="H76" s="52"/>
+      <c r="I76" s="52"/>
     </row>
     <row r="77" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B77" s="3" t="s">
+      <c r="B77" s="58" t="s">
         <v>200</v>
       </c>
-      <c r="C77" s="3"/>
-      <c r="D77" s="3"/>
-      <c r="E77" s="3"/>
-      <c r="F77" s="3"/>
-      <c r="G77" s="3"/>
-      <c r="H77" s="3"/>
-      <c r="I77" s="3"/>
+      <c r="C77" s="58"/>
+      <c r="D77" s="58"/>
+      <c r="E77" s="58"/>
+      <c r="F77" s="58"/>
+      <c r="G77" s="58"/>
+      <c r="H77" s="58"/>
+      <c r="I77" s="58"/>
     </row>
     <row r="78" spans="2:9" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B78" s="1" t="s">
+      <c r="B78" s="57" t="s">
         <v>91</v>
       </c>
-      <c r="C78" s="1"/>
-      <c r="D78" s="1"/>
-      <c r="E78" s="1"/>
-      <c r="F78" s="1"/>
-      <c r="G78" s="1"/>
-      <c r="H78" s="1"/>
-      <c r="I78" s="1"/>
+      <c r="C78" s="57"/>
+      <c r="D78" s="57"/>
+      <c r="E78" s="57"/>
+      <c r="F78" s="57"/>
+      <c r="G78" s="57"/>
+      <c r="H78" s="57"/>
+      <c r="I78" s="57"/>
     </row>
     <row r="79" spans="2:9" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B79" s="8" t="s">
+      <c r="B79" s="51" t="s">
         <v>92</v>
       </c>
-      <c r="C79" s="8"/>
-      <c r="D79" s="8"/>
-      <c r="E79" s="8"/>
-      <c r="F79" s="8"/>
-      <c r="G79" s="8"/>
-      <c r="H79" s="8"/>
-      <c r="I79" s="8"/>
+      <c r="C79" s="51"/>
+      <c r="D79" s="51"/>
+      <c r="E79" s="51"/>
+      <c r="F79" s="51"/>
+      <c r="G79" s="51"/>
+      <c r="H79" s="51"/>
+      <c r="I79" s="51"/>
     </row>
     <row r="80" spans="2:9" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B80" s="1" t="s">
+      <c r="B80" s="57" t="s">
         <v>93</v>
       </c>
-      <c r="C80" s="1"/>
-      <c r="D80" s="1"/>
-      <c r="E80" s="1"/>
-      <c r="F80" s="1"/>
-      <c r="G80" s="1"/>
-      <c r="H80" s="1"/>
-      <c r="I80" s="1"/>
+      <c r="C80" s="57"/>
+      <c r="D80" s="57"/>
+      <c r="E80" s="57"/>
+      <c r="F80" s="57"/>
+      <c r="G80" s="57"/>
+      <c r="H80" s="57"/>
+      <c r="I80" s="57"/>
     </row>
     <row r="81" spans="2:9" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B81" s="8" t="s">
+      <c r="B81" s="51" t="s">
         <v>94</v>
       </c>
-      <c r="C81" s="8"/>
-      <c r="D81" s="8"/>
-      <c r="E81" s="8"/>
-      <c r="F81" s="8"/>
-      <c r="G81" s="8"/>
-      <c r="H81" s="8"/>
-      <c r="I81" s="8"/>
+      <c r="C81" s="51"/>
+      <c r="D81" s="51"/>
+      <c r="E81" s="51"/>
+      <c r="F81" s="51"/>
+      <c r="G81" s="51"/>
+      <c r="H81" s="51"/>
+      <c r="I81" s="51"/>
     </row>
     <row r="82" spans="2:9" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B82" s="1" t="s">
+      <c r="B82" s="57" t="s">
         <v>95</v>
       </c>
-      <c r="C82" s="1"/>
-      <c r="D82" s="1"/>
-      <c r="E82" s="1"/>
-      <c r="F82" s="1"/>
-      <c r="G82" s="1"/>
-      <c r="H82" s="1"/>
-      <c r="I82" s="1"/>
+      <c r="C82" s="57"/>
+      <c r="D82" s="57"/>
+      <c r="E82" s="57"/>
+      <c r="F82" s="57"/>
+      <c r="G82" s="57"/>
+      <c r="H82" s="57"/>
+      <c r="I82" s="57"/>
     </row>
     <row r="84" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B84" s="5" t="s">
+      <c r="B84" s="50" t="s">
         <v>2</v>
       </c>
-      <c r="C84" s="5"/>
-      <c r="D84" s="5"/>
-      <c r="E84" s="5"/>
-      <c r="F84" s="5"/>
-      <c r="G84" s="5"/>
-      <c r="H84" s="5"/>
-      <c r="I84" s="5"/>
+      <c r="C84" s="50"/>
+      <c r="D84" s="50"/>
+      <c r="E84" s="50"/>
+      <c r="F84" s="50"/>
+      <c r="G84" s="50"/>
+      <c r="H84" s="50"/>
+      <c r="I84" s="50"/>
     </row>
   </sheetData>
   <mergeCells count="36">
+    <mergeCell ref="B1:I1"/>
+    <mergeCell ref="B3:F3"/>
+    <mergeCell ref="B8:F8"/>
+    <mergeCell ref="B15:F15"/>
+    <mergeCell ref="B20:I20"/>
+    <mergeCell ref="B27:F27"/>
+    <mergeCell ref="B28:F28"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="B30:F30"/>
+    <mergeCell ref="B31:F31"/>
+    <mergeCell ref="B32:I32"/>
+    <mergeCell ref="B41:F41"/>
+    <mergeCell ref="B42:F42"/>
+    <mergeCell ref="B43:F43"/>
+    <mergeCell ref="B44:F44"/>
+    <mergeCell ref="B45:F45"/>
+    <mergeCell ref="B46:I46"/>
+    <mergeCell ref="B55:F55"/>
+    <mergeCell ref="B56:F56"/>
+    <mergeCell ref="B57:F57"/>
+    <mergeCell ref="B58:F58"/>
+    <mergeCell ref="B59:F59"/>
+    <mergeCell ref="B60:I60"/>
+    <mergeCell ref="B65:I65"/>
+    <mergeCell ref="B72:I72"/>
+    <mergeCell ref="B73:I73"/>
+    <mergeCell ref="B74:I74"/>
+    <mergeCell ref="B75:I75"/>
+    <mergeCell ref="B76:I76"/>
+    <mergeCell ref="B77:I77"/>
     <mergeCell ref="B84:I84"/>
     <mergeCell ref="B78:I78"/>
     <mergeCell ref="B79:I79"/>
     <mergeCell ref="B80:I80"/>
     <mergeCell ref="B81:I81"/>
     <mergeCell ref="B82:I82"/>
-    <mergeCell ref="B73:I73"/>
-    <mergeCell ref="B74:I74"/>
-    <mergeCell ref="B75:I75"/>
-    <mergeCell ref="B76:I76"/>
-    <mergeCell ref="B77:I77"/>
-    <mergeCell ref="B58:F58"/>
-    <mergeCell ref="B59:F59"/>
-    <mergeCell ref="B60:I60"/>
-    <mergeCell ref="B65:I65"/>
-    <mergeCell ref="B72:I72"/>
-    <mergeCell ref="B45:F45"/>
-    <mergeCell ref="B46:I46"/>
-    <mergeCell ref="B55:F55"/>
-    <mergeCell ref="B56:F56"/>
-    <mergeCell ref="B57:F57"/>
-    <mergeCell ref="B32:I32"/>
-    <mergeCell ref="B41:F41"/>
-    <mergeCell ref="B42:F42"/>
-    <mergeCell ref="B43:F43"/>
-    <mergeCell ref="B44:F44"/>
-    <mergeCell ref="B27:F27"/>
-    <mergeCell ref="B28:F28"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="B30:F30"/>
-    <mergeCell ref="B31:F31"/>
-    <mergeCell ref="B1:I1"/>
-    <mergeCell ref="B3:F3"/>
-    <mergeCell ref="B8:F8"/>
-    <mergeCell ref="B15:F15"/>
-    <mergeCell ref="B20:I20"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -2755,657 +2783,667 @@
   <dimension ref="A1:J48"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="2" style="14" customWidth="1"/>
-    <col min="2" max="2" width="51.140625" style="14" bestFit="1" customWidth="1"/>
-    <col min="3" max="6" width="13" style="14" customWidth="1"/>
-    <col min="7" max="9" width="14" style="14" customWidth="1"/>
-    <col min="10" max="10" width="2" style="14" customWidth="1"/>
+    <col min="1" max="1" width="2" style="1" customWidth="1"/>
+    <col min="2" max="2" width="51.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="6" width="13" style="1" customWidth="1"/>
+    <col min="7" max="9" width="14" style="1" customWidth="1"/>
+    <col min="10" max="10" width="2" style="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B1" s="4" t="s">
+      <c r="B1" s="63" t="s">
         <v>203</v>
       </c>
-      <c r="C1" s="4"/>
-      <c r="D1" s="4"/>
-      <c r="E1" s="4"/>
-      <c r="F1" s="4"/>
-      <c r="G1" s="4"/>
-      <c r="H1" s="4"/>
-      <c r="I1" s="4"/>
+      <c r="C1" s="63"/>
+      <c r="D1" s="63"/>
+      <c r="E1" s="63"/>
+      <c r="F1" s="63"/>
+      <c r="G1" s="63"/>
+      <c r="H1" s="63"/>
+      <c r="I1" s="63"/>
     </row>
     <row r="3" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="58" t="s">
         <v>96</v>
       </c>
-      <c r="C3" s="3"/>
-      <c r="D3" s="3"/>
-      <c r="E3" s="3"/>
-      <c r="F3" s="3"/>
+      <c r="C3" s="58"/>
+      <c r="D3" s="58"/>
+      <c r="E3" s="58"/>
+      <c r="F3" s="58"/>
     </row>
     <row r="4" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B4" s="20" t="s">
+      <c r="B4" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="C4" s="21" t="s">
+      <c r="C4" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="D4" s="21" t="s">
+      <c r="D4" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="E4" s="21" t="s">
+      <c r="E4" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="F4" s="21" t="s">
+      <c r="F4" s="8" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="5" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="23" t="s">
+      <c r="B5" s="10" t="s">
         <v>97</v>
       </c>
-      <c r="C5" s="24">
+      <c r="C5" s="11">
         <v>19379.09</v>
       </c>
-      <c r="D5" s="24">
+      <c r="D5" s="11">
         <v>17581.45</v>
       </c>
-      <c r="E5" s="24">
+      <c r="E5" s="11">
         <v>18733.53</v>
       </c>
-      <c r="F5" s="24">
+      <c r="F5" s="11">
         <v>19484.52</v>
       </c>
     </row>
     <row r="6" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="17" t="s">
+      <c r="B6" s="4" t="s">
         <v>98</v>
       </c>
-      <c r="C6" s="22">
+      <c r="C6" s="9">
         <v>4569.93</v>
       </c>
-      <c r="D6" s="22">
+      <c r="D6" s="9">
         <v>807.53</v>
       </c>
-      <c r="E6" s="22">
+      <c r="E6" s="9">
         <v>1027.49</v>
       </c>
-      <c r="F6" s="22">
+      <c r="F6" s="9">
         <v>3044.8</v>
       </c>
     </row>
     <row r="7" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B7" s="25" t="s">
+      <c r="B7" s="12" t="s">
         <v>99</v>
       </c>
-      <c r="C7" s="26">
+      <c r="C7" s="13">
         <v>938.17</v>
       </c>
-      <c r="D7" s="26">
+      <c r="D7" s="13">
         <v>969.3</v>
       </c>
-      <c r="E7" s="26">
+      <c r="E7" s="13">
         <v>1106.48</v>
       </c>
-      <c r="F7" s="26">
+      <c r="F7" s="13">
         <v>1489.51</v>
       </c>
     </row>
     <row r="8" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B8" s="27" t="s">
+      <c r="B8" s="14" t="s">
         <v>100</v>
       </c>
-      <c r="C8" s="28">
+      <c r="C8" s="15">
         <v>5631.44</v>
       </c>
-      <c r="D8" s="28">
+      <c r="D8" s="15">
         <v>6479.15</v>
       </c>
-      <c r="E8" s="28">
+      <c r="E8" s="15">
         <v>7867.28</v>
       </c>
-      <c r="F8" s="28">
+      <c r="F8" s="15">
         <v>8623.7199999999993</v>
       </c>
     </row>
     <row r="9" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B9" s="17" t="s">
+      <c r="B9" s="4" t="s">
         <v>101</v>
       </c>
-      <c r="C9" s="22">
+      <c r="C9" s="9">
         <v>6315.42</v>
       </c>
-      <c r="D9" s="22">
+      <c r="D9" s="9">
         <v>6030.58</v>
       </c>
-      <c r="E9" s="22">
+      <c r="E9" s="9">
         <v>5515.77</v>
       </c>
-      <c r="F9" s="22">
+      <c r="F9" s="9">
         <v>4889.51</v>
       </c>
     </row>
     <row r="10" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B10" s="25" t="s">
+      <c r="B10" s="12" t="s">
         <v>102</v>
       </c>
-      <c r="C10" s="26">
+      <c r="C10" s="13">
         <v>230.5</v>
       </c>
-      <c r="D10" s="26">
+      <c r="D10" s="13">
         <v>626.29</v>
       </c>
-      <c r="E10" s="26">
+      <c r="E10" s="13">
         <v>252.4</v>
       </c>
-      <c r="F10" s="26">
+      <c r="F10" s="13">
         <v>344.87</v>
       </c>
     </row>
     <row r="12" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B12" s="3" t="s">
+      <c r="B12" s="58" t="s">
         <v>103</v>
       </c>
-      <c r="C12" s="3"/>
-      <c r="D12" s="3"/>
-      <c r="E12" s="3"/>
-      <c r="F12" s="3"/>
-      <c r="G12" s="3"/>
-      <c r="H12" s="3"/>
-      <c r="I12" s="3"/>
+      <c r="C12" s="58"/>
+      <c r="D12" s="58"/>
+      <c r="E12" s="58"/>
+      <c r="F12" s="58"/>
+      <c r="G12" s="58"/>
+      <c r="H12" s="58"/>
+      <c r="I12" s="58"/>
     </row>
     <row r="13" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B13" s="20" t="s">
+      <c r="B13" s="7" t="s">
         <v>104</v>
       </c>
-      <c r="C13" s="21" t="s">
+      <c r="C13" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="D13" s="21" t="s">
+      <c r="D13" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="E13" s="21" t="s">
+      <c r="E13" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="F13" s="21" t="s">
+      <c r="F13" s="8" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="14" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B14" s="17" t="s">
+      <c r="B14" s="4" t="s">
         <v>105</v>
       </c>
-      <c r="C14" s="39">
+      <c r="C14" s="26">
         <f>C6</f>
         <v>4569.93</v>
       </c>
-      <c r="D14" s="39">
+      <c r="D14" s="26">
         <f>D6</f>
         <v>807.53</v>
       </c>
-      <c r="E14" s="39">
+      <c r="E14" s="26">
         <f>E6</f>
         <v>1027.49</v>
       </c>
-      <c r="F14" s="39">
+      <c r="F14" s="26">
         <f>F6</f>
         <v>3044.8</v>
       </c>
     </row>
     <row r="15" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B15" s="25" t="s">
+      <c r="B15" s="12" t="s">
         <v>106</v>
       </c>
-      <c r="C15" s="40">
+      <c r="C15" s="27">
         <f>C8</f>
         <v>5631.44</v>
       </c>
-      <c r="D15" s="40">
+      <c r="D15" s="27">
         <f>D8</f>
         <v>6479.15</v>
       </c>
-      <c r="E15" s="40">
+      <c r="E15" s="27">
         <f>E8</f>
         <v>7867.28</v>
       </c>
-      <c r="F15" s="40">
+      <c r="F15" s="27">
         <f>F8</f>
         <v>8623.7199999999993</v>
       </c>
     </row>
     <row r="16" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B16" s="23" t="s">
+      <c r="B16" s="10" t="s">
         <v>107</v>
       </c>
-      <c r="C16" s="29">
+      <c r="C16" s="16">
         <f>C14-C15</f>
         <v>-1061.5099999999993</v>
       </c>
-      <c r="D16" s="29">
+      <c r="D16" s="16">
         <f>D14-D15</f>
         <v>-5671.62</v>
       </c>
-      <c r="E16" s="29">
+      <c r="E16" s="16">
         <f>E14-E15</f>
         <v>-6839.79</v>
       </c>
-      <c r="F16" s="29">
+      <c r="F16" s="16">
         <f>F14-F15</f>
         <v>-5578.9199999999992</v>
       </c>
     </row>
     <row r="17" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B17" s="17" t="s">
+      <c r="B17" s="4" t="s">
         <v>108</v>
       </c>
-      <c r="C17" s="41">
+      <c r="C17" s="28">
         <f>C14*365/19381.71</f>
         <v>86.061779378599738</v>
       </c>
-      <c r="D17" s="41">
+      <c r="D17" s="28">
         <f>D14*365/20281.57</f>
         <v>14.532822163175732</v>
       </c>
-      <c r="E17" s="41">
+      <c r="E17" s="28">
         <f>E14*365/21732.58</f>
         <v>17.256756905990912</v>
       </c>
-      <c r="F17" s="41">
+      <c r="F17" s="28">
         <f>F14*365/19869.35</f>
         <v>55.932982206262416</v>
       </c>
     </row>
     <row r="19" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B19" s="3" t="s">
+      <c r="B19" s="58" t="s">
         <v>109</v>
       </c>
-      <c r="C19" s="3"/>
-      <c r="D19" s="3"/>
-      <c r="E19" s="3"/>
-      <c r="F19" s="3"/>
-      <c r="G19" s="3"/>
-      <c r="H19" s="3"/>
-      <c r="I19" s="3"/>
+      <c r="C19" s="58"/>
+      <c r="D19" s="58"/>
+      <c r="E19" s="58"/>
+      <c r="F19" s="58"/>
+      <c r="G19" s="58"/>
+      <c r="H19" s="58"/>
+      <c r="I19" s="58"/>
     </row>
     <row r="20" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B20" s="20" t="s">
+      <c r="B20" s="7" t="s">
         <v>110</v>
       </c>
-      <c r="C20" s="21" t="s">
+      <c r="C20" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="D20" s="21" t="s">
+      <c r="D20" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="E20" s="21" t="s">
+      <c r="E20" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="F20" s="21" t="s">
+      <c r="F20" s="8" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="21" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B21" s="17" t="s">
+      <c r="B21" s="4" t="s">
         <v>111</v>
       </c>
-      <c r="C21" s="42">
+      <c r="C21" s="29">
         <f>C7/C6</f>
         <v>0.20529198477876026</v>
       </c>
-      <c r="D21" s="42">
+      <c r="D21" s="29">
         <f>D7/D6</f>
         <v>1.2003269228387801</v>
       </c>
-      <c r="E21" s="42">
+      <c r="E21" s="29">
         <f>E7/E6</f>
         <v>1.0768766606001032</v>
       </c>
-      <c r="F21" s="42">
+      <c r="F21" s="29">
         <f>F7/F6</f>
         <v>0.48919797687861266</v>
       </c>
     </row>
     <row r="22" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B22" s="25" t="s">
+      <c r="B22" s="12" t="s">
         <v>112</v>
       </c>
-      <c r="C22" s="43">
+      <c r="C22" s="30">
         <f>C5/C6</f>
         <v>4.2405660480576284</v>
       </c>
-      <c r="D22" s="43">
+      <c r="D22" s="30">
         <f>D5/D6</f>
         <v>21.771884635864922</v>
       </c>
-      <c r="E22" s="43">
+      <c r="E22" s="30">
         <f>E5/E6</f>
         <v>18.232323428938479</v>
       </c>
-      <c r="F22" s="43">
+      <c r="F22" s="30">
         <f>F5/F6</f>
         <v>6.3992774566473987</v>
       </c>
     </row>
     <row r="23" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B23" s="17" t="s">
+      <c r="B23" s="4" t="s">
         <v>113</v>
       </c>
-      <c r="C23" s="44" t="s">
+      <c r="C23" s="31" t="s">
         <v>114</v>
       </c>
-      <c r="D23" s="45">
+      <c r="D23" s="32">
         <v>2.02</v>
       </c>
-      <c r="E23" s="45">
+      <c r="E23" s="32">
         <v>2.11</v>
       </c>
-      <c r="F23" s="45">
+      <c r="F23" s="32">
         <v>2.0499999999999998</v>
       </c>
     </row>
     <row r="24" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B24" s="25" t="s">
+      <c r="B24" s="12" t="s">
         <v>115</v>
       </c>
-      <c r="C24" s="46" t="s">
+      <c r="C24" s="33" t="s">
         <v>114</v>
       </c>
-      <c r="D24" s="47">
+      <c r="D24" s="34">
         <v>0.99</v>
       </c>
-      <c r="E24" s="47">
+      <c r="E24" s="34">
         <v>0.76</v>
       </c>
-      <c r="F24" s="47">
+      <c r="F24" s="34">
         <v>0.62</v>
       </c>
     </row>
     <row r="25" spans="2:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="26" spans="2:9" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B26" s="63" t="s">
+      <c r="B26" s="59" t="s">
         <v>116</v>
       </c>
-      <c r="C26" s="64"/>
-      <c r="D26" s="64"/>
-      <c r="E26" s="64"/>
-      <c r="F26" s="65"/>
+      <c r="C26" s="60"/>
+      <c r="D26" s="60"/>
+      <c r="E26" s="60"/>
+      <c r="F26" s="61"/>
     </row>
     <row r="27" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B27" s="66" t="s">
+      <c r="B27" s="65" t="s">
         <v>117</v>
       </c>
-      <c r="C27" s="66"/>
-      <c r="D27" s="66"/>
-      <c r="E27" s="66"/>
-      <c r="F27" s="66"/>
+      <c r="C27" s="65"/>
+      <c r="D27" s="65"/>
+      <c r="E27" s="65"/>
+      <c r="F27" s="65"/>
     </row>
     <row r="28" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B28" s="7" t="s">
+      <c r="B28" s="52" t="s">
         <v>118</v>
       </c>
-      <c r="C28" s="7"/>
-      <c r="D28" s="7"/>
-      <c r="E28" s="7"/>
-      <c r="F28" s="7"/>
+      <c r="C28" s="52"/>
+      <c r="D28" s="52"/>
+      <c r="E28" s="52"/>
+      <c r="F28" s="52"/>
     </row>
     <row r="29" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B29" s="8" t="s">
+      <c r="B29" s="51" t="s">
         <v>119</v>
       </c>
-      <c r="C29" s="8"/>
-      <c r="D29" s="8"/>
-      <c r="E29" s="8"/>
-      <c r="F29" s="8"/>
+      <c r="C29" s="51"/>
+      <c r="D29" s="51"/>
+      <c r="E29" s="51"/>
+      <c r="F29" s="51"/>
     </row>
     <row r="30" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B30" s="7" t="s">
+      <c r="B30" s="52" t="s">
         <v>120</v>
       </c>
-      <c r="C30" s="7"/>
-      <c r="D30" s="7"/>
-      <c r="E30" s="7"/>
-      <c r="F30" s="7"/>
+      <c r="C30" s="52"/>
+      <c r="D30" s="52"/>
+      <c r="E30" s="52"/>
+      <c r="F30" s="52"/>
     </row>
     <row r="31" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B31" s="3" t="s">
+      <c r="B31" s="58" t="s">
         <v>121</v>
       </c>
-      <c r="C31" s="3"/>
-      <c r="D31" s="3"/>
-      <c r="E31" s="3"/>
-      <c r="F31" s="3"/>
-      <c r="G31" s="3"/>
-      <c r="H31" s="3"/>
-      <c r="I31" s="3"/>
+      <c r="C31" s="58"/>
+      <c r="D31" s="58"/>
+      <c r="E31" s="58"/>
+      <c r="F31" s="58"/>
+      <c r="G31" s="58"/>
+      <c r="H31" s="58"/>
+      <c r="I31" s="58"/>
     </row>
     <row r="32" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B32" s="20" t="s">
+      <c r="B32" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="C32" s="21" t="s">
+      <c r="C32" s="8" t="s">
         <v>77</v>
       </c>
-      <c r="D32" s="21" t="s">
+      <c r="D32" s="8" t="s">
         <v>78</v>
       </c>
-      <c r="E32" s="21" t="s">
+      <c r="E32" s="8" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="33" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B33" s="33" t="s">
+      <c r="B33" s="20" t="s">
         <v>122</v>
       </c>
-      <c r="C33" s="34">
+      <c r="C33" s="21">
         <v>0.09</v>
       </c>
-      <c r="D33" s="34">
+      <c r="D33" s="21">
         <v>0.1</v>
       </c>
-      <c r="E33" s="34">
+      <c r="E33" s="21">
         <v>0.11</v>
       </c>
     </row>
     <row r="34" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B34" s="33" t="s">
+      <c r="B34" s="20" t="s">
         <v>123</v>
       </c>
-      <c r="C34" s="24">
+      <c r="C34" s="11">
         <v>300</v>
       </c>
-      <c r="D34" s="24">
+      <c r="D34" s="11">
         <v>300</v>
       </c>
-      <c r="E34" s="24">
+      <c r="E34" s="11">
         <v>300</v>
       </c>
     </row>
     <row r="35" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B35" s="33" t="s">
+      <c r="B35" s="20" t="s">
         <v>124</v>
       </c>
-      <c r="C35" s="34">
+      <c r="C35" s="21">
         <v>0.08</v>
       </c>
-      <c r="D35" s="34">
+      <c r="D35" s="21">
         <v>0.08</v>
       </c>
-      <c r="E35" s="34">
+      <c r="E35" s="21">
         <v>0.08</v>
       </c>
     </row>
     <row r="36" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B36" s="3" t="s">
+      <c r="B36" s="58" t="s">
         <v>125</v>
       </c>
-      <c r="C36" s="3"/>
-      <c r="D36" s="3"/>
-      <c r="E36" s="3"/>
-      <c r="F36" s="3"/>
-      <c r="G36" s="3"/>
-      <c r="H36" s="3"/>
-      <c r="I36" s="3"/>
+      <c r="C36" s="58"/>
+      <c r="D36" s="58"/>
+      <c r="E36" s="58"/>
+      <c r="F36" s="58"/>
+      <c r="G36" s="58"/>
+      <c r="H36" s="58"/>
+      <c r="I36" s="58"/>
     </row>
     <row r="37" spans="2:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B37" s="20" t="s">
+      <c r="B37" s="7" t="s">
         <v>83</v>
       </c>
-      <c r="C37" s="35" t="s">
+      <c r="C37" s="22" t="s">
         <v>77</v>
       </c>
-      <c r="D37" s="35" t="s">
+      <c r="D37" s="22" t="s">
         <v>78</v>
       </c>
-      <c r="E37" s="35" t="s">
+      <c r="E37" s="22" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="38" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B38" s="38">
+      <c r="B38" s="25">
         <f>8623.72</f>
         <v>8623.7199999999993</v>
       </c>
-      <c r="C38" s="38">
+      <c r="C38" s="25">
         <f>B38*(1+C33)</f>
         <v>9399.8547999999992</v>
       </c>
-      <c r="D38" s="38">
+      <c r="D38" s="25">
         <f>C38*(1+D33)</f>
         <v>10339.84028</v>
       </c>
-      <c r="E38" s="38">
+      <c r="E38" s="25">
         <f>D38*(1+E33)</f>
         <v>11477.222710800001</v>
       </c>
     </row>
     <row r="39" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B39" s="37">
+      <c r="B39" s="24">
         <f>4889.51</f>
         <v>4889.51</v>
       </c>
-      <c r="C39" s="37">
+      <c r="C39" s="24">
         <f>B39-C34</f>
         <v>4589.51</v>
       </c>
-      <c r="D39" s="37">
+      <c r="D39" s="24">
         <f>C39-D34</f>
         <v>4289.51</v>
       </c>
-      <c r="E39" s="37">
+      <c r="E39" s="24">
         <f>D39-E34</f>
         <v>3989.51</v>
       </c>
     </row>
     <row r="40" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B40" s="36">
+      <c r="B40" s="23">
         <f>1489.51</f>
         <v>1489.51</v>
       </c>
-      <c r="C40" s="36">
+      <c r="C40" s="23">
         <f>B40*(1+C35)</f>
         <v>1608.6708000000001</v>
       </c>
-      <c r="D40" s="36">
+      <c r="D40" s="23">
         <f>C40*(1+D35)</f>
         <v>1737.3644640000002</v>
       </c>
-      <c r="E40" s="36">
+      <c r="E40" s="23">
         <f>D40*(1+E35)</f>
         <v>1876.3536211200003</v>
       </c>
     </row>
     <row r="41" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B41" s="42">
+      <c r="B41" s="29">
         <f>4889.51/8623.72</f>
         <v>0.56698385383569971</v>
       </c>
-      <c r="C41" s="42">
+      <c r="C41" s="29">
         <f>C39/C38</f>
         <v>0.48825328663587447</v>
       </c>
-      <c r="D41" s="42">
+      <c r="D41" s="29">
         <f>D39/D38</f>
         <v>0.41485263638907971</v>
       </c>
-      <c r="E41" s="42">
+      <c r="E41" s="29">
         <f>E39/E38</f>
         <v>0.34760238609344873</v>
       </c>
     </row>
     <row r="42" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B42" s="3" t="s">
+      <c r="B42" s="58" t="s">
         <v>126</v>
       </c>
-      <c r="C42" s="3"/>
-      <c r="D42" s="3"/>
-      <c r="E42" s="3"/>
-      <c r="F42" s="3"/>
-      <c r="G42" s="3"/>
-      <c r="H42" s="3"/>
-      <c r="I42" s="3"/>
+      <c r="C42" s="58"/>
+      <c r="D42" s="58"/>
+      <c r="E42" s="58"/>
+      <c r="F42" s="58"/>
+      <c r="G42" s="58"/>
+      <c r="H42" s="58"/>
+      <c r="I42" s="58"/>
     </row>
     <row r="43" spans="2:9" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B43" s="8" t="s">
+      <c r="B43" s="51" t="s">
         <v>127</v>
       </c>
-      <c r="C43" s="8"/>
-      <c r="D43" s="8"/>
-      <c r="E43" s="8"/>
-      <c r="F43" s="8"/>
-      <c r="G43" s="8"/>
-      <c r="H43" s="8"/>
-      <c r="I43" s="8"/>
+      <c r="C43" s="51"/>
+      <c r="D43" s="51"/>
+      <c r="E43" s="51"/>
+      <c r="F43" s="51"/>
+      <c r="G43" s="51"/>
+      <c r="H43" s="51"/>
+      <c r="I43" s="51"/>
     </row>
     <row r="44" spans="2:9" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B44" s="1" t="s">
+      <c r="B44" s="57" t="s">
         <v>128</v>
       </c>
-      <c r="C44" s="1"/>
-      <c r="D44" s="1"/>
-      <c r="E44" s="1"/>
-      <c r="F44" s="1"/>
-      <c r="G44" s="1"/>
-      <c r="H44" s="1"/>
-      <c r="I44" s="1"/>
+      <c r="C44" s="57"/>
+      <c r="D44" s="57"/>
+      <c r="E44" s="57"/>
+      <c r="F44" s="57"/>
+      <c r="G44" s="57"/>
+      <c r="H44" s="57"/>
+      <c r="I44" s="57"/>
     </row>
     <row r="45" spans="2:9" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B45" s="8" t="s">
+      <c r="B45" s="51" t="s">
         <v>129</v>
       </c>
-      <c r="C45" s="8"/>
-      <c r="D45" s="8"/>
-      <c r="E45" s="8"/>
-      <c r="F45" s="8"/>
-      <c r="G45" s="8"/>
-      <c r="H45" s="8"/>
-      <c r="I45" s="8"/>
+      <c r="C45" s="51"/>
+      <c r="D45" s="51"/>
+      <c r="E45" s="51"/>
+      <c r="F45" s="51"/>
+      <c r="G45" s="51"/>
+      <c r="H45" s="51"/>
+      <c r="I45" s="51"/>
     </row>
     <row r="46" spans="2:9" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B46" s="1" t="s">
+      <c r="B46" s="57" t="s">
         <v>130</v>
       </c>
-      <c r="C46" s="1"/>
-      <c r="D46" s="1"/>
-      <c r="E46" s="1"/>
-      <c r="F46" s="1"/>
-      <c r="G46" s="1"/>
-      <c r="H46" s="1"/>
-      <c r="I46" s="1"/>
+      <c r="C46" s="57"/>
+      <c r="D46" s="57"/>
+      <c r="E46" s="57"/>
+      <c r="F46" s="57"/>
+      <c r="G46" s="57"/>
+      <c r="H46" s="57"/>
+      <c r="I46" s="57"/>
     </row>
     <row r="48" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B48" s="5" t="s">
+      <c r="B48" s="50" t="s">
         <v>2</v>
       </c>
-      <c r="C48" s="5"/>
-      <c r="D48" s="5"/>
-      <c r="E48" s="5"/>
-      <c r="F48" s="5"/>
-      <c r="G48" s="5"/>
-      <c r="H48" s="5"/>
-      <c r="I48" s="5"/>
+      <c r="C48" s="50"/>
+      <c r="D48" s="50"/>
+      <c r="E48" s="50"/>
+      <c r="F48" s="50"/>
+      <c r="G48" s="50"/>
+      <c r="H48" s="50"/>
+      <c r="I48" s="50"/>
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="B1:I1"/>
+    <mergeCell ref="B3:F3"/>
+    <mergeCell ref="B12:I12"/>
+    <mergeCell ref="B19:I19"/>
+    <mergeCell ref="B26:F26"/>
+    <mergeCell ref="B27:F27"/>
+    <mergeCell ref="B28:F28"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="B30:F30"/>
+    <mergeCell ref="B31:I31"/>
     <mergeCell ref="B46:I46"/>
     <mergeCell ref="B48:I48"/>
     <mergeCell ref="B36:I36"/>
@@ -3413,16 +3451,6 @@
     <mergeCell ref="B43:I43"/>
     <mergeCell ref="B44:I44"/>
     <mergeCell ref="B45:I45"/>
-    <mergeCell ref="B27:F27"/>
-    <mergeCell ref="B28:F28"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="B30:F30"/>
-    <mergeCell ref="B31:I31"/>
-    <mergeCell ref="B1:I1"/>
-    <mergeCell ref="B3:F3"/>
-    <mergeCell ref="B12:I12"/>
-    <mergeCell ref="B19:I19"/>
-    <mergeCell ref="B26:F26"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -3434,553 +3462,563 @@
   <dimension ref="A1:J42"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="2" style="14" customWidth="1"/>
-    <col min="2" max="2" width="46.85546875" style="14" bestFit="1" customWidth="1"/>
-    <col min="3" max="5" width="13" style="14" customWidth="1"/>
-    <col min="6" max="6" width="9.85546875" style="14" bestFit="1" customWidth="1"/>
-    <col min="7" max="9" width="14" style="14" customWidth="1"/>
-    <col min="10" max="10" width="2" style="14" customWidth="1"/>
+    <col min="1" max="1" width="2" style="1" customWidth="1"/>
+    <col min="2" max="2" width="46.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="5" width="13" style="1" customWidth="1"/>
+    <col min="6" max="6" width="9.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="9" width="14" style="1" customWidth="1"/>
+    <col min="10" max="10" width="2" style="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B1" s="4" t="s">
+      <c r="B1" s="63" t="s">
         <v>131</v>
       </c>
-      <c r="C1" s="4"/>
-      <c r="D1" s="4"/>
-      <c r="E1" s="4"/>
-      <c r="F1" s="4"/>
-      <c r="G1" s="4"/>
-      <c r="H1" s="4"/>
-      <c r="I1" s="4"/>
+      <c r="C1" s="63"/>
+      <c r="D1" s="63"/>
+      <c r="E1" s="63"/>
+      <c r="F1" s="63"/>
+      <c r="G1" s="63"/>
+      <c r="H1" s="63"/>
+      <c r="I1" s="63"/>
     </row>
     <row r="3" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="58" t="s">
         <v>132</v>
       </c>
-      <c r="C3" s="3"/>
-      <c r="D3" s="3"/>
-      <c r="E3" s="3"/>
-      <c r="F3" s="3"/>
+      <c r="C3" s="58"/>
+      <c r="D3" s="58"/>
+      <c r="E3" s="58"/>
+      <c r="F3" s="58"/>
     </row>
     <row r="4" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B4" s="20" t="s">
+      <c r="B4" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="C4" s="21" t="s">
+      <c r="C4" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="D4" s="21" t="s">
+      <c r="D4" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="E4" s="21" t="s">
+      <c r="E4" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="F4" s="21" t="s">
+      <c r="F4" s="8" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="5" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="23" t="s">
+      <c r="B5" s="10" t="s">
         <v>133</v>
       </c>
-      <c r="C5" s="24">
+      <c r="C5" s="11">
         <v>4806.17</v>
       </c>
-      <c r="D5" s="24">
+      <c r="D5" s="11">
         <v>-4080.06</v>
       </c>
-      <c r="E5" s="24">
+      <c r="E5" s="11">
         <v>2939.27</v>
       </c>
-      <c r="F5" s="24">
+      <c r="F5" s="11">
         <v>1919.9</v>
       </c>
     </row>
     <row r="6" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="17" t="s">
+      <c r="B6" s="4" t="s">
         <v>134</v>
       </c>
-      <c r="C6" s="22">
+      <c r="C6" s="9">
         <v>-1462.83</v>
       </c>
-      <c r="D6" s="22">
+      <c r="D6" s="9">
         <v>1353.66</v>
       </c>
-      <c r="E6" s="22">
+      <c r="E6" s="9">
         <v>-1431.35</v>
       </c>
-      <c r="F6" s="22">
+      <c r="F6" s="9">
         <v>1581.62</v>
       </c>
     </row>
     <row r="7" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B7" s="25" t="s">
+      <c r="B7" s="12" t="s">
         <v>135</v>
       </c>
-      <c r="C7" s="26">
+      <c r="C7" s="13">
         <v>-189.36</v>
       </c>
-      <c r="D7" s="26">
+      <c r="D7" s="13">
         <v>-1036.01</v>
       </c>
-      <c r="E7" s="26">
+      <c r="E7" s="13">
         <v>-1286.56</v>
       </c>
-      <c r="F7" s="26">
+      <c r="F7" s="13">
         <v>-1484.17</v>
       </c>
     </row>
     <row r="8" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B8" s="27" t="s">
+      <c r="B8" s="14" t="s">
         <v>136</v>
       </c>
-      <c r="C8" s="38">
+      <c r="C8" s="25">
         <f>C5+C6+C7</f>
         <v>3153.98</v>
       </c>
-      <c r="D8" s="38">
+      <c r="D8" s="25">
         <f>D5+D6+D7</f>
         <v>-3762.41</v>
       </c>
-      <c r="E8" s="38">
+      <c r="E8" s="25">
         <f>E5+E6+E7</f>
         <v>221.36000000000013</v>
       </c>
-      <c r="F8" s="38">
+      <c r="F8" s="25">
         <f>F5+F6+F7</f>
         <v>2017.35</v>
       </c>
     </row>
     <row r="9" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B9" s="27" t="s">
+      <c r="B9" s="14" t="s">
         <v>137</v>
       </c>
-      <c r="C9" s="28">
+      <c r="C9" s="15">
         <v>4569.93</v>
       </c>
-      <c r="D9" s="28">
+      <c r="D9" s="15">
         <v>807.53</v>
       </c>
-      <c r="E9" s="28">
+      <c r="E9" s="15">
         <v>1027.49</v>
       </c>
-      <c r="F9" s="28">
+      <c r="F9" s="15">
         <v>3044.8</v>
       </c>
     </row>
     <row r="11" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B11" s="3" t="s">
+      <c r="B11" s="58" t="s">
         <v>210</v>
       </c>
-      <c r="C11" s="3"/>
-      <c r="D11" s="3"/>
-      <c r="E11" s="3"/>
-      <c r="F11" s="3"/>
-      <c r="G11" s="3"/>
-      <c r="H11" s="3"/>
-      <c r="I11" s="3"/>
+      <c r="C11" s="58"/>
+      <c r="D11" s="58"/>
+      <c r="E11" s="58"/>
+      <c r="F11" s="58"/>
+      <c r="G11" s="58"/>
+      <c r="H11" s="58"/>
+      <c r="I11" s="58"/>
     </row>
     <row r="12" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B12" s="20" t="s">
+      <c r="B12" s="7" t="s">
         <v>104</v>
       </c>
-      <c r="C12" s="21" t="s">
+      <c r="C12" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="D12" s="21" t="s">
+      <c r="D12" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="E12" s="21" t="s">
+      <c r="E12" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="F12" s="21" t="s">
+      <c r="F12" s="8" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="13" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B13" s="17" t="s">
+      <c r="B13" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="C13" s="22">
+      <c r="C13" s="9">
         <v>1087.3499999999999</v>
       </c>
-      <c r="D13" s="22">
+      <c r="D13" s="9">
         <v>1267.97</v>
       </c>
-      <c r="E13" s="22">
+      <c r="E13" s="9">
         <v>1462.95</v>
       </c>
-      <c r="F13" s="22">
+      <c r="F13" s="9">
         <v>1188.6199999999999</v>
       </c>
     </row>
     <row r="14" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B14" s="25" t="s">
+      <c r="B14" s="12" t="s">
         <v>138</v>
       </c>
-      <c r="C14" s="26">
+      <c r="C14" s="13">
         <v>4806.17</v>
       </c>
-      <c r="D14" s="26">
+      <c r="D14" s="13">
         <v>-4080.06</v>
       </c>
-      <c r="E14" s="26">
+      <c r="E14" s="13">
         <v>2939.27</v>
       </c>
-      <c r="F14" s="26">
+      <c r="F14" s="13">
         <v>1919.9</v>
       </c>
     </row>
     <row r="15" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B15" s="23" t="s">
+      <c r="B15" s="10" t="s">
         <v>139</v>
       </c>
-      <c r="C15" s="29">
+      <c r="C15" s="16">
         <f>C14-C13</f>
         <v>3718.82</v>
       </c>
-      <c r="D15" s="29">
+      <c r="D15" s="16">
         <f>D14-D13</f>
         <v>-5348.03</v>
       </c>
-      <c r="E15" s="29">
+      <c r="E15" s="16">
         <f>E14-E13</f>
         <v>1476.32</v>
       </c>
-      <c r="F15" s="29">
+      <c r="F15" s="16">
         <f>F14-F13</f>
         <v>731.2800000000002</v>
       </c>
     </row>
     <row r="16" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B16" s="17" t="s">
+      <c r="B16" s="4" t="s">
         <v>140</v>
       </c>
-      <c r="C16" s="42">
+      <c r="C16" s="29">
         <f>C14/C13</f>
         <v>4.4200763323676835</v>
       </c>
-      <c r="D16" s="42">
+      <c r="D16" s="29">
         <f>D14/D13</f>
         <v>-3.2177890644100411</v>
       </c>
-      <c r="E16" s="42">
+      <c r="E16" s="29">
         <f>E14/E13</f>
         <v>2.0091390683208585</v>
       </c>
-      <c r="F16" s="42">
+      <c r="F16" s="29">
         <f>F14/F13</f>
         <v>1.6152344735912236</v>
       </c>
     </row>
     <row r="17" spans="2:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="18" spans="2:9" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B18" s="63" t="s">
+      <c r="B18" s="59" t="s">
         <v>141</v>
       </c>
-      <c r="C18" s="64"/>
-      <c r="D18" s="64"/>
-      <c r="E18" s="64"/>
-      <c r="F18" s="65"/>
+      <c r="C18" s="60"/>
+      <c r="D18" s="60"/>
+      <c r="E18" s="60"/>
+      <c r="F18" s="61"/>
     </row>
     <row r="19" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B19" s="66" t="s">
+      <c r="B19" s="65" t="s">
         <v>142</v>
       </c>
-      <c r="C19" s="66"/>
-      <c r="D19" s="66"/>
-      <c r="E19" s="66"/>
-      <c r="F19" s="66"/>
+      <c r="C19" s="65"/>
+      <c r="D19" s="65"/>
+      <c r="E19" s="65"/>
+      <c r="F19" s="65"/>
     </row>
     <row r="20" spans="2:9" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B20" s="7" t="s">
+      <c r="B20" s="52" t="s">
         <v>143</v>
       </c>
-      <c r="C20" s="7"/>
-      <c r="D20" s="7"/>
-      <c r="E20" s="7"/>
-      <c r="F20" s="7"/>
+      <c r="C20" s="52"/>
+      <c r="D20" s="52"/>
+      <c r="E20" s="52"/>
+      <c r="F20" s="52"/>
     </row>
     <row r="21" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B21" s="8" t="s">
+      <c r="B21" s="51" t="s">
         <v>144</v>
       </c>
-      <c r="C21" s="8"/>
-      <c r="D21" s="8"/>
-      <c r="E21" s="8"/>
-      <c r="F21" s="8"/>
+      <c r="C21" s="51"/>
+      <c r="D21" s="51"/>
+      <c r="E21" s="51"/>
+      <c r="F21" s="51"/>
     </row>
     <row r="22" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B22" s="7" t="s">
+      <c r="B22" s="52" t="s">
         <v>145</v>
       </c>
-      <c r="C22" s="7"/>
-      <c r="D22" s="7"/>
-      <c r="E22" s="7"/>
-      <c r="F22" s="7"/>
+      <c r="C22" s="52"/>
+      <c r="D22" s="52"/>
+      <c r="E22" s="52"/>
+      <c r="F22" s="52"/>
     </row>
     <row r="23" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B23" s="8" t="s">
+      <c r="B23" s="51" t="s">
         <v>146</v>
       </c>
-      <c r="C23" s="8"/>
-      <c r="D23" s="8"/>
-      <c r="E23" s="8"/>
-      <c r="F23" s="8"/>
+      <c r="C23" s="51"/>
+      <c r="D23" s="51"/>
+      <c r="E23" s="51"/>
+      <c r="F23" s="51"/>
     </row>
     <row r="24" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B24" s="3" t="s">
+      <c r="B24" s="58" t="s">
         <v>208</v>
       </c>
-      <c r="C24" s="3"/>
-      <c r="D24" s="3"/>
-      <c r="E24" s="3"/>
-      <c r="F24" s="3"/>
-      <c r="G24" s="3"/>
-      <c r="H24" s="3"/>
-      <c r="I24" s="3"/>
+      <c r="C24" s="58"/>
+      <c r="D24" s="58"/>
+      <c r="E24" s="58"/>
+      <c r="F24" s="58"/>
+      <c r="G24" s="58"/>
+      <c r="H24" s="58"/>
+      <c r="I24" s="58"/>
     </row>
     <row r="25" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B25" s="20" t="s">
+      <c r="B25" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="C25" s="21" t="s">
+      <c r="C25" s="8" t="s">
         <v>77</v>
       </c>
-      <c r="D25" s="21" t="s">
+      <c r="D25" s="8" t="s">
         <v>78</v>
       </c>
-      <c r="E25" s="21" t="s">
+      <c r="E25" s="8" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="26" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B26" s="33" t="s">
+      <c r="B26" s="20" t="s">
         <v>147</v>
       </c>
-      <c r="C26" s="24">
+      <c r="C26" s="11">
         <v>1350</v>
       </c>
-      <c r="D26" s="24">
+      <c r="D26" s="11">
         <v>1500</v>
       </c>
-      <c r="E26" s="24">
+      <c r="E26" s="11">
         <v>1700</v>
       </c>
     </row>
     <row r="27" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B27" s="33" t="s">
+      <c r="B27" s="20" t="s">
         <v>148</v>
       </c>
-      <c r="C27" s="48">
+      <c r="C27" s="35">
         <v>1.2</v>
       </c>
-      <c r="D27" s="48">
+      <c r="D27" s="35">
         <v>1.3</v>
       </c>
-      <c r="E27" s="48">
+      <c r="E27" s="35">
         <v>1.4</v>
       </c>
     </row>
     <row r="28" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B28" s="33" t="s">
+      <c r="B28" s="20" t="s">
         <v>149</v>
       </c>
-      <c r="C28" s="24">
+      <c r="C28" s="11">
         <v>-1500</v>
       </c>
-      <c r="D28" s="24">
+      <c r="D28" s="11">
         <v>-1500</v>
       </c>
-      <c r="E28" s="24">
+      <c r="E28" s="11">
         <v>-1500</v>
       </c>
     </row>
     <row r="29" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B29" s="3" t="s">
+      <c r="B29" s="58" t="s">
         <v>209</v>
       </c>
-      <c r="C29" s="3"/>
-      <c r="D29" s="3"/>
-      <c r="E29" s="3"/>
-      <c r="F29" s="3"/>
-      <c r="G29" s="3"/>
-      <c r="H29" s="3"/>
-      <c r="I29" s="3"/>
+      <c r="C29" s="58"/>
+      <c r="D29" s="58"/>
+      <c r="E29" s="58"/>
+      <c r="F29" s="58"/>
+      <c r="G29" s="58"/>
+      <c r="H29" s="58"/>
+      <c r="I29" s="58"/>
     </row>
     <row r="30" spans="2:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B30" s="20" t="s">
+      <c r="B30" s="7" t="s">
         <v>83</v>
       </c>
-      <c r="C30" s="35" t="s">
+      <c r="C30" s="22" t="s">
         <v>77</v>
       </c>
-      <c r="D30" s="35" t="s">
+      <c r="D30" s="22" t="s">
         <v>78</v>
       </c>
-      <c r="E30" s="35" t="s">
+      <c r="E30" s="22" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="31" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B31" s="29">
+      <c r="B31" s="16">
         <f>1919.9</f>
         <v>1919.9</v>
       </c>
-      <c r="C31" s="29">
+      <c r="C31" s="16">
         <f>C26*C27</f>
         <v>1620</v>
       </c>
-      <c r="D31" s="29">
+      <c r="D31" s="16">
         <f>D26*D27</f>
         <v>1950</v>
       </c>
-      <c r="E31" s="29">
+      <c r="E31" s="16">
         <f>E26*E27</f>
         <v>2380</v>
       </c>
     </row>
     <row r="32" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B32" s="37">
+      <c r="B32" s="24">
         <f>-1484.17</f>
         <v>-1484.17</v>
       </c>
-      <c r="C32" s="37">
+      <c r="C32" s="24">
         <f>C28</f>
         <v>-1500</v>
       </c>
-      <c r="D32" s="37">
+      <c r="D32" s="24">
         <f>D28</f>
         <v>-1500</v>
       </c>
-      <c r="E32" s="37">
+      <c r="E32" s="24">
         <f>E28</f>
         <v>-1500</v>
       </c>
     </row>
     <row r="33" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B33" s="38">
+      <c r="B33" s="25">
         <f>B31+B32</f>
         <v>435.73</v>
       </c>
-      <c r="C33" s="38">
+      <c r="C33" s="25">
         <f>C31+C32</f>
         <v>120</v>
       </c>
-      <c r="D33" s="38">
+      <c r="D33" s="25">
         <f>D31+D32</f>
         <v>450</v>
       </c>
-      <c r="E33" s="38">
+      <c r="E33" s="25">
         <f>E31+E32</f>
         <v>880</v>
       </c>
     </row>
     <row r="34" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B34" s="38">
+      <c r="B34" s="25">
         <f>3044.8</f>
         <v>3044.8</v>
       </c>
-      <c r="C34" s="38">
+      <c r="C34" s="25">
         <f>B34+C33</f>
         <v>3164.8</v>
       </c>
-      <c r="D34" s="38">
+      <c r="D34" s="25">
         <f>C34+D33</f>
         <v>3614.8</v>
       </c>
-      <c r="E34" s="38">
+      <c r="E34" s="25">
         <f>D34+E33</f>
         <v>4494.8</v>
       </c>
     </row>
     <row r="35" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B35" s="3" t="s">
+      <c r="B35" s="58" t="s">
         <v>150</v>
       </c>
-      <c r="C35" s="3"/>
-      <c r="D35" s="3"/>
-      <c r="E35" s="3"/>
-      <c r="F35" s="3"/>
-      <c r="G35" s="3"/>
-      <c r="H35" s="3"/>
-      <c r="I35" s="3"/>
+      <c r="C35" s="58"/>
+      <c r="D35" s="58"/>
+      <c r="E35" s="58"/>
+      <c r="F35" s="58"/>
+      <c r="G35" s="58"/>
+      <c r="H35" s="58"/>
+      <c r="I35" s="58"/>
     </row>
     <row r="36" spans="2:9" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B36" s="1" t="s">
+      <c r="B36" s="57" t="s">
         <v>151</v>
       </c>
-      <c r="C36" s="1"/>
-      <c r="D36" s="1"/>
-      <c r="E36" s="1"/>
-      <c r="F36" s="1"/>
-      <c r="G36" s="1"/>
-      <c r="H36" s="1"/>
-      <c r="I36" s="1"/>
+      <c r="C36" s="57"/>
+      <c r="D36" s="57"/>
+      <c r="E36" s="57"/>
+      <c r="F36" s="57"/>
+      <c r="G36" s="57"/>
+      <c r="H36" s="57"/>
+      <c r="I36" s="57"/>
     </row>
     <row r="37" spans="2:9" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B37" s="8" t="s">
+      <c r="B37" s="51" t="s">
         <v>152</v>
       </c>
-      <c r="C37" s="8"/>
-      <c r="D37" s="8"/>
-      <c r="E37" s="8"/>
-      <c r="F37" s="8"/>
-      <c r="G37" s="8"/>
-      <c r="H37" s="8"/>
-      <c r="I37" s="8"/>
+      <c r="C37" s="51"/>
+      <c r="D37" s="51"/>
+      <c r="E37" s="51"/>
+      <c r="F37" s="51"/>
+      <c r="G37" s="51"/>
+      <c r="H37" s="51"/>
+      <c r="I37" s="51"/>
     </row>
     <row r="38" spans="2:9" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B38" s="1" t="s">
+      <c r="B38" s="57" t="s">
         <v>153</v>
       </c>
-      <c r="C38" s="1"/>
-      <c r="D38" s="1"/>
-      <c r="E38" s="1"/>
-      <c r="F38" s="1"/>
-      <c r="G38" s="1"/>
-      <c r="H38" s="1"/>
-      <c r="I38" s="1"/>
+      <c r="C38" s="57"/>
+      <c r="D38" s="57"/>
+      <c r="E38" s="57"/>
+      <c r="F38" s="57"/>
+      <c r="G38" s="57"/>
+      <c r="H38" s="57"/>
+      <c r="I38" s="57"/>
     </row>
     <row r="39" spans="2:9" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B39" s="8" t="s">
+      <c r="B39" s="51" t="s">
         <v>154</v>
       </c>
-      <c r="C39" s="8"/>
-      <c r="D39" s="8"/>
-      <c r="E39" s="8"/>
-      <c r="F39" s="8"/>
-      <c r="G39" s="8"/>
-      <c r="H39" s="8"/>
-      <c r="I39" s="8"/>
+      <c r="C39" s="51"/>
+      <c r="D39" s="51"/>
+      <c r="E39" s="51"/>
+      <c r="F39" s="51"/>
+      <c r="G39" s="51"/>
+      <c r="H39" s="51"/>
+      <c r="I39" s="51"/>
     </row>
     <row r="40" spans="2:9" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B40" s="1" t="s">
+      <c r="B40" s="57" t="s">
         <v>155</v>
       </c>
-      <c r="C40" s="1"/>
-      <c r="D40" s="1"/>
-      <c r="E40" s="1"/>
-      <c r="F40" s="1"/>
-      <c r="G40" s="1"/>
-      <c r="H40" s="1"/>
-      <c r="I40" s="1"/>
+      <c r="C40" s="57"/>
+      <c r="D40" s="57"/>
+      <c r="E40" s="57"/>
+      <c r="F40" s="57"/>
+      <c r="G40" s="57"/>
+      <c r="H40" s="57"/>
+      <c r="I40" s="57"/>
     </row>
     <row r="42" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B42" s="5" t="s">
+      <c r="B42" s="50" t="s">
         <v>2</v>
       </c>
-      <c r="C42" s="5"/>
-      <c r="D42" s="5"/>
-      <c r="E42" s="5"/>
-      <c r="F42" s="5"/>
-      <c r="G42" s="5"/>
-      <c r="H42" s="5"/>
-      <c r="I42" s="5"/>
+      <c r="C42" s="50"/>
+      <c r="D42" s="50"/>
+      <c r="E42" s="50"/>
+      <c r="F42" s="50"/>
+      <c r="G42" s="50"/>
+      <c r="H42" s="50"/>
+      <c r="I42" s="50"/>
     </row>
   </sheetData>
   <mergeCells count="18">
+    <mergeCell ref="B1:I1"/>
+    <mergeCell ref="B3:F3"/>
+    <mergeCell ref="B11:I11"/>
+    <mergeCell ref="B18:F18"/>
+    <mergeCell ref="B19:F19"/>
+    <mergeCell ref="B20:F20"/>
+    <mergeCell ref="B21:F21"/>
+    <mergeCell ref="B22:F22"/>
+    <mergeCell ref="B23:F23"/>
+    <mergeCell ref="B24:I24"/>
     <mergeCell ref="B39:I39"/>
     <mergeCell ref="B40:I40"/>
     <mergeCell ref="B42:I42"/>
@@ -3989,16 +4027,6 @@
     <mergeCell ref="B36:I36"/>
     <mergeCell ref="B37:I37"/>
     <mergeCell ref="B38:I38"/>
-    <mergeCell ref="B20:F20"/>
-    <mergeCell ref="B21:F21"/>
-    <mergeCell ref="B22:F22"/>
-    <mergeCell ref="B23:F23"/>
-    <mergeCell ref="B24:I24"/>
-    <mergeCell ref="B1:I1"/>
-    <mergeCell ref="B3:F3"/>
-    <mergeCell ref="B11:I11"/>
-    <mergeCell ref="B18:F18"/>
-    <mergeCell ref="B19:F19"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -4010,477 +4038,477 @@
   <dimension ref="A1:F39"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="68.85546875" style="14" bestFit="1" customWidth="1"/>
-    <col min="2" max="5" width="14" style="14" customWidth="1"/>
-    <col min="6" max="6" width="4" style="14" customWidth="1"/>
+    <col min="1" max="1" width="68.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="5" width="14" style="1" customWidth="1"/>
+    <col min="6" max="6" width="4" style="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="4" t="s">
+      <c r="A1" s="63" t="s">
         <v>207</v>
       </c>
-      <c r="B1" s="4"/>
-      <c r="C1" s="4"/>
-      <c r="D1" s="4"/>
-      <c r="E1" s="4"/>
+      <c r="B1" s="63"/>
+      <c r="C1" s="63"/>
+      <c r="D1" s="63"/>
+      <c r="E1" s="63"/>
     </row>
     <row r="2" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="61" t="s">
+      <c r="A2" s="66" t="s">
         <v>204</v>
       </c>
-      <c r="B2" s="61"/>
-      <c r="C2" s="61"/>
-      <c r="D2" s="61"/>
-      <c r="E2" s="61"/>
+      <c r="B2" s="66"/>
+      <c r="C2" s="66"/>
+      <c r="D2" s="66"/>
+      <c r="E2" s="66"/>
     </row>
     <row r="4" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="20" t="s">
+      <c r="A4" s="7" t="s">
         <v>156</v>
       </c>
-      <c r="B4" s="21" t="s">
+      <c r="B4" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="C4" s="21" t="s">
+      <c r="C4" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="D4" s="21" t="s">
+      <c r="D4" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="E4" s="21" t="s">
+      <c r="E4" s="8" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="49" t="s">
+      <c r="A5" s="36" t="s">
         <v>157</v>
       </c>
-      <c r="B5" s="50"/>
-      <c r="C5" s="50"/>
-      <c r="D5" s="50"/>
-      <c r="E5" s="50"/>
+      <c r="B5" s="37"/>
+      <c r="C5" s="37"/>
+      <c r="D5" s="37"/>
+      <c r="E5" s="37"/>
     </row>
     <row r="6" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="25" t="s">
+      <c r="A6" s="12" t="s">
         <v>32</v>
       </c>
-      <c r="B6" s="26">
+      <c r="B6" s="13">
         <v>19381.71</v>
       </c>
-      <c r="C6" s="26">
+      <c r="C6" s="13">
         <v>20281.57</v>
       </c>
-      <c r="D6" s="26">
+      <c r="D6" s="13">
         <v>21732.58</v>
       </c>
-      <c r="E6" s="26">
+      <c r="E6" s="13">
         <v>19869.349999999999</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="17" t="s">
+      <c r="A7" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="B7" s="22">
+      <c r="B7" s="9">
         <v>809.26</v>
       </c>
-      <c r="C7" s="22">
+      <c r="C7" s="9">
         <v>1003.94</v>
       </c>
-      <c r="D7" s="22">
+      <c r="D7" s="9">
         <v>1182.55</v>
       </c>
-      <c r="E7" s="22">
+      <c r="E7" s="9">
         <v>1018.89</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="23" t="s">
+      <c r="A8" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="B8" s="24">
+      <c r="B8" s="11">
         <v>20190.97</v>
       </c>
-      <c r="C8" s="24">
+      <c r="C8" s="11">
         <v>21285.51</v>
       </c>
-      <c r="D8" s="24">
+      <c r="D8" s="11">
         <v>22915.13</v>
       </c>
-      <c r="E8" s="24">
+      <c r="E8" s="11">
         <v>20888.240000000002</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="49" t="s">
+      <c r="A10" s="36" t="s">
         <v>35</v>
       </c>
-      <c r="B10" s="50"/>
-      <c r="C10" s="50"/>
-      <c r="D10" s="50"/>
-      <c r="E10" s="50"/>
+      <c r="B10" s="37"/>
+      <c r="C10" s="37"/>
+      <c r="D10" s="37"/>
+      <c r="E10" s="37"/>
     </row>
     <row r="11" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="17" t="s">
+      <c r="A11" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="B11" s="22">
+      <c r="B11" s="9">
         <v>17905.57</v>
       </c>
-      <c r="C11" s="22">
+      <c r="C11" s="9">
         <v>18727.599999999999</v>
       </c>
-      <c r="D11" s="22">
+      <c r="D11" s="9">
         <v>20041.240000000002</v>
       </c>
-      <c r="E11" s="22">
+      <c r="E11" s="9">
         <v>18385.2</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="25" t="s">
+      <c r="A12" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="B12" s="26">
+      <c r="B12" s="13">
         <v>203.05</v>
       </c>
-      <c r="C12" s="26">
+      <c r="C12" s="13">
         <v>187.16</v>
       </c>
-      <c r="D12" s="26">
+      <c r="D12" s="13">
         <v>184.18</v>
       </c>
-      <c r="E12" s="26">
+      <c r="E12" s="13">
         <v>182.98</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="17" t="s">
+      <c r="A13" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="B13" s="22">
+      <c r="B13" s="9">
         <v>563.71</v>
       </c>
-      <c r="C13" s="22">
+      <c r="C13" s="9">
         <v>581.37</v>
       </c>
-      <c r="D13" s="22">
+      <c r="D13" s="9">
         <v>568.49</v>
       </c>
-      <c r="E13" s="22">
+      <c r="E13" s="9">
         <v>539.51</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="25" t="s">
+      <c r="A14" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="B14" s="26">
+      <c r="B14" s="13">
         <v>20.9</v>
       </c>
-      <c r="C14" s="26">
+      <c r="C14" s="13">
         <v>22.27</v>
       </c>
-      <c r="D14" s="26">
+      <c r="D14" s="13">
         <v>20.82</v>
       </c>
-      <c r="E14" s="26">
+      <c r="E14" s="13">
         <v>30.6</v>
       </c>
     </row>
     <row r="15" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="17" t="s">
+      <c r="A15" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="B15" s="22">
+      <c r="B15" s="9">
         <v>91.5</v>
       </c>
-      <c r="C15" s="22">
+      <c r="C15" s="9">
         <v>122.73</v>
       </c>
-      <c r="D15" s="22">
+      <c r="D15" s="9">
         <v>161</v>
       </c>
-      <c r="E15" s="22">
+      <c r="E15" s="9">
         <v>199.78</v>
       </c>
     </row>
     <row r="16" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="23" t="s">
+      <c r="A16" s="10" t="s">
         <v>41</v>
       </c>
-      <c r="B16" s="24">
+      <c r="B16" s="11">
         <v>18784.73</v>
       </c>
-      <c r="C16" s="24">
+      <c r="C16" s="11">
         <v>19641.13</v>
       </c>
-      <c r="D16" s="24">
+      <c r="D16" s="11">
         <v>20975.73</v>
       </c>
-      <c r="E16" s="24">
+      <c r="E16" s="11">
         <v>19338.07</v>
       </c>
     </row>
     <row r="18" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="49" t="s">
+      <c r="A18" s="36" t="s">
         <v>42</v>
       </c>
-      <c r="B18" s="50"/>
-      <c r="C18" s="50"/>
-      <c r="D18" s="50"/>
-      <c r="E18" s="50"/>
+      <c r="B18" s="37"/>
+      <c r="C18" s="37"/>
+      <c r="D18" s="37"/>
+      <c r="E18" s="37"/>
     </row>
     <row r="19" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="17" t="s">
+      <c r="A19" s="4" t="s">
         <v>158</v>
       </c>
-      <c r="B19" s="22">
+      <c r="B19" s="9">
         <v>1406.24</v>
       </c>
-      <c r="C19" s="22">
+      <c r="C19" s="9">
         <v>1644.38</v>
       </c>
-      <c r="D19" s="22">
+      <c r="D19" s="9">
         <v>1939.4</v>
       </c>
-      <c r="E19" s="22">
+      <c r="E19" s="9">
         <v>1550.17</v>
       </c>
     </row>
     <row r="20" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="23" t="s">
+      <c r="A20" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="B20" s="24">
+      <c r="B20" s="11">
         <v>318.89</v>
       </c>
-      <c r="C20" s="24">
+      <c r="C20" s="11">
         <v>376.42</v>
       </c>
-      <c r="D20" s="24">
+      <c r="D20" s="11">
         <v>476.45</v>
       </c>
-      <c r="E20" s="24">
+      <c r="E20" s="11">
         <v>361.55</v>
       </c>
     </row>
     <row r="21" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="27" t="s">
+      <c r="A21" s="14" t="s">
         <v>45</v>
       </c>
-      <c r="B21" s="28">
+      <c r="B21" s="15">
         <v>1087.3499999999999</v>
       </c>
-      <c r="C21" s="28">
+      <c r="C21" s="15">
         <v>1267.97</v>
       </c>
-      <c r="D21" s="28">
+      <c r="D21" s="15">
         <v>1462.95</v>
       </c>
-      <c r="E21" s="28">
+      <c r="E21" s="15">
         <v>1188.6199999999999</v>
       </c>
     </row>
     <row r="23" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="49" t="s">
+      <c r="A23" s="36" t="s">
         <v>159</v>
       </c>
-      <c r="B23" s="50"/>
-      <c r="C23" s="50"/>
-      <c r="D23" s="50"/>
-      <c r="E23" s="50"/>
+      <c r="B23" s="37"/>
+      <c r="C23" s="37"/>
+      <c r="D23" s="37"/>
+      <c r="E23" s="37"/>
     </row>
     <row r="24" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="23" t="s">
+      <c r="A24" s="10" t="s">
         <v>160</v>
       </c>
-      <c r="B24" s="24">
+      <c r="B24" s="11">
         <v>19379.09</v>
       </c>
-      <c r="C24" s="24">
+      <c r="C24" s="11">
         <v>17581.45</v>
       </c>
-      <c r="D24" s="24">
+      <c r="D24" s="11">
         <v>18733.53</v>
       </c>
-      <c r="E24" s="24">
+      <c r="E24" s="11">
         <v>19484.52</v>
       </c>
     </row>
     <row r="25" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="23" t="s">
+      <c r="A25" s="10" t="s">
         <v>100</v>
       </c>
-      <c r="B25" s="24">
+      <c r="B25" s="11">
         <v>5631.44</v>
       </c>
-      <c r="C25" s="24">
+      <c r="C25" s="11">
         <v>6479.15</v>
       </c>
-      <c r="D25" s="24">
+      <c r="D25" s="11">
         <v>7867.28</v>
       </c>
-      <c r="E25" s="24">
+      <c r="E25" s="11">
         <v>8623.7199999999993</v>
       </c>
     </row>
     <row r="26" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="25" t="s">
+      <c r="A26" s="12" t="s">
         <v>99</v>
       </c>
-      <c r="B26" s="26">
+      <c r="B26" s="13">
         <v>938.17</v>
       </c>
-      <c r="C26" s="26">
+      <c r="C26" s="13">
         <v>969.3</v>
       </c>
-      <c r="D26" s="26">
+      <c r="D26" s="13">
         <v>1106.48</v>
       </c>
-      <c r="E26" s="26">
+      <c r="E26" s="13">
         <v>1489.51</v>
       </c>
     </row>
     <row r="27" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="17" t="s">
+      <c r="A27" s="4" t="s">
         <v>98</v>
       </c>
-      <c r="B27" s="22">
+      <c r="B27" s="9">
         <v>4569.93</v>
       </c>
-      <c r="C27" s="22">
+      <c r="C27" s="9">
         <v>807.53</v>
       </c>
-      <c r="D27" s="22">
+      <c r="D27" s="9">
         <v>1027.49</v>
       </c>
-      <c r="E27" s="22">
+      <c r="E27" s="9">
         <v>3044.8</v>
       </c>
     </row>
     <row r="28" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="25" t="s">
+      <c r="A28" s="12" t="s">
         <v>101</v>
       </c>
-      <c r="B28" s="26">
+      <c r="B28" s="13">
         <v>6315.42</v>
       </c>
-      <c r="C28" s="26">
+      <c r="C28" s="13">
         <v>6030.58</v>
       </c>
-      <c r="D28" s="26">
+      <c r="D28" s="13">
         <v>5515.77</v>
       </c>
-      <c r="E28" s="26">
+      <c r="E28" s="13">
         <v>4889.51</v>
       </c>
     </row>
     <row r="29" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="17" t="s">
+      <c r="A29" s="4" t="s">
         <v>102</v>
       </c>
-      <c r="B29" s="22">
+      <c r="B29" s="9">
         <v>230.5</v>
       </c>
-      <c r="C29" s="22">
+      <c r="C29" s="9">
         <v>626.29</v>
       </c>
-      <c r="D29" s="22">
+      <c r="D29" s="9">
         <v>252.4</v>
       </c>
-      <c r="E29" s="22">
+      <c r="E29" s="9">
         <v>344.87</v>
       </c>
     </row>
     <row r="31" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="49" t="s">
+      <c r="A31" s="36" t="s">
         <v>161</v>
       </c>
-      <c r="B31" s="50"/>
-      <c r="C31" s="50"/>
-      <c r="D31" s="50"/>
-      <c r="E31" s="50"/>
+      <c r="B31" s="37"/>
+      <c r="C31" s="37"/>
+      <c r="D31" s="37"/>
+      <c r="E31" s="37"/>
     </row>
     <row r="32" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="25" t="s">
+      <c r="A32" s="12" t="s">
         <v>133</v>
       </c>
-      <c r="B32" s="26">
+      <c r="B32" s="13">
         <v>4806.17</v>
       </c>
-      <c r="C32" s="26">
+      <c r="C32" s="13">
         <v>-4080.06</v>
       </c>
-      <c r="D32" s="26">
+      <c r="D32" s="13">
         <v>2939.27</v>
       </c>
-      <c r="E32" s="26">
+      <c r="E32" s="13">
         <v>1919.9</v>
       </c>
     </row>
     <row r="33" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="17" t="s">
+      <c r="A33" s="4" t="s">
         <v>134</v>
       </c>
-      <c r="B33" s="22">
+      <c r="B33" s="9">
         <v>-1462.83</v>
       </c>
-      <c r="C33" s="22">
+      <c r="C33" s="9">
         <v>1353.66</v>
       </c>
-      <c r="D33" s="22">
+      <c r="D33" s="9">
         <v>-1431.35</v>
       </c>
-      <c r="E33" s="22">
+      <c r="E33" s="9">
         <v>1581.62</v>
       </c>
     </row>
     <row r="34" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="25" t="s">
+      <c r="A34" s="12" t="s">
         <v>135</v>
       </c>
-      <c r="B34" s="26">
+      <c r="B34" s="13">
         <v>-189.36</v>
       </c>
-      <c r="C34" s="26">
+      <c r="C34" s="13">
         <v>-1036.01</v>
       </c>
-      <c r="D34" s="26">
+      <c r="D34" s="13">
         <v>-1286.56</v>
       </c>
-      <c r="E34" s="26">
+      <c r="E34" s="13">
         <v>-1484.17</v>
       </c>
     </row>
     <row r="35" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="17" t="s">
+      <c r="A35" s="4" t="s">
         <v>137</v>
       </c>
-      <c r="B35" s="22">
+      <c r="B35" s="9">
         <v>4569.93</v>
       </c>
-      <c r="C35" s="22">
+      <c r="C35" s="9">
         <v>807.53</v>
       </c>
-      <c r="D35" s="22">
+      <c r="D35" s="9">
         <v>1027.49</v>
       </c>
-      <c r="E35" s="22">
+      <c r="E35" s="9">
         <v>3044.8</v>
       </c>
     </row>
     <row r="37" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="51" t="s">
+      <c r="A37" s="38" t="s">
         <v>162</v>
       </c>
     </row>
     <row r="39" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B39" s="5" t="s">
+      <c r="B39" s="50" t="s">
         <v>2</v>
       </c>
-      <c r="C39" s="5"/>
-      <c r="D39" s="5"/>
-      <c r="E39" s="5"/>
+      <c r="C39" s="50"/>
+      <c r="D39" s="50"/>
+      <c r="E39" s="50"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -4498,198 +4526,198 @@
   <dimension ref="A1:C46"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="2" style="14" customWidth="1"/>
-    <col min="2" max="2" width="141.28515625" style="14" customWidth="1"/>
-    <col min="3" max="3" width="2" style="14" customWidth="1"/>
+    <col min="1" max="1" width="2" style="1" customWidth="1"/>
+    <col min="2" max="2" width="141.28515625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="2" style="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:2" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B1" s="52" t="s">
+      <c r="B1" s="39" t="s">
         <v>205</v>
       </c>
     </row>
     <row r="2" spans="2:2" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="53" t="s">
+      <c r="B2" s="40" t="s">
         <v>163</v>
       </c>
     </row>
     <row r="4" spans="2:2" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B4" s="54" t="s">
+      <c r="B4" s="41" t="s">
         <v>164</v>
       </c>
     </row>
     <row r="5" spans="2:2" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="55" t="s">
+      <c r="B5" s="42" t="s">
         <v>165</v>
       </c>
     </row>
     <row r="6" spans="2:2" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="56" t="s">
+      <c r="B6" s="43" t="s">
         <v>166</v>
       </c>
     </row>
     <row r="7" spans="2:2" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B7" s="55" t="s">
+      <c r="B7" s="42" t="s">
         <v>167</v>
       </c>
     </row>
     <row r="8" spans="2:2" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B8" s="56" t="s">
+      <c r="B8" s="43" t="s">
         <v>168</v>
       </c>
     </row>
     <row r="10" spans="2:2" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B10" s="54" t="s">
+      <c r="B10" s="41" t="s">
         <v>169</v>
       </c>
     </row>
     <row r="11" spans="2:2" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B11" s="55" t="s">
+      <c r="B11" s="42" t="s">
         <v>170</v>
       </c>
     </row>
     <row r="12" spans="2:2" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B12" s="56" t="s">
+      <c r="B12" s="43" t="s">
         <v>171</v>
       </c>
     </row>
     <row r="13" spans="2:2" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B13" s="55" t="s">
+      <c r="B13" s="42" t="s">
         <v>172</v>
       </c>
     </row>
     <row r="14" spans="2:2" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B14" s="56" t="s">
+      <c r="B14" s="43" t="s">
         <v>173</v>
       </c>
     </row>
     <row r="16" spans="2:2" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B16" s="54" t="s">
+      <c r="B16" s="41" t="s">
         <v>174</v>
       </c>
     </row>
     <row r="17" spans="2:2" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B17" s="55" t="s">
+      <c r="B17" s="42" t="s">
         <v>175</v>
       </c>
     </row>
     <row r="18" spans="2:2" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B18" s="56" t="s">
+      <c r="B18" s="43" t="s">
         <v>176</v>
       </c>
     </row>
     <row r="19" spans="2:2" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B19" s="55" t="s">
+      <c r="B19" s="42" t="s">
         <v>177</v>
       </c>
     </row>
     <row r="20" spans="2:2" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B20" s="56" t="s">
+      <c r="B20" s="43" t="s">
         <v>178</v>
       </c>
     </row>
     <row r="22" spans="2:2" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B22" s="54" t="s">
+      <c r="B22" s="41" t="s">
         <v>179</v>
       </c>
     </row>
     <row r="23" spans="2:2" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B23" s="55" t="s">
+      <c r="B23" s="42" t="s">
         <v>180</v>
       </c>
     </row>
     <row r="24" spans="2:2" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B24" s="56" t="s">
+      <c r="B24" s="43" t="s">
         <v>181</v>
       </c>
     </row>
     <row r="25" spans="2:2" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B25" s="55" t="s">
+      <c r="B25" s="42" t="s">
         <v>182</v>
       </c>
     </row>
     <row r="27" spans="2:2" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B27" s="54" t="s">
+      <c r="B27" s="41" t="s">
         <v>183</v>
       </c>
     </row>
     <row r="28" spans="2:2" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B28" s="56" t="s">
+      <c r="B28" s="43" t="s">
         <v>184</v>
       </c>
     </row>
     <row r="29" spans="2:2" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B29" s="55" t="s">
+      <c r="B29" s="42" t="s">
         <v>185</v>
       </c>
     </row>
     <row r="30" spans="2:2" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B30" s="56" t="s">
+      <c r="B30" s="43" t="s">
         <v>186</v>
       </c>
     </row>
     <row r="31" spans="2:2" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B31" s="55" t="s">
+      <c r="B31" s="42" t="s">
         <v>187</v>
       </c>
     </row>
     <row r="33" spans="2:2" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B33" s="54" t="s">
+      <c r="B33" s="41" t="s">
         <v>188</v>
       </c>
     </row>
     <row r="34" spans="2:2" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B34" s="56" t="s">
+      <c r="B34" s="43" t="s">
         <v>189</v>
       </c>
     </row>
     <row r="35" spans="2:2" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B35" s="55" t="s">
+      <c r="B35" s="42" t="s">
         <v>190</v>
       </c>
     </row>
     <row r="36" spans="2:2" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B36" s="56" t="s">
+      <c r="B36" s="43" t="s">
         <v>191</v>
       </c>
     </row>
     <row r="37" spans="2:2" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B37" s="55" t="s">
+      <c r="B37" s="42" t="s">
         <v>192</v>
       </c>
     </row>
     <row r="39" spans="2:2" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B39" s="57" t="s">
+      <c r="B39" s="44" t="s">
         <v>206</v>
       </c>
     </row>
     <row r="40" spans="2:2" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B40" s="58" t="s">
+      <c r="B40" s="45" t="s">
         <v>193</v>
       </c>
     </row>
     <row r="41" spans="2:2" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B41" s="59" t="s">
+      <c r="B41" s="46" t="s">
         <v>194</v>
       </c>
     </row>
     <row r="42" spans="2:2" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B42" s="58" t="s">
+      <c r="B42" s="45" t="s">
         <v>195</v>
       </c>
     </row>
     <row r="43" spans="2:2" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B43" s="59" t="s">
+      <c r="B43" s="46" t="s">
         <v>196</v>
       </c>
     </row>
     <row r="44" spans="2:2" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B44" s="58" t="s">
+      <c r="B44" s="45" t="s">
         <v>197</v>
       </c>
     </row>
     <row r="46" spans="2:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B46" s="60" t="s">
+      <c r="B46" s="47" t="s">
         <v>2</v>
       </c>
     </row>

--- a/myprojects/RVNL/RVNL_Business_Performance.xlsx
+++ b/myprojects/RVNL/RVNL_Business_Performance.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="450" windowWidth="28800" windowHeight="13860" tabRatio="500" activeTab="2"/>
+    <workbookView xWindow="0" yWindow="900" windowWidth="28800" windowHeight="13860" tabRatio="500" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="HOME" sheetId="1" r:id="rId1"/>
@@ -319,9 +319,6 @@
     <t>International projects in Mauritius, Nepal, and Sri Lanka carry better margins. Scaling this segment will improve overall profitability.</t>
   </si>
   <si>
-    <t>A.  BALANCE SHEET KEY ITEMS  (Rs. in Crore)  |  Blue numbers are from Annual Reports</t>
-  </si>
-  <si>
     <t>TOTAL ASSETS</t>
   </si>
   <si>
@@ -662,6 +659,9 @@
   </si>
   <si>
     <t xml:space="preserve">B.  PROFIT VS CASH CHECK </t>
+  </si>
+  <si>
+    <t xml:space="preserve">A.  BALANCE SHEET KEY ITEMS  (Rs. in Crore) </t>
   </si>
 </sst>
 </file>
@@ -1104,9 +1104,21 @@
     <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -1119,41 +1131,29 @@
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="10" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="10" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="10" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="10" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="10" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="10" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -1436,81 +1436,81 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:4" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B1" s="53" t="s">
+      <c r="B1" s="48" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="53"/>
-      <c r="D1" s="53"/>
+      <c r="C1" s="48"/>
+      <c r="D1" s="48"/>
     </row>
     <row r="2" spans="2:4" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="54" t="s">
+      <c r="B2" s="49" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="54"/>
-      <c r="D2" s="54"/>
+      <c r="C2" s="49"/>
+      <c r="D2" s="49"/>
     </row>
     <row r="3" spans="2:4" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="55" t="s">
+      <c r="B3" s="50" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="55"/>
-      <c r="D3" s="55"/>
+      <c r="C3" s="50"/>
+      <c r="D3" s="50"/>
     </row>
     <row r="5" spans="2:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="48" t="s">
+      <c r="B5" s="51" t="s">
         <v>3</v>
       </c>
-      <c r="C5" s="48"/>
-      <c r="D5" s="48"/>
+      <c r="C5" s="51"/>
+      <c r="D5" s="51"/>
     </row>
     <row r="6" spans="2:4" ht="54.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="56" t="s">
+      <c r="B6" s="52" t="s">
         <v>4</v>
       </c>
-      <c r="C6" s="56"/>
-      <c r="D6" s="56"/>
+      <c r="C6" s="52"/>
+      <c r="D6" s="52"/>
     </row>
     <row r="8" spans="2:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B8" s="48" t="s">
+      <c r="B8" s="51" t="s">
         <v>5</v>
       </c>
-      <c r="C8" s="48"/>
-      <c r="D8" s="48"/>
+      <c r="C8" s="51"/>
+      <c r="D8" s="51"/>
     </row>
     <row r="9" spans="2:4" ht="48" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B9" s="51" t="s">
+      <c r="B9" s="55" t="s">
         <v>6</v>
       </c>
-      <c r="C9" s="51"/>
-      <c r="D9" s="51"/>
+      <c r="C9" s="55"/>
+      <c r="D9" s="55"/>
     </row>
     <row r="10" spans="2:4" ht="48" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B10" s="52" t="s">
+      <c r="B10" s="56" t="s">
         <v>7</v>
       </c>
-      <c r="C10" s="52"/>
-      <c r="D10" s="52"/>
+      <c r="C10" s="56"/>
+      <c r="D10" s="56"/>
     </row>
     <row r="11" spans="2:4" ht="48" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B11" s="51" t="s">
+      <c r="B11" s="55" t="s">
         <v>8</v>
       </c>
-      <c r="C11" s="51"/>
-      <c r="D11" s="51"/>
+      <c r="C11" s="55"/>
+      <c r="D11" s="55"/>
     </row>
     <row r="12" spans="2:4" ht="48" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B12" s="52" t="s">
+      <c r="B12" s="56" t="s">
         <v>9</v>
       </c>
-      <c r="C12" s="52"/>
-      <c r="D12" s="52"/>
+      <c r="C12" s="56"/>
+      <c r="D12" s="56"/>
     </row>
     <row r="13" spans="2:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B13" s="48" t="s">
+      <c r="B13" s="51" t="s">
         <v>10</v>
       </c>
-      <c r="C13" s="48"/>
-      <c r="D13" s="48"/>
+      <c r="C13" s="51"/>
+      <c r="D13" s="51"/>
     </row>
     <row r="14" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B14" s="2" t="s">
@@ -1569,26 +1569,21 @@
       </c>
     </row>
     <row r="21" spans="2:4" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B21" s="49" t="s">
+      <c r="B21" s="53" t="s">
         <v>25</v>
       </c>
-      <c r="C21" s="49"/>
-      <c r="D21" s="49"/>
+      <c r="C21" s="53"/>
+      <c r="D21" s="53"/>
     </row>
     <row r="23" spans="2:4" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B23" s="50" t="s">
+      <c r="B23" s="54" t="s">
         <v>2</v>
       </c>
-      <c r="C23" s="50"/>
-      <c r="D23" s="50"/>
+      <c r="C23" s="54"/>
+      <c r="D23" s="54"/>
     </row>
   </sheetData>
   <mergeCells count="13">
-    <mergeCell ref="B1:D1"/>
-    <mergeCell ref="B2:D2"/>
-    <mergeCell ref="B3:D3"/>
-    <mergeCell ref="B5:D5"/>
-    <mergeCell ref="B6:D6"/>
     <mergeCell ref="B13:D13"/>
     <mergeCell ref="B21:D21"/>
     <mergeCell ref="B23:D23"/>
@@ -1597,6 +1592,11 @@
     <mergeCell ref="B10:D10"/>
     <mergeCell ref="B11:D11"/>
     <mergeCell ref="B12:D12"/>
+    <mergeCell ref="B1:D1"/>
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="B3:D3"/>
+    <mergeCell ref="B5:D5"/>
+    <mergeCell ref="B6:D6"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -1616,16 +1616,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B1" s="63" t="s">
-        <v>198</v>
-      </c>
-      <c r="C1" s="63"/>
-      <c r="D1" s="63"/>
-      <c r="E1" s="63"/>
-      <c r="F1" s="63"/>
-      <c r="G1" s="63"/>
-      <c r="H1" s="63"/>
-      <c r="I1" s="63"/>
+      <c r="B1" s="57" t="s">
+        <v>197</v>
+      </c>
+      <c r="C1" s="57"/>
+      <c r="D1" s="57"/>
+      <c r="E1" s="57"/>
+      <c r="F1" s="57"/>
+      <c r="G1" s="57"/>
+      <c r="H1" s="57"/>
+      <c r="I1" s="57"/>
     </row>
     <row r="3" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B3" s="58" t="s">
@@ -1709,13 +1709,13 @@
       </c>
     </row>
     <row r="8" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B8" s="64" t="s">
+      <c r="B8" s="59" t="s">
         <v>35</v>
       </c>
-      <c r="C8" s="64"/>
-      <c r="D8" s="64"/>
-      <c r="E8" s="64"/>
-      <c r="F8" s="64"/>
+      <c r="C8" s="59"/>
+      <c r="D8" s="59"/>
+      <c r="E8" s="59"/>
+      <c r="F8" s="59"/>
     </row>
     <row r="9" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B9" s="4" t="s">
@@ -1824,13 +1824,13 @@
       </c>
     </row>
     <row r="15" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B15" s="64" t="s">
+      <c r="B15" s="59" t="s">
         <v>42</v>
       </c>
-      <c r="C15" s="64"/>
-      <c r="D15" s="64"/>
-      <c r="E15" s="64"/>
-      <c r="F15" s="64"/>
+      <c r="C15" s="59"/>
+      <c r="D15" s="59"/>
+      <c r="E15" s="59"/>
+      <c r="F15" s="59"/>
     </row>
     <row r="16" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B16" s="14" t="s">
@@ -1987,49 +1987,49 @@
     </row>
     <row r="26" spans="2:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="27" spans="2:9" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B27" s="59" t="s">
+      <c r="B27" s="60" t="s">
         <v>52</v>
       </c>
-      <c r="C27" s="60"/>
-      <c r="D27" s="60"/>
-      <c r="E27" s="60"/>
-      <c r="F27" s="61"/>
+      <c r="C27" s="61"/>
+      <c r="D27" s="61"/>
+      <c r="E27" s="61"/>
+      <c r="F27" s="62"/>
     </row>
     <row r="28" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B28" s="62" t="s">
+      <c r="B28" s="63" t="s">
         <v>53</v>
       </c>
-      <c r="C28" s="62"/>
-      <c r="D28" s="62"/>
-      <c r="E28" s="62"/>
-      <c r="F28" s="62"/>
+      <c r="C28" s="63"/>
+      <c r="D28" s="63"/>
+      <c r="E28" s="63"/>
+      <c r="F28" s="63"/>
     </row>
     <row r="29" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B29" s="51" t="s">
+      <c r="B29" s="55" t="s">
         <v>54</v>
       </c>
-      <c r="C29" s="51"/>
-      <c r="D29" s="51"/>
-      <c r="E29" s="51"/>
-      <c r="F29" s="51"/>
+      <c r="C29" s="55"/>
+      <c r="D29" s="55"/>
+      <c r="E29" s="55"/>
+      <c r="F29" s="55"/>
     </row>
     <row r="30" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B30" s="52" t="s">
+      <c r="B30" s="56" t="s">
         <v>55</v>
       </c>
-      <c r="C30" s="52"/>
-      <c r="D30" s="52"/>
-      <c r="E30" s="52"/>
-      <c r="F30" s="52"/>
+      <c r="C30" s="56"/>
+      <c r="D30" s="56"/>
+      <c r="E30" s="56"/>
+      <c r="F30" s="56"/>
     </row>
     <row r="31" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B31" s="51" t="s">
+      <c r="B31" s="55" t="s">
         <v>56</v>
       </c>
-      <c r="C31" s="51"/>
-      <c r="D31" s="51"/>
-      <c r="E31" s="51"/>
-      <c r="F31" s="51"/>
+      <c r="C31" s="55"/>
+      <c r="D31" s="55"/>
+      <c r="E31" s="55"/>
+      <c r="F31" s="55"/>
     </row>
     <row r="32" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B32" s="58" t="s">
@@ -2100,7 +2100,7 @@
         <v>0.16934520423256585</v>
       </c>
       <c r="D36" s="17">
-        <f t="shared" ref="D36:E36" si="5">(E16-D16)/D16</f>
+        <f t="shared" ref="D36" si="5">(E16-D16)/D16</f>
         <v>0.17941108502900582</v>
       </c>
       <c r="E36" s="17">
@@ -2161,49 +2161,49 @@
     </row>
     <row r="40" spans="2:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="41" spans="2:9" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B41" s="59" t="s">
+      <c r="B41" s="60" t="s">
         <v>64</v>
       </c>
-      <c r="C41" s="60"/>
-      <c r="D41" s="60"/>
-      <c r="E41" s="60"/>
-      <c r="F41" s="61"/>
+      <c r="C41" s="61"/>
+      <c r="D41" s="61"/>
+      <c r="E41" s="61"/>
+      <c r="F41" s="62"/>
     </row>
     <row r="42" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B42" s="62" t="s">
+      <c r="B42" s="63" t="s">
         <v>65</v>
       </c>
-      <c r="C42" s="62"/>
-      <c r="D42" s="62"/>
-      <c r="E42" s="62"/>
-      <c r="F42" s="62"/>
+      <c r="C42" s="63"/>
+      <c r="D42" s="63"/>
+      <c r="E42" s="63"/>
+      <c r="F42" s="63"/>
     </row>
     <row r="43" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B43" s="51" t="s">
+      <c r="B43" s="55" t="s">
         <v>66</v>
       </c>
-      <c r="C43" s="51"/>
-      <c r="D43" s="51"/>
-      <c r="E43" s="51"/>
-      <c r="F43" s="51"/>
+      <c r="C43" s="55"/>
+      <c r="D43" s="55"/>
+      <c r="E43" s="55"/>
+      <c r="F43" s="55"/>
     </row>
     <row r="44" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B44" s="52" t="s">
+      <c r="B44" s="56" t="s">
         <v>67</v>
       </c>
-      <c r="C44" s="52"/>
-      <c r="D44" s="52"/>
-      <c r="E44" s="52"/>
-      <c r="F44" s="52"/>
+      <c r="C44" s="56"/>
+      <c r="D44" s="56"/>
+      <c r="E44" s="56"/>
+      <c r="F44" s="56"/>
     </row>
     <row r="45" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B45" s="51" t="s">
+      <c r="B45" s="55" t="s">
         <v>68</v>
       </c>
-      <c r="C45" s="51"/>
-      <c r="D45" s="51"/>
-      <c r="E45" s="51"/>
-      <c r="F45" s="51"/>
+      <c r="C45" s="55"/>
+      <c r="D45" s="55"/>
+      <c r="E45" s="55"/>
+      <c r="F45" s="55"/>
     </row>
     <row r="46" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B46" s="58" t="s">
@@ -2362,53 +2362,53 @@
     </row>
     <row r="54" spans="2:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="55" spans="2:9" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B55" s="59" t="s">
+      <c r="B55" s="60" t="s">
         <v>71</v>
       </c>
-      <c r="C55" s="60"/>
-      <c r="D55" s="60"/>
-      <c r="E55" s="60"/>
-      <c r="F55" s="61"/>
+      <c r="C55" s="61"/>
+      <c r="D55" s="61"/>
+      <c r="E55" s="61"/>
+      <c r="F55" s="62"/>
     </row>
     <row r="56" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B56" s="62" t="s">
+      <c r="B56" s="63" t="s">
         <v>72</v>
       </c>
-      <c r="C56" s="62"/>
-      <c r="D56" s="62"/>
-      <c r="E56" s="62"/>
-      <c r="F56" s="62"/>
+      <c r="C56" s="63"/>
+      <c r="D56" s="63"/>
+      <c r="E56" s="63"/>
+      <c r="F56" s="63"/>
     </row>
     <row r="57" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B57" s="51" t="s">
+      <c r="B57" s="55" t="s">
         <v>73</v>
       </c>
-      <c r="C57" s="51"/>
-      <c r="D57" s="51"/>
-      <c r="E57" s="51"/>
-      <c r="F57" s="51"/>
+      <c r="C57" s="55"/>
+      <c r="D57" s="55"/>
+      <c r="E57" s="55"/>
+      <c r="F57" s="55"/>
     </row>
     <row r="58" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B58" s="52" t="s">
+      <c r="B58" s="56" t="s">
         <v>74</v>
       </c>
-      <c r="C58" s="52"/>
-      <c r="D58" s="52"/>
-      <c r="E58" s="52"/>
-      <c r="F58" s="52"/>
+      <c r="C58" s="56"/>
+      <c r="D58" s="56"/>
+      <c r="E58" s="56"/>
+      <c r="F58" s="56"/>
     </row>
     <row r="59" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B59" s="51" t="s">
+      <c r="B59" s="55" t="s">
         <v>75</v>
       </c>
-      <c r="C59" s="51"/>
-      <c r="D59" s="51"/>
-      <c r="E59" s="51"/>
-      <c r="F59" s="51"/>
+      <c r="C59" s="55"/>
+      <c r="D59" s="55"/>
+      <c r="E59" s="55"/>
+      <c r="F59" s="55"/>
     </row>
     <row r="60" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B60" s="58" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C60" s="58"/>
       <c r="D60" s="58"/>
@@ -2476,7 +2476,7 @@
     </row>
     <row r="65" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B65" s="58" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="C65" s="58"/>
       <c r="D65" s="58"/>
@@ -2592,7 +2592,7 @@
     </row>
     <row r="72" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B72" s="58" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="C72" s="58"/>
       <c r="D72" s="58"/>
@@ -2603,56 +2603,56 @@
       <c r="I72" s="58"/>
     </row>
     <row r="73" spans="2:9" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B73" s="51" t="s">
+      <c r="B73" s="55" t="s">
         <v>87</v>
       </c>
-      <c r="C73" s="51"/>
-      <c r="D73" s="51"/>
-      <c r="E73" s="51"/>
-      <c r="F73" s="51"/>
-      <c r="G73" s="51"/>
-      <c r="H73" s="51"/>
-      <c r="I73" s="51"/>
+      <c r="C73" s="55"/>
+      <c r="D73" s="55"/>
+      <c r="E73" s="55"/>
+      <c r="F73" s="55"/>
+      <c r="G73" s="55"/>
+      <c r="H73" s="55"/>
+      <c r="I73" s="55"/>
     </row>
     <row r="74" spans="2:9" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B74" s="52" t="s">
+      <c r="B74" s="56" t="s">
         <v>88</v>
       </c>
-      <c r="C74" s="52"/>
-      <c r="D74" s="52"/>
-      <c r="E74" s="52"/>
-      <c r="F74" s="52"/>
-      <c r="G74" s="52"/>
-      <c r="H74" s="52"/>
-      <c r="I74" s="52"/>
+      <c r="C74" s="56"/>
+      <c r="D74" s="56"/>
+      <c r="E74" s="56"/>
+      <c r="F74" s="56"/>
+      <c r="G74" s="56"/>
+      <c r="H74" s="56"/>
+      <c r="I74" s="56"/>
     </row>
     <row r="75" spans="2:9" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B75" s="51" t="s">
+      <c r="B75" s="55" t="s">
         <v>89</v>
       </c>
-      <c r="C75" s="51"/>
-      <c r="D75" s="51"/>
-      <c r="E75" s="51"/>
-      <c r="F75" s="51"/>
-      <c r="G75" s="51"/>
-      <c r="H75" s="51"/>
-      <c r="I75" s="51"/>
+      <c r="C75" s="55"/>
+      <c r="D75" s="55"/>
+      <c r="E75" s="55"/>
+      <c r="F75" s="55"/>
+      <c r="G75" s="55"/>
+      <c r="H75" s="55"/>
+      <c r="I75" s="55"/>
     </row>
     <row r="76" spans="2:9" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B76" s="52" t="s">
+      <c r="B76" s="56" t="s">
         <v>90</v>
       </c>
-      <c r="C76" s="52"/>
-      <c r="D76" s="52"/>
-      <c r="E76" s="52"/>
-      <c r="F76" s="52"/>
-      <c r="G76" s="52"/>
-      <c r="H76" s="52"/>
-      <c r="I76" s="52"/>
+      <c r="C76" s="56"/>
+      <c r="D76" s="56"/>
+      <c r="E76" s="56"/>
+      <c r="F76" s="56"/>
+      <c r="G76" s="56"/>
+      <c r="H76" s="56"/>
+      <c r="I76" s="56"/>
     </row>
     <row r="77" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B77" s="58" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="C77" s="58"/>
       <c r="D77" s="58"/>
@@ -2663,115 +2663,115 @@
       <c r="I77" s="58"/>
     </row>
     <row r="78" spans="2:9" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B78" s="57" t="s">
+      <c r="B78" s="64" t="s">
         <v>91</v>
       </c>
-      <c r="C78" s="57"/>
-      <c r="D78" s="57"/>
-      <c r="E78" s="57"/>
-      <c r="F78" s="57"/>
-      <c r="G78" s="57"/>
-      <c r="H78" s="57"/>
-      <c r="I78" s="57"/>
+      <c r="C78" s="64"/>
+      <c r="D78" s="64"/>
+      <c r="E78" s="64"/>
+      <c r="F78" s="64"/>
+      <c r="G78" s="64"/>
+      <c r="H78" s="64"/>
+      <c r="I78" s="64"/>
     </row>
     <row r="79" spans="2:9" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B79" s="51" t="s">
+      <c r="B79" s="55" t="s">
         <v>92</v>
       </c>
-      <c r="C79" s="51"/>
-      <c r="D79" s="51"/>
-      <c r="E79" s="51"/>
-      <c r="F79" s="51"/>
-      <c r="G79" s="51"/>
-      <c r="H79" s="51"/>
-      <c r="I79" s="51"/>
+      <c r="C79" s="55"/>
+      <c r="D79" s="55"/>
+      <c r="E79" s="55"/>
+      <c r="F79" s="55"/>
+      <c r="G79" s="55"/>
+      <c r="H79" s="55"/>
+      <c r="I79" s="55"/>
     </row>
     <row r="80" spans="2:9" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B80" s="57" t="s">
+      <c r="B80" s="64" t="s">
         <v>93</v>
       </c>
-      <c r="C80" s="57"/>
-      <c r="D80" s="57"/>
-      <c r="E80" s="57"/>
-      <c r="F80" s="57"/>
-      <c r="G80" s="57"/>
-      <c r="H80" s="57"/>
-      <c r="I80" s="57"/>
+      <c r="C80" s="64"/>
+      <c r="D80" s="64"/>
+      <c r="E80" s="64"/>
+      <c r="F80" s="64"/>
+      <c r="G80" s="64"/>
+      <c r="H80" s="64"/>
+      <c r="I80" s="64"/>
     </row>
     <row r="81" spans="2:9" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B81" s="51" t="s">
+      <c r="B81" s="55" t="s">
         <v>94</v>
       </c>
-      <c r="C81" s="51"/>
-      <c r="D81" s="51"/>
-      <c r="E81" s="51"/>
-      <c r="F81" s="51"/>
-      <c r="G81" s="51"/>
-      <c r="H81" s="51"/>
-      <c r="I81" s="51"/>
+      <c r="C81" s="55"/>
+      <c r="D81" s="55"/>
+      <c r="E81" s="55"/>
+      <c r="F81" s="55"/>
+      <c r="G81" s="55"/>
+      <c r="H81" s="55"/>
+      <c r="I81" s="55"/>
     </row>
     <row r="82" spans="2:9" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B82" s="57" t="s">
+      <c r="B82" s="64" t="s">
         <v>95</v>
       </c>
-      <c r="C82" s="57"/>
-      <c r="D82" s="57"/>
-      <c r="E82" s="57"/>
-      <c r="F82" s="57"/>
-      <c r="G82" s="57"/>
-      <c r="H82" s="57"/>
-      <c r="I82" s="57"/>
+      <c r="C82" s="64"/>
+      <c r="D82" s="64"/>
+      <c r="E82" s="64"/>
+      <c r="F82" s="64"/>
+      <c r="G82" s="64"/>
+      <c r="H82" s="64"/>
+      <c r="I82" s="64"/>
     </row>
     <row r="84" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B84" s="50" t="s">
+      <c r="B84" s="54" t="s">
         <v>2</v>
       </c>
-      <c r="C84" s="50"/>
-      <c r="D84" s="50"/>
-      <c r="E84" s="50"/>
-      <c r="F84" s="50"/>
-      <c r="G84" s="50"/>
-      <c r="H84" s="50"/>
-      <c r="I84" s="50"/>
+      <c r="C84" s="54"/>
+      <c r="D84" s="54"/>
+      <c r="E84" s="54"/>
+      <c r="F84" s="54"/>
+      <c r="G84" s="54"/>
+      <c r="H84" s="54"/>
+      <c r="I84" s="54"/>
     </row>
   </sheetData>
   <mergeCells count="36">
-    <mergeCell ref="B1:I1"/>
-    <mergeCell ref="B3:F3"/>
-    <mergeCell ref="B8:F8"/>
-    <mergeCell ref="B15:F15"/>
-    <mergeCell ref="B20:I20"/>
-    <mergeCell ref="B27:F27"/>
-    <mergeCell ref="B28:F28"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="B30:F30"/>
-    <mergeCell ref="B31:F31"/>
-    <mergeCell ref="B32:I32"/>
-    <mergeCell ref="B41:F41"/>
-    <mergeCell ref="B42:F42"/>
-    <mergeCell ref="B43:F43"/>
-    <mergeCell ref="B44:F44"/>
-    <mergeCell ref="B45:F45"/>
-    <mergeCell ref="B46:I46"/>
-    <mergeCell ref="B55:F55"/>
-    <mergeCell ref="B56:F56"/>
-    <mergeCell ref="B57:F57"/>
-    <mergeCell ref="B58:F58"/>
-    <mergeCell ref="B59:F59"/>
-    <mergeCell ref="B60:I60"/>
-    <mergeCell ref="B65:I65"/>
-    <mergeCell ref="B72:I72"/>
-    <mergeCell ref="B73:I73"/>
-    <mergeCell ref="B74:I74"/>
-    <mergeCell ref="B75:I75"/>
-    <mergeCell ref="B76:I76"/>
-    <mergeCell ref="B77:I77"/>
     <mergeCell ref="B84:I84"/>
     <mergeCell ref="B78:I78"/>
     <mergeCell ref="B79:I79"/>
     <mergeCell ref="B80:I80"/>
     <mergeCell ref="B81:I81"/>
     <mergeCell ref="B82:I82"/>
+    <mergeCell ref="B73:I73"/>
+    <mergeCell ref="B74:I74"/>
+    <mergeCell ref="B75:I75"/>
+    <mergeCell ref="B76:I76"/>
+    <mergeCell ref="B77:I77"/>
+    <mergeCell ref="B58:F58"/>
+    <mergeCell ref="B59:F59"/>
+    <mergeCell ref="B60:I60"/>
+    <mergeCell ref="B65:I65"/>
+    <mergeCell ref="B72:I72"/>
+    <mergeCell ref="B45:F45"/>
+    <mergeCell ref="B46:I46"/>
+    <mergeCell ref="B55:F55"/>
+    <mergeCell ref="B56:F56"/>
+    <mergeCell ref="B57:F57"/>
+    <mergeCell ref="B32:I32"/>
+    <mergeCell ref="B41:F41"/>
+    <mergeCell ref="B42:F42"/>
+    <mergeCell ref="B43:F43"/>
+    <mergeCell ref="B44:F44"/>
+    <mergeCell ref="B27:F27"/>
+    <mergeCell ref="B28:F28"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="B30:F30"/>
+    <mergeCell ref="B31:F31"/>
+    <mergeCell ref="B1:I1"/>
+    <mergeCell ref="B3:F3"/>
+    <mergeCell ref="B8:F8"/>
+    <mergeCell ref="B15:F15"/>
+    <mergeCell ref="B20:I20"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -2791,20 +2791,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B1" s="63" t="s">
-        <v>203</v>
-      </c>
-      <c r="C1" s="63"/>
-      <c r="D1" s="63"/>
-      <c r="E1" s="63"/>
-      <c r="F1" s="63"/>
-      <c r="G1" s="63"/>
-      <c r="H1" s="63"/>
-      <c r="I1" s="63"/>
+      <c r="B1" s="57" t="s">
+        <v>202</v>
+      </c>
+      <c r="C1" s="57"/>
+      <c r="D1" s="57"/>
+      <c r="E1" s="57"/>
+      <c r="F1" s="57"/>
+      <c r="G1" s="57"/>
+      <c r="H1" s="57"/>
+      <c r="I1" s="57"/>
     </row>
     <row r="3" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B3" s="58" t="s">
-        <v>96</v>
+        <v>210</v>
       </c>
       <c r="C3" s="58"/>
       <c r="D3" s="58"/>
@@ -2830,7 +2830,7 @@
     </row>
     <row r="5" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B5" s="10" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C5" s="11">
         <v>19379.09</v>
@@ -2847,7 +2847,7 @@
     </row>
     <row r="6" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B6" s="4" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C6" s="9">
         <v>4569.93</v>
@@ -2864,7 +2864,7 @@
     </row>
     <row r="7" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B7" s="12" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C7" s="13">
         <v>938.17</v>
@@ -2881,7 +2881,7 @@
     </row>
     <row r="8" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B8" s="14" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C8" s="15">
         <v>5631.44</v>
@@ -2898,7 +2898,7 @@
     </row>
     <row r="9" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B9" s="4" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C9" s="9">
         <v>6315.42</v>
@@ -2915,7 +2915,7 @@
     </row>
     <row r="10" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B10" s="12" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C10" s="13">
         <v>230.5</v>
@@ -2932,7 +2932,7 @@
     </row>
     <row r="12" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B12" s="58" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C12" s="58"/>
       <c r="D12" s="58"/>
@@ -2944,7 +2944,7 @@
     </row>
     <row r="13" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B13" s="7" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C13" s="8" t="s">
         <v>28</v>
@@ -2961,7 +2961,7 @@
     </row>
     <row r="14" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B14" s="4" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C14" s="26">
         <f>C6</f>
@@ -2982,7 +2982,7 @@
     </row>
     <row r="15" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B15" s="12" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C15" s="27">
         <f>C8</f>
@@ -3003,7 +3003,7 @@
     </row>
     <row r="16" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B16" s="10" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C16" s="16">
         <f>C14-C15</f>
@@ -3024,7 +3024,7 @@
     </row>
     <row r="17" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B17" s="4" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C17" s="28">
         <f>C14*365/19381.71</f>
@@ -3045,7 +3045,7 @@
     </row>
     <row r="19" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B19" s="58" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C19" s="58"/>
       <c r="D19" s="58"/>
@@ -3057,7 +3057,7 @@
     </row>
     <row r="20" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B20" s="7" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C20" s="8" t="s">
         <v>28</v>
@@ -3074,7 +3074,7 @@
     </row>
     <row r="21" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B21" s="4" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C21" s="29">
         <f>C7/C6</f>
@@ -3095,7 +3095,7 @@
     </row>
     <row r="22" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B22" s="12" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C22" s="30">
         <f>C5/C6</f>
@@ -3116,10 +3116,10 @@
     </row>
     <row r="23" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B23" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="C23" s="31" t="s">
         <v>113</v>
-      </c>
-      <c r="C23" s="31" t="s">
-        <v>114</v>
       </c>
       <c r="D23" s="32">
         <v>2.02</v>
@@ -3133,10 +3133,10 @@
     </row>
     <row r="24" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B24" s="12" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C24" s="33" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D24" s="34">
         <v>0.99</v>
@@ -3150,17 +3150,17 @@
     </row>
     <row r="25" spans="2:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="26" spans="2:9" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B26" s="59" t="s">
-        <v>116</v>
-      </c>
-      <c r="C26" s="60"/>
-      <c r="D26" s="60"/>
-      <c r="E26" s="60"/>
-      <c r="F26" s="61"/>
+      <c r="B26" s="60" t="s">
+        <v>115</v>
+      </c>
+      <c r="C26" s="61"/>
+      <c r="D26" s="61"/>
+      <c r="E26" s="61"/>
+      <c r="F26" s="62"/>
     </row>
     <row r="27" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B27" s="65" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C27" s="65"/>
       <c r="D27" s="65"/>
@@ -3168,35 +3168,35 @@
       <c r="F27" s="65"/>
     </row>
     <row r="28" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B28" s="52" t="s">
+      <c r="B28" s="56" t="s">
+        <v>117</v>
+      </c>
+      <c r="C28" s="56"/>
+      <c r="D28" s="56"/>
+      <c r="E28" s="56"/>
+      <c r="F28" s="56"/>
+    </row>
+    <row r="29" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B29" s="55" t="s">
         <v>118</v>
       </c>
-      <c r="C28" s="52"/>
-      <c r="D28" s="52"/>
-      <c r="E28" s="52"/>
-      <c r="F28" s="52"/>
-    </row>
-    <row r="29" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B29" s="51" t="s">
+      <c r="C29" s="55"/>
+      <c r="D29" s="55"/>
+      <c r="E29" s="55"/>
+      <c r="F29" s="55"/>
+    </row>
+    <row r="30" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B30" s="56" t="s">
         <v>119</v>
       </c>
-      <c r="C29" s="51"/>
-      <c r="D29" s="51"/>
-      <c r="E29" s="51"/>
-      <c r="F29" s="51"/>
-    </row>
-    <row r="30" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B30" s="52" t="s">
-        <v>120</v>
-      </c>
-      <c r="C30" s="52"/>
-      <c r="D30" s="52"/>
-      <c r="E30" s="52"/>
-      <c r="F30" s="52"/>
+      <c r="C30" s="56"/>
+      <c r="D30" s="56"/>
+      <c r="E30" s="56"/>
+      <c r="F30" s="56"/>
     </row>
     <row r="31" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B31" s="58" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C31" s="58"/>
       <c r="D31" s="58"/>
@@ -3222,7 +3222,7 @@
     </row>
     <row r="33" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B33" s="20" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C33" s="21">
         <v>0.09</v>
@@ -3236,7 +3236,7 @@
     </row>
     <row r="34" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B34" s="20" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C34" s="11">
         <v>300</v>
@@ -3250,7 +3250,7 @@
     </row>
     <row r="35" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B35" s="20" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C35" s="21">
         <v>0.08</v>
@@ -3264,7 +3264,7 @@
     </row>
     <row r="36" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B36" s="58" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C36" s="58"/>
       <c r="D36" s="58"/>
@@ -3362,7 +3362,7 @@
     </row>
     <row r="42" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B42" s="58" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C42" s="58"/>
       <c r="D42" s="58"/>
@@ -3373,77 +3373,67 @@
       <c r="I42" s="58"/>
     </row>
     <row r="43" spans="2:9" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B43" s="51" t="s">
+      <c r="B43" s="55" t="s">
+        <v>126</v>
+      </c>
+      <c r="C43" s="55"/>
+      <c r="D43" s="55"/>
+      <c r="E43" s="55"/>
+      <c r="F43" s="55"/>
+      <c r="G43" s="55"/>
+      <c r="H43" s="55"/>
+      <c r="I43" s="55"/>
+    </row>
+    <row r="44" spans="2:9" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B44" s="64" t="s">
         <v>127</v>
       </c>
-      <c r="C43" s="51"/>
-      <c r="D43" s="51"/>
-      <c r="E43" s="51"/>
-      <c r="F43" s="51"/>
-      <c r="G43" s="51"/>
-      <c r="H43" s="51"/>
-      <c r="I43" s="51"/>
-    </row>
-    <row r="44" spans="2:9" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B44" s="57" t="s">
+      <c r="C44" s="64"/>
+      <c r="D44" s="64"/>
+      <c r="E44" s="64"/>
+      <c r="F44" s="64"/>
+      <c r="G44" s="64"/>
+      <c r="H44" s="64"/>
+      <c r="I44" s="64"/>
+    </row>
+    <row r="45" spans="2:9" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B45" s="55" t="s">
         <v>128</v>
       </c>
-      <c r="C44" s="57"/>
-      <c r="D44" s="57"/>
-      <c r="E44" s="57"/>
-      <c r="F44" s="57"/>
-      <c r="G44" s="57"/>
-      <c r="H44" s="57"/>
-      <c r="I44" s="57"/>
-    </row>
-    <row r="45" spans="2:9" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B45" s="51" t="s">
+      <c r="C45" s="55"/>
+      <c r="D45" s="55"/>
+      <c r="E45" s="55"/>
+      <c r="F45" s="55"/>
+      <c r="G45" s="55"/>
+      <c r="H45" s="55"/>
+      <c r="I45" s="55"/>
+    </row>
+    <row r="46" spans="2:9" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B46" s="64" t="s">
         <v>129</v>
       </c>
-      <c r="C45" s="51"/>
-      <c r="D45" s="51"/>
-      <c r="E45" s="51"/>
-      <c r="F45" s="51"/>
-      <c r="G45" s="51"/>
-      <c r="H45" s="51"/>
-      <c r="I45" s="51"/>
-    </row>
-    <row r="46" spans="2:9" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B46" s="57" t="s">
-        <v>130</v>
-      </c>
-      <c r="C46" s="57"/>
-      <c r="D46" s="57"/>
-      <c r="E46" s="57"/>
-      <c r="F46" s="57"/>
-      <c r="G46" s="57"/>
-      <c r="H46" s="57"/>
-      <c r="I46" s="57"/>
+      <c r="C46" s="64"/>
+      <c r="D46" s="64"/>
+      <c r="E46" s="64"/>
+      <c r="F46" s="64"/>
+      <c r="G46" s="64"/>
+      <c r="H46" s="64"/>
+      <c r="I46" s="64"/>
     </row>
     <row r="48" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B48" s="50" t="s">
+      <c r="B48" s="54" t="s">
         <v>2</v>
       </c>
-      <c r="C48" s="50"/>
-      <c r="D48" s="50"/>
-      <c r="E48" s="50"/>
-      <c r="F48" s="50"/>
-      <c r="G48" s="50"/>
-      <c r="H48" s="50"/>
-      <c r="I48" s="50"/>
+      <c r="C48" s="54"/>
+      <c r="D48" s="54"/>
+      <c r="E48" s="54"/>
+      <c r="F48" s="54"/>
+      <c r="G48" s="54"/>
+      <c r="H48" s="54"/>
+      <c r="I48" s="54"/>
     </row>
   </sheetData>
   <mergeCells count="17">
-    <mergeCell ref="B1:I1"/>
-    <mergeCell ref="B3:F3"/>
-    <mergeCell ref="B12:I12"/>
-    <mergeCell ref="B19:I19"/>
-    <mergeCell ref="B26:F26"/>
-    <mergeCell ref="B27:F27"/>
-    <mergeCell ref="B28:F28"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="B30:F30"/>
-    <mergeCell ref="B31:I31"/>
     <mergeCell ref="B46:I46"/>
     <mergeCell ref="B48:I48"/>
     <mergeCell ref="B36:I36"/>
@@ -3451,6 +3441,16 @@
     <mergeCell ref="B43:I43"/>
     <mergeCell ref="B44:I44"/>
     <mergeCell ref="B45:I45"/>
+    <mergeCell ref="B27:F27"/>
+    <mergeCell ref="B28:F28"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="B30:F30"/>
+    <mergeCell ref="B31:I31"/>
+    <mergeCell ref="B1:I1"/>
+    <mergeCell ref="B3:F3"/>
+    <mergeCell ref="B12:I12"/>
+    <mergeCell ref="B19:I19"/>
+    <mergeCell ref="B26:F26"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -3471,20 +3471,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B1" s="63" t="s">
-        <v>131</v>
-      </c>
-      <c r="C1" s="63"/>
-      <c r="D1" s="63"/>
-      <c r="E1" s="63"/>
-      <c r="F1" s="63"/>
-      <c r="G1" s="63"/>
-      <c r="H1" s="63"/>
-      <c r="I1" s="63"/>
+      <c r="B1" s="57" t="s">
+        <v>130</v>
+      </c>
+      <c r="C1" s="57"/>
+      <c r="D1" s="57"/>
+      <c r="E1" s="57"/>
+      <c r="F1" s="57"/>
+      <c r="G1" s="57"/>
+      <c r="H1" s="57"/>
+      <c r="I1" s="57"/>
     </row>
     <row r="3" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B3" s="58" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C3" s="58"/>
       <c r="D3" s="58"/>
@@ -3510,7 +3510,7 @@
     </row>
     <row r="5" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B5" s="10" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C5" s="11">
         <v>4806.17</v>
@@ -3527,7 +3527,7 @@
     </row>
     <row r="6" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B6" s="4" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C6" s="9">
         <v>-1462.83</v>
@@ -3544,7 +3544,7 @@
     </row>
     <row r="7" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B7" s="12" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C7" s="13">
         <v>-189.36</v>
@@ -3561,7 +3561,7 @@
     </row>
     <row r="8" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B8" s="14" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C8" s="25">
         <f>C5+C6+C7</f>
@@ -3582,7 +3582,7 @@
     </row>
     <row r="9" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B9" s="14" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C9" s="15">
         <v>4569.93</v>
@@ -3599,7 +3599,7 @@
     </row>
     <row r="11" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B11" s="58" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="C11" s="58"/>
       <c r="D11" s="58"/>
@@ -3611,7 +3611,7 @@
     </row>
     <row r="12" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B12" s="7" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C12" s="8" t="s">
         <v>28</v>
@@ -3645,7 +3645,7 @@
     </row>
     <row r="14" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B14" s="12" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C14" s="13">
         <v>4806.17</v>
@@ -3662,7 +3662,7 @@
     </row>
     <row r="15" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B15" s="10" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C15" s="16">
         <f>C14-C13</f>
@@ -3683,7 +3683,7 @@
     </row>
     <row r="16" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B16" s="4" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C16" s="29">
         <f>C14/C13</f>
@@ -3704,17 +3704,17 @@
     </row>
     <row r="17" spans="2:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="18" spans="2:9" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B18" s="59" t="s">
-        <v>141</v>
-      </c>
-      <c r="C18" s="60"/>
-      <c r="D18" s="60"/>
-      <c r="E18" s="60"/>
-      <c r="F18" s="61"/>
+      <c r="B18" s="60" t="s">
+        <v>140</v>
+      </c>
+      <c r="C18" s="61"/>
+      <c r="D18" s="61"/>
+      <c r="E18" s="61"/>
+      <c r="F18" s="62"/>
     </row>
     <row r="19" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B19" s="65" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C19" s="65"/>
       <c r="D19" s="65"/>
@@ -3722,44 +3722,44 @@
       <c r="F19" s="65"/>
     </row>
     <row r="20" spans="2:9" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B20" s="52" t="s">
+      <c r="B20" s="56" t="s">
+        <v>142</v>
+      </c>
+      <c r="C20" s="56"/>
+      <c r="D20" s="56"/>
+      <c r="E20" s="56"/>
+      <c r="F20" s="56"/>
+    </row>
+    <row r="21" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B21" s="55" t="s">
         <v>143</v>
       </c>
-      <c r="C20" s="52"/>
-      <c r="D20" s="52"/>
-      <c r="E20" s="52"/>
-      <c r="F20" s="52"/>
-    </row>
-    <row r="21" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B21" s="51" t="s">
+      <c r="C21" s="55"/>
+      <c r="D21" s="55"/>
+      <c r="E21" s="55"/>
+      <c r="F21" s="55"/>
+    </row>
+    <row r="22" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B22" s="56" t="s">
         <v>144</v>
       </c>
-      <c r="C21" s="51"/>
-      <c r="D21" s="51"/>
-      <c r="E21" s="51"/>
-      <c r="F21" s="51"/>
-    </row>
-    <row r="22" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B22" s="52" t="s">
+      <c r="C22" s="56"/>
+      <c r="D22" s="56"/>
+      <c r="E22" s="56"/>
+      <c r="F22" s="56"/>
+    </row>
+    <row r="23" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B23" s="55" t="s">
         <v>145</v>
       </c>
-      <c r="C22" s="52"/>
-      <c r="D22" s="52"/>
-      <c r="E22" s="52"/>
-      <c r="F22" s="52"/>
-    </row>
-    <row r="23" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B23" s="51" t="s">
-        <v>146</v>
-      </c>
-      <c r="C23" s="51"/>
-      <c r="D23" s="51"/>
-      <c r="E23" s="51"/>
-      <c r="F23" s="51"/>
+      <c r="C23" s="55"/>
+      <c r="D23" s="55"/>
+      <c r="E23" s="55"/>
+      <c r="F23" s="55"/>
     </row>
     <row r="24" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B24" s="58" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="C24" s="58"/>
       <c r="D24" s="58"/>
@@ -3785,7 +3785,7 @@
     </row>
     <row r="26" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B26" s="20" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C26" s="11">
         <v>1350</v>
@@ -3799,7 +3799,7 @@
     </row>
     <row r="27" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B27" s="20" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C27" s="35">
         <v>1.2</v>
@@ -3813,7 +3813,7 @@
     </row>
     <row r="28" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B28" s="20" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C28" s="11">
         <v>-1500</v>
@@ -3827,7 +3827,7 @@
     </row>
     <row r="29" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B29" s="58" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C29" s="58"/>
       <c r="D29" s="58"/>
@@ -3925,7 +3925,7 @@
     </row>
     <row r="35" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B35" s="58" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C35" s="58"/>
       <c r="D35" s="58"/>
@@ -3936,89 +3936,79 @@
       <c r="I35" s="58"/>
     </row>
     <row r="36" spans="2:9" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B36" s="57" t="s">
+      <c r="B36" s="64" t="s">
+        <v>150</v>
+      </c>
+      <c r="C36" s="64"/>
+      <c r="D36" s="64"/>
+      <c r="E36" s="64"/>
+      <c r="F36" s="64"/>
+      <c r="G36" s="64"/>
+      <c r="H36" s="64"/>
+      <c r="I36" s="64"/>
+    </row>
+    <row r="37" spans="2:9" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B37" s="55" t="s">
         <v>151</v>
       </c>
-      <c r="C36" s="57"/>
-      <c r="D36" s="57"/>
-      <c r="E36" s="57"/>
-      <c r="F36" s="57"/>
-      <c r="G36" s="57"/>
-      <c r="H36" s="57"/>
-      <c r="I36" s="57"/>
-    </row>
-    <row r="37" spans="2:9" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B37" s="51" t="s">
+      <c r="C37" s="55"/>
+      <c r="D37" s="55"/>
+      <c r="E37" s="55"/>
+      <c r="F37" s="55"/>
+      <c r="G37" s="55"/>
+      <c r="H37" s="55"/>
+      <c r="I37" s="55"/>
+    </row>
+    <row r="38" spans="2:9" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B38" s="64" t="s">
         <v>152</v>
       </c>
-      <c r="C37" s="51"/>
-      <c r="D37" s="51"/>
-      <c r="E37" s="51"/>
-      <c r="F37" s="51"/>
-      <c r="G37" s="51"/>
-      <c r="H37" s="51"/>
-      <c r="I37" s="51"/>
-    </row>
-    <row r="38" spans="2:9" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B38" s="57" t="s">
+      <c r="C38" s="64"/>
+      <c r="D38" s="64"/>
+      <c r="E38" s="64"/>
+      <c r="F38" s="64"/>
+      <c r="G38" s="64"/>
+      <c r="H38" s="64"/>
+      <c r="I38" s="64"/>
+    </row>
+    <row r="39" spans="2:9" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B39" s="55" t="s">
         <v>153</v>
       </c>
-      <c r="C38" s="57"/>
-      <c r="D38" s="57"/>
-      <c r="E38" s="57"/>
-      <c r="F38" s="57"/>
-      <c r="G38" s="57"/>
-      <c r="H38" s="57"/>
-      <c r="I38" s="57"/>
-    </row>
-    <row r="39" spans="2:9" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B39" s="51" t="s">
+      <c r="C39" s="55"/>
+      <c r="D39" s="55"/>
+      <c r="E39" s="55"/>
+      <c r="F39" s="55"/>
+      <c r="G39" s="55"/>
+      <c r="H39" s="55"/>
+      <c r="I39" s="55"/>
+    </row>
+    <row r="40" spans="2:9" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B40" s="64" t="s">
         <v>154</v>
       </c>
-      <c r="C39" s="51"/>
-      <c r="D39" s="51"/>
-      <c r="E39" s="51"/>
-      <c r="F39" s="51"/>
-      <c r="G39" s="51"/>
-      <c r="H39" s="51"/>
-      <c r="I39" s="51"/>
-    </row>
-    <row r="40" spans="2:9" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B40" s="57" t="s">
-        <v>155</v>
-      </c>
-      <c r="C40" s="57"/>
-      <c r="D40" s="57"/>
-      <c r="E40" s="57"/>
-      <c r="F40" s="57"/>
-      <c r="G40" s="57"/>
-      <c r="H40" s="57"/>
-      <c r="I40" s="57"/>
+      <c r="C40" s="64"/>
+      <c r="D40" s="64"/>
+      <c r="E40" s="64"/>
+      <c r="F40" s="64"/>
+      <c r="G40" s="64"/>
+      <c r="H40" s="64"/>
+      <c r="I40" s="64"/>
     </row>
     <row r="42" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B42" s="50" t="s">
+      <c r="B42" s="54" t="s">
         <v>2</v>
       </c>
-      <c r="C42" s="50"/>
-      <c r="D42" s="50"/>
-      <c r="E42" s="50"/>
-      <c r="F42" s="50"/>
-      <c r="G42" s="50"/>
-      <c r="H42" s="50"/>
-      <c r="I42" s="50"/>
+      <c r="C42" s="54"/>
+      <c r="D42" s="54"/>
+      <c r="E42" s="54"/>
+      <c r="F42" s="54"/>
+      <c r="G42" s="54"/>
+      <c r="H42" s="54"/>
+      <c r="I42" s="54"/>
     </row>
   </sheetData>
   <mergeCells count="18">
-    <mergeCell ref="B1:I1"/>
-    <mergeCell ref="B3:F3"/>
-    <mergeCell ref="B11:I11"/>
-    <mergeCell ref="B18:F18"/>
-    <mergeCell ref="B19:F19"/>
-    <mergeCell ref="B20:F20"/>
-    <mergeCell ref="B21:F21"/>
-    <mergeCell ref="B22:F22"/>
-    <mergeCell ref="B23:F23"/>
-    <mergeCell ref="B24:I24"/>
     <mergeCell ref="B39:I39"/>
     <mergeCell ref="B40:I40"/>
     <mergeCell ref="B42:I42"/>
@@ -4027,6 +4017,16 @@
     <mergeCell ref="B36:I36"/>
     <mergeCell ref="B37:I37"/>
     <mergeCell ref="B38:I38"/>
+    <mergeCell ref="B20:F20"/>
+    <mergeCell ref="B21:F21"/>
+    <mergeCell ref="B22:F22"/>
+    <mergeCell ref="B23:F23"/>
+    <mergeCell ref="B24:I24"/>
+    <mergeCell ref="B1:I1"/>
+    <mergeCell ref="B3:F3"/>
+    <mergeCell ref="B11:I11"/>
+    <mergeCell ref="B18:F18"/>
+    <mergeCell ref="B19:F19"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -4044,17 +4044,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="63" t="s">
-        <v>207</v>
-      </c>
-      <c r="B1" s="63"/>
-      <c r="C1" s="63"/>
-      <c r="D1" s="63"/>
-      <c r="E1" s="63"/>
+      <c r="A1" s="57" t="s">
+        <v>206</v>
+      </c>
+      <c r="B1" s="57"/>
+      <c r="C1" s="57"/>
+      <c r="D1" s="57"/>
+      <c r="E1" s="57"/>
     </row>
     <row r="2" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="66" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="B2" s="66"/>
       <c r="C2" s="66"/>
@@ -4063,7 +4063,7 @@
     </row>
     <row r="4" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="7" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B4" s="8" t="s">
         <v>28</v>
@@ -4080,7 +4080,7 @@
     </row>
     <row r="5" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="36" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B5" s="37"/>
       <c r="C5" s="37"/>
@@ -4260,7 +4260,7 @@
     </row>
     <row r="19" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B19" s="9">
         <v>1406.24</v>
@@ -4311,7 +4311,7 @@
     </row>
     <row r="23" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="36" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B23" s="37"/>
       <c r="C23" s="37"/>
@@ -4320,7 +4320,7 @@
     </row>
     <row r="24" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="10" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B24" s="11">
         <v>19379.09</v>
@@ -4337,7 +4337,7 @@
     </row>
     <row r="25" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="10" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B25" s="11">
         <v>5631.44</v>
@@ -4354,7 +4354,7 @@
     </row>
     <row r="26" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="12" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B26" s="13">
         <v>938.17</v>
@@ -4371,7 +4371,7 @@
     </row>
     <row r="27" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="4" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B27" s="9">
         <v>4569.93</v>
@@ -4388,7 +4388,7 @@
     </row>
     <row r="28" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="12" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B28" s="13">
         <v>6315.42</v>
@@ -4405,7 +4405,7 @@
     </row>
     <row r="29" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="4" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B29" s="9">
         <v>230.5</v>
@@ -4422,7 +4422,7 @@
     </row>
     <row r="31" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="36" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B31" s="37"/>
       <c r="C31" s="37"/>
@@ -4431,7 +4431,7 @@
     </row>
     <row r="32" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="12" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B32" s="13">
         <v>4806.17</v>
@@ -4448,7 +4448,7 @@
     </row>
     <row r="33" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="4" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B33" s="9">
         <v>-1462.83</v>
@@ -4465,7 +4465,7 @@
     </row>
     <row r="34" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="12" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B34" s="13">
         <v>-189.36</v>
@@ -4482,7 +4482,7 @@
     </row>
     <row r="35" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="4" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B35" s="9">
         <v>4569.93</v>
@@ -4499,16 +4499,16 @@
     </row>
     <row r="37" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="38" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="39" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B39" s="50" t="s">
+      <c r="B39" s="54" t="s">
         <v>2</v>
       </c>
-      <c r="C39" s="50"/>
-      <c r="D39" s="50"/>
-      <c r="E39" s="50"/>
+      <c r="C39" s="54"/>
+      <c r="D39" s="54"/>
+      <c r="E39" s="54"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -4533,187 +4533,187 @@
   <sheetData>
     <row r="1" spans="2:2" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B1" s="39" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
     <row r="2" spans="2:2" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="40" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
     </row>
     <row r="4" spans="2:2" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B4" s="41" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="5" spans="2:2" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B5" s="42" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="6" spans="2:2" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B6" s="43" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="7" spans="2:2" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B7" s="42" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="8" spans="2:2" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B8" s="43" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="10" spans="2:2" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B10" s="41" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="11" spans="2:2" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B11" s="42" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="12" spans="2:2" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B12" s="43" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="13" spans="2:2" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B13" s="42" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="14" spans="2:2" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B14" s="43" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="16" spans="2:2" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B16" s="41" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="17" spans="2:2" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B17" s="42" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="18" spans="2:2" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B18" s="43" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="19" spans="2:2" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B19" s="42" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="20" spans="2:2" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B20" s="43" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="22" spans="2:2" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B22" s="41" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="23" spans="2:2" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B23" s="42" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="24" spans="2:2" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B24" s="43" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="25" spans="2:2" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B25" s="42" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="27" spans="2:2" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B27" s="41" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="28" spans="2:2" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B28" s="43" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="29" spans="2:2" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B29" s="42" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="30" spans="2:2" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B30" s="43" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="31" spans="2:2" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B31" s="42" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="33" spans="2:2" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B33" s="41" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="34" spans="2:2" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B34" s="43" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="35" spans="2:2" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B35" s="42" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="36" spans="2:2" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B36" s="43" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
     </row>
     <row r="37" spans="2:2" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B37" s="42" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="39" spans="2:2" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B39" s="44" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
     </row>
     <row r="40" spans="2:2" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B40" s="45" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="41" spans="2:2" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B41" s="46" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="42" spans="2:2" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B42" s="45" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="43" spans="2:2" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B43" s="46" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="44" spans="2:2" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B44" s="45" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
     <row r="46" spans="2:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">

--- a/myprojects/RVNL/RVNL_Business_Performance.xlsx
+++ b/myprojects/RVNL/RVNL_Business_Performance.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="900" windowWidth="28800" windowHeight="13860" tabRatio="500" activeTab="2"/>
+    <workbookView xWindow="0" yWindow="1350" windowWidth="28800" windowHeight="13860" tabRatio="500" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="HOME" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="301" uniqueCount="211">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="299" uniqueCount="209">
   <si>
     <t>RAIL VIKAS NIGAM LIMITED (RVNL)</t>
   </si>
@@ -343,18 +343,6 @@
     <t>Item</t>
   </si>
   <si>
-    <t>Trade Receivables  (money Railways owes RVNL)</t>
-  </si>
-  <si>
-    <t>Trade Payables  (money RVNL owes contractors)</t>
-  </si>
-  <si>
-    <t>Net Working Capital  (Receivables minus Payables)</t>
-  </si>
-  <si>
-    <t>Receivable Days  (how many days to collect payment)</t>
-  </si>
-  <si>
     <t>C.  KEY RATIOS  (Measuring financial health)</t>
   </si>
   <si>
@@ -370,9 +358,6 @@
     <t>Current Ratio  (from Annual Reports)</t>
   </si>
   <si>
-    <t>N/A</t>
-  </si>
-  <si>
     <t>Debt to Equity  (from Annual Reports)</t>
   </si>
   <si>
@@ -662,6 +647,15 @@
   </si>
   <si>
     <t xml:space="preserve">A.  BALANCE SHEET KEY ITEMS  (Rs. in Crore) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Receivable Days </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trade Payables  </t>
+  </si>
+  <si>
+    <t>Net Working Capital  (Receivables - Payables)</t>
   </si>
 </sst>
 </file>
@@ -776,13 +770,6 @@
     </font>
     <font>
       <i/>
-      <sz val="9"/>
-      <color rgb="FF808080"/>
-      <name val="Arial"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <i/>
       <sz val="8"/>
       <color rgb="FF0000FF"/>
       <name val="Arial"/>
@@ -815,6 +802,12 @@
       <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
       <charset val="1"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color theme="3"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="11">
@@ -1057,15 +1050,9 @@
     <xf numFmtId="2" fontId="13" fillId="8" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
     <xf numFmtId="2" fontId="10" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
     <xf numFmtId="2" fontId="10" fillId="8" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
@@ -1076,14 +1063,14 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1092,7 +1079,7 @@
     <xf numFmtId="0" fontId="5" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1104,6 +1091,21 @@
     <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1113,53 +1115,44 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="10" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="10" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="10" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="10" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="10" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="10" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1436,81 +1429,81 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:4" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B1" s="48" t="s">
+      <c r="B1" s="51" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="48"/>
-      <c r="D1" s="48"/>
+      <c r="C1" s="51"/>
+      <c r="D1" s="51"/>
     </row>
     <row r="2" spans="2:4" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="49" t="s">
+      <c r="B2" s="52" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="49"/>
-      <c r="D2" s="49"/>
+      <c r="C2" s="52"/>
+      <c r="D2" s="52"/>
     </row>
     <row r="3" spans="2:4" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="50" t="s">
+      <c r="B3" s="53" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="50"/>
-      <c r="D3" s="50"/>
+      <c r="C3" s="53"/>
+      <c r="D3" s="53"/>
     </row>
     <row r="5" spans="2:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="51" t="s">
+      <c r="B5" s="46" t="s">
         <v>3</v>
       </c>
-      <c r="C5" s="51"/>
-      <c r="D5" s="51"/>
+      <c r="C5" s="46"/>
+      <c r="D5" s="46"/>
     </row>
     <row r="6" spans="2:4" ht="54.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="52" t="s">
+      <c r="B6" s="54" t="s">
         <v>4</v>
       </c>
-      <c r="C6" s="52"/>
-      <c r="D6" s="52"/>
+      <c r="C6" s="54"/>
+      <c r="D6" s="54"/>
     </row>
     <row r="8" spans="2:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B8" s="51" t="s">
+      <c r="B8" s="46" t="s">
         <v>5</v>
       </c>
-      <c r="C8" s="51"/>
-      <c r="D8" s="51"/>
+      <c r="C8" s="46"/>
+      <c r="D8" s="46"/>
     </row>
     <row r="9" spans="2:4" ht="48" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B9" s="55" t="s">
+      <c r="B9" s="49" t="s">
         <v>6</v>
       </c>
-      <c r="C9" s="55"/>
-      <c r="D9" s="55"/>
+      <c r="C9" s="49"/>
+      <c r="D9" s="49"/>
     </row>
     <row r="10" spans="2:4" ht="48" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B10" s="56" t="s">
+      <c r="B10" s="50" t="s">
         <v>7</v>
       </c>
-      <c r="C10" s="56"/>
-      <c r="D10" s="56"/>
+      <c r="C10" s="50"/>
+      <c r="D10" s="50"/>
     </row>
     <row r="11" spans="2:4" ht="48" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B11" s="55" t="s">
+      <c r="B11" s="49" t="s">
         <v>8</v>
       </c>
-      <c r="C11" s="55"/>
-      <c r="D11" s="55"/>
+      <c r="C11" s="49"/>
+      <c r="D11" s="49"/>
     </row>
     <row r="12" spans="2:4" ht="48" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B12" s="56" t="s">
+      <c r="B12" s="50" t="s">
         <v>9</v>
       </c>
-      <c r="C12" s="56"/>
-      <c r="D12" s="56"/>
+      <c r="C12" s="50"/>
+      <c r="D12" s="50"/>
     </row>
     <row r="13" spans="2:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B13" s="51" t="s">
+      <c r="B13" s="46" t="s">
         <v>10</v>
       </c>
-      <c r="C13" s="51"/>
-      <c r="D13" s="51"/>
+      <c r="C13" s="46"/>
+      <c r="D13" s="46"/>
     </row>
     <row r="14" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B14" s="2" t="s">
@@ -1569,21 +1562,26 @@
       </c>
     </row>
     <row r="21" spans="2:4" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B21" s="53" t="s">
+      <c r="B21" s="47" t="s">
         <v>25</v>
       </c>
-      <c r="C21" s="53"/>
-      <c r="D21" s="53"/>
+      <c r="C21" s="47"/>
+      <c r="D21" s="47"/>
     </row>
     <row r="23" spans="2:4" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B23" s="54" t="s">
+      <c r="B23" s="48" t="s">
         <v>2</v>
       </c>
-      <c r="C23" s="54"/>
-      <c r="D23" s="54"/>
+      <c r="C23" s="48"/>
+      <c r="D23" s="48"/>
     </row>
   </sheetData>
   <mergeCells count="13">
+    <mergeCell ref="B1:D1"/>
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="B3:D3"/>
+    <mergeCell ref="B5:D5"/>
+    <mergeCell ref="B6:D6"/>
     <mergeCell ref="B13:D13"/>
     <mergeCell ref="B21:D21"/>
     <mergeCell ref="B23:D23"/>
@@ -1592,11 +1590,6 @@
     <mergeCell ref="B10:D10"/>
     <mergeCell ref="B11:D11"/>
     <mergeCell ref="B12:D12"/>
-    <mergeCell ref="B1:D1"/>
-    <mergeCell ref="B2:D2"/>
-    <mergeCell ref="B3:D3"/>
-    <mergeCell ref="B5:D5"/>
-    <mergeCell ref="B6:D6"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -1616,25 +1609,25 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B1" s="57" t="s">
-        <v>197</v>
-      </c>
-      <c r="C1" s="57"/>
-      <c r="D1" s="57"/>
-      <c r="E1" s="57"/>
-      <c r="F1" s="57"/>
-      <c r="G1" s="57"/>
-      <c r="H1" s="57"/>
-      <c r="I1" s="57"/>
+      <c r="B1" s="61" t="s">
+        <v>192</v>
+      </c>
+      <c r="C1" s="61"/>
+      <c r="D1" s="61"/>
+      <c r="E1" s="61"/>
+      <c r="F1" s="61"/>
+      <c r="G1" s="61"/>
+      <c r="H1" s="61"/>
+      <c r="I1" s="61"/>
     </row>
     <row r="3" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="58" t="s">
+      <c r="B3" s="56" t="s">
         <v>26</v>
       </c>
-      <c r="C3" s="58"/>
-      <c r="D3" s="58"/>
-      <c r="E3" s="58"/>
-      <c r="F3" s="58"/>
+      <c r="C3" s="56"/>
+      <c r="D3" s="56"/>
+      <c r="E3" s="56"/>
+      <c r="F3" s="56"/>
     </row>
     <row r="4" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B4" s="7" t="s">
@@ -1709,13 +1702,13 @@
       </c>
     </row>
     <row r="8" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B8" s="59" t="s">
+      <c r="B8" s="62" t="s">
         <v>35</v>
       </c>
-      <c r="C8" s="59"/>
-      <c r="D8" s="59"/>
-      <c r="E8" s="59"/>
-      <c r="F8" s="59"/>
+      <c r="C8" s="62"/>
+      <c r="D8" s="62"/>
+      <c r="E8" s="62"/>
+      <c r="F8" s="62"/>
     </row>
     <row r="9" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B9" s="4" t="s">
@@ -1824,13 +1817,13 @@
       </c>
     </row>
     <row r="15" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B15" s="59" t="s">
+      <c r="B15" s="62" t="s">
         <v>42</v>
       </c>
-      <c r="C15" s="59"/>
-      <c r="D15" s="59"/>
-      <c r="E15" s="59"/>
-      <c r="F15" s="59"/>
+      <c r="C15" s="62"/>
+      <c r="D15" s="62"/>
+      <c r="E15" s="62"/>
+      <c r="F15" s="62"/>
     </row>
     <row r="16" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B16" s="14" t="s">
@@ -1892,16 +1885,16 @@
       </c>
     </row>
     <row r="20" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B20" s="58" t="s">
+      <c r="B20" s="56" t="s">
         <v>46</v>
       </c>
-      <c r="C20" s="58"/>
-      <c r="D20" s="58"/>
-      <c r="E20" s="58"/>
-      <c r="F20" s="58"/>
-      <c r="G20" s="58"/>
-      <c r="H20" s="58"/>
-      <c r="I20" s="58"/>
+      <c r="C20" s="56"/>
+      <c r="D20" s="56"/>
+      <c r="E20" s="56"/>
+      <c r="F20" s="56"/>
+      <c r="G20" s="56"/>
+      <c r="H20" s="56"/>
+      <c r="I20" s="56"/>
     </row>
     <row r="21" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B21" s="7" t="s">
@@ -1987,61 +1980,61 @@
     </row>
     <row r="26" spans="2:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="27" spans="2:9" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B27" s="60" t="s">
+      <c r="B27" s="57" t="s">
         <v>52</v>
       </c>
-      <c r="C27" s="61"/>
-      <c r="D27" s="61"/>
-      <c r="E27" s="61"/>
-      <c r="F27" s="62"/>
+      <c r="C27" s="58"/>
+      <c r="D27" s="58"/>
+      <c r="E27" s="58"/>
+      <c r="F27" s="59"/>
     </row>
     <row r="28" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B28" s="63" t="s">
+      <c r="B28" s="60" t="s">
         <v>53</v>
       </c>
-      <c r="C28" s="63"/>
-      <c r="D28" s="63"/>
-      <c r="E28" s="63"/>
-      <c r="F28" s="63"/>
+      <c r="C28" s="60"/>
+      <c r="D28" s="60"/>
+      <c r="E28" s="60"/>
+      <c r="F28" s="60"/>
     </row>
     <row r="29" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B29" s="55" t="s">
+      <c r="B29" s="49" t="s">
         <v>54</v>
       </c>
-      <c r="C29" s="55"/>
-      <c r="D29" s="55"/>
-      <c r="E29" s="55"/>
-      <c r="F29" s="55"/>
+      <c r="C29" s="49"/>
+      <c r="D29" s="49"/>
+      <c r="E29" s="49"/>
+      <c r="F29" s="49"/>
     </row>
     <row r="30" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B30" s="56" t="s">
+      <c r="B30" s="50" t="s">
         <v>55</v>
       </c>
-      <c r="C30" s="56"/>
-      <c r="D30" s="56"/>
-      <c r="E30" s="56"/>
-      <c r="F30" s="56"/>
+      <c r="C30" s="50"/>
+      <c r="D30" s="50"/>
+      <c r="E30" s="50"/>
+      <c r="F30" s="50"/>
     </row>
     <row r="31" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B31" s="55" t="s">
+      <c r="B31" s="49" t="s">
         <v>56</v>
       </c>
-      <c r="C31" s="55"/>
-      <c r="D31" s="55"/>
-      <c r="E31" s="55"/>
-      <c r="F31" s="55"/>
+      <c r="C31" s="49"/>
+      <c r="D31" s="49"/>
+      <c r="E31" s="49"/>
+      <c r="F31" s="49"/>
     </row>
     <row r="32" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B32" s="58" t="s">
+      <c r="B32" s="56" t="s">
         <v>57</v>
       </c>
-      <c r="C32" s="58"/>
-      <c r="D32" s="58"/>
-      <c r="E32" s="58"/>
-      <c r="F32" s="58"/>
-      <c r="G32" s="58"/>
-      <c r="H32" s="58"/>
-      <c r="I32" s="58"/>
+      <c r="C32" s="56"/>
+      <c r="D32" s="56"/>
+      <c r="E32" s="56"/>
+      <c r="F32" s="56"/>
+      <c r="G32" s="56"/>
+      <c r="H32" s="56"/>
+      <c r="I32" s="56"/>
     </row>
     <row r="33" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B33" s="7" t="s">
@@ -2161,61 +2154,61 @@
     </row>
     <row r="40" spans="2:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="41" spans="2:9" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B41" s="60" t="s">
+      <c r="B41" s="57" t="s">
         <v>64</v>
       </c>
-      <c r="C41" s="61"/>
-      <c r="D41" s="61"/>
-      <c r="E41" s="61"/>
-      <c r="F41" s="62"/>
+      <c r="C41" s="58"/>
+      <c r="D41" s="58"/>
+      <c r="E41" s="58"/>
+      <c r="F41" s="59"/>
     </row>
     <row r="42" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B42" s="63" t="s">
+      <c r="B42" s="60" t="s">
         <v>65</v>
       </c>
-      <c r="C42" s="63"/>
-      <c r="D42" s="63"/>
-      <c r="E42" s="63"/>
-      <c r="F42" s="63"/>
+      <c r="C42" s="60"/>
+      <c r="D42" s="60"/>
+      <c r="E42" s="60"/>
+      <c r="F42" s="60"/>
     </row>
     <row r="43" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B43" s="55" t="s">
+      <c r="B43" s="49" t="s">
         <v>66</v>
       </c>
-      <c r="C43" s="55"/>
-      <c r="D43" s="55"/>
-      <c r="E43" s="55"/>
-      <c r="F43" s="55"/>
+      <c r="C43" s="49"/>
+      <c r="D43" s="49"/>
+      <c r="E43" s="49"/>
+      <c r="F43" s="49"/>
     </row>
     <row r="44" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B44" s="56" t="s">
+      <c r="B44" s="50" t="s">
         <v>67</v>
       </c>
-      <c r="C44" s="56"/>
-      <c r="D44" s="56"/>
-      <c r="E44" s="56"/>
-      <c r="F44" s="56"/>
+      <c r="C44" s="50"/>
+      <c r="D44" s="50"/>
+      <c r="E44" s="50"/>
+      <c r="F44" s="50"/>
     </row>
     <row r="45" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B45" s="55" t="s">
+      <c r="B45" s="49" t="s">
         <v>68</v>
       </c>
-      <c r="C45" s="55"/>
-      <c r="D45" s="55"/>
-      <c r="E45" s="55"/>
-      <c r="F45" s="55"/>
+      <c r="C45" s="49"/>
+      <c r="D45" s="49"/>
+      <c r="E45" s="49"/>
+      <c r="F45" s="49"/>
     </row>
     <row r="46" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B46" s="58" t="s">
+      <c r="B46" s="56" t="s">
         <v>69</v>
       </c>
-      <c r="C46" s="58"/>
-      <c r="D46" s="58"/>
-      <c r="E46" s="58"/>
-      <c r="F46" s="58"/>
-      <c r="G46" s="58"/>
-      <c r="H46" s="58"/>
-      <c r="I46" s="58"/>
+      <c r="C46" s="56"/>
+      <c r="D46" s="56"/>
+      <c r="E46" s="56"/>
+      <c r="F46" s="56"/>
+      <c r="G46" s="56"/>
+      <c r="H46" s="56"/>
+      <c r="I46" s="56"/>
     </row>
     <row r="47" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B47" s="7" t="s">
@@ -2362,61 +2355,61 @@
     </row>
     <row r="54" spans="2:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="55" spans="2:9" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B55" s="60" t="s">
+      <c r="B55" s="57" t="s">
         <v>71</v>
       </c>
-      <c r="C55" s="61"/>
-      <c r="D55" s="61"/>
-      <c r="E55" s="61"/>
-      <c r="F55" s="62"/>
+      <c r="C55" s="58"/>
+      <c r="D55" s="58"/>
+      <c r="E55" s="58"/>
+      <c r="F55" s="59"/>
     </row>
     <row r="56" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B56" s="63" t="s">
+      <c r="B56" s="60" t="s">
         <v>72</v>
       </c>
-      <c r="C56" s="63"/>
-      <c r="D56" s="63"/>
-      <c r="E56" s="63"/>
-      <c r="F56" s="63"/>
+      <c r="C56" s="60"/>
+      <c r="D56" s="60"/>
+      <c r="E56" s="60"/>
+      <c r="F56" s="60"/>
     </row>
     <row r="57" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B57" s="55" t="s">
+      <c r="B57" s="49" t="s">
         <v>73</v>
       </c>
-      <c r="C57" s="55"/>
-      <c r="D57" s="55"/>
-      <c r="E57" s="55"/>
-      <c r="F57" s="55"/>
+      <c r="C57" s="49"/>
+      <c r="D57" s="49"/>
+      <c r="E57" s="49"/>
+      <c r="F57" s="49"/>
     </row>
     <row r="58" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B58" s="56" t="s">
+      <c r="B58" s="50" t="s">
         <v>74</v>
       </c>
-      <c r="C58" s="56"/>
-      <c r="D58" s="56"/>
-      <c r="E58" s="56"/>
-      <c r="F58" s="56"/>
+      <c r="C58" s="50"/>
+      <c r="D58" s="50"/>
+      <c r="E58" s="50"/>
+      <c r="F58" s="50"/>
     </row>
     <row r="59" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B59" s="55" t="s">
+      <c r="B59" s="49" t="s">
         <v>75</v>
       </c>
-      <c r="C59" s="55"/>
-      <c r="D59" s="55"/>
-      <c r="E59" s="55"/>
-      <c r="F59" s="55"/>
+      <c r="C59" s="49"/>
+      <c r="D59" s="49"/>
+      <c r="E59" s="49"/>
+      <c r="F59" s="49"/>
     </row>
     <row r="60" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B60" s="58" t="s">
-        <v>200</v>
-      </c>
-      <c r="C60" s="58"/>
-      <c r="D60" s="58"/>
-      <c r="E60" s="58"/>
-      <c r="F60" s="58"/>
-      <c r="G60" s="58"/>
-      <c r="H60" s="58"/>
-      <c r="I60" s="58"/>
+      <c r="B60" s="56" t="s">
+        <v>195</v>
+      </c>
+      <c r="C60" s="56"/>
+      <c r="D60" s="56"/>
+      <c r="E60" s="56"/>
+      <c r="F60" s="56"/>
+      <c r="G60" s="56"/>
+      <c r="H60" s="56"/>
+      <c r="I60" s="56"/>
     </row>
     <row r="61" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B61" s="7" t="s">
@@ -2475,16 +2468,16 @@
       </c>
     </row>
     <row r="65" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B65" s="58" t="s">
-        <v>201</v>
-      </c>
-      <c r="C65" s="58"/>
-      <c r="D65" s="58"/>
-      <c r="E65" s="58"/>
-      <c r="F65" s="58"/>
-      <c r="G65" s="58"/>
-      <c r="H65" s="58"/>
-      <c r="I65" s="58"/>
+      <c r="B65" s="56" t="s">
+        <v>196</v>
+      </c>
+      <c r="C65" s="56"/>
+      <c r="D65" s="56"/>
+      <c r="E65" s="56"/>
+      <c r="F65" s="56"/>
+      <c r="G65" s="56"/>
+      <c r="H65" s="56"/>
+      <c r="I65" s="56"/>
     </row>
     <row r="66" spans="2:9" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B66" s="7" t="s">
@@ -2591,187 +2584,187 @@
       </c>
     </row>
     <row r="72" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B72" s="58" t="s">
-        <v>198</v>
-      </c>
-      <c r="C72" s="58"/>
-      <c r="D72" s="58"/>
-      <c r="E72" s="58"/>
-      <c r="F72" s="58"/>
-      <c r="G72" s="58"/>
-      <c r="H72" s="58"/>
-      <c r="I72" s="58"/>
+      <c r="B72" s="56" t="s">
+        <v>193</v>
+      </c>
+      <c r="C72" s="56"/>
+      <c r="D72" s="56"/>
+      <c r="E72" s="56"/>
+      <c r="F72" s="56"/>
+      <c r="G72" s="56"/>
+      <c r="H72" s="56"/>
+      <c r="I72" s="56"/>
     </row>
     <row r="73" spans="2:9" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B73" s="55" t="s">
+      <c r="B73" s="49" t="s">
         <v>87</v>
       </c>
-      <c r="C73" s="55"/>
-      <c r="D73" s="55"/>
-      <c r="E73" s="55"/>
-      <c r="F73" s="55"/>
-      <c r="G73" s="55"/>
-      <c r="H73" s="55"/>
-      <c r="I73" s="55"/>
+      <c r="C73" s="49"/>
+      <c r="D73" s="49"/>
+      <c r="E73" s="49"/>
+      <c r="F73" s="49"/>
+      <c r="G73" s="49"/>
+      <c r="H73" s="49"/>
+      <c r="I73" s="49"/>
     </row>
     <row r="74" spans="2:9" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B74" s="56" t="s">
+      <c r="B74" s="50" t="s">
         <v>88</v>
       </c>
-      <c r="C74" s="56"/>
-      <c r="D74" s="56"/>
-      <c r="E74" s="56"/>
-      <c r="F74" s="56"/>
-      <c r="G74" s="56"/>
-      <c r="H74" s="56"/>
-      <c r="I74" s="56"/>
+      <c r="C74" s="50"/>
+      <c r="D74" s="50"/>
+      <c r="E74" s="50"/>
+      <c r="F74" s="50"/>
+      <c r="G74" s="50"/>
+      <c r="H74" s="50"/>
+      <c r="I74" s="50"/>
     </row>
     <row r="75" spans="2:9" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B75" s="55" t="s">
+      <c r="B75" s="49" t="s">
         <v>89</v>
       </c>
-      <c r="C75" s="55"/>
-      <c r="D75" s="55"/>
-      <c r="E75" s="55"/>
-      <c r="F75" s="55"/>
-      <c r="G75" s="55"/>
-      <c r="H75" s="55"/>
-      <c r="I75" s="55"/>
+      <c r="C75" s="49"/>
+      <c r="D75" s="49"/>
+      <c r="E75" s="49"/>
+      <c r="F75" s="49"/>
+      <c r="G75" s="49"/>
+      <c r="H75" s="49"/>
+      <c r="I75" s="49"/>
     </row>
     <row r="76" spans="2:9" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B76" s="56" t="s">
+      <c r="B76" s="50" t="s">
         <v>90</v>
       </c>
-      <c r="C76" s="56"/>
-      <c r="D76" s="56"/>
-      <c r="E76" s="56"/>
-      <c r="F76" s="56"/>
-      <c r="G76" s="56"/>
-      <c r="H76" s="56"/>
-      <c r="I76" s="56"/>
+      <c r="C76" s="50"/>
+      <c r="D76" s="50"/>
+      <c r="E76" s="50"/>
+      <c r="F76" s="50"/>
+      <c r="G76" s="50"/>
+      <c r="H76" s="50"/>
+      <c r="I76" s="50"/>
     </row>
     <row r="77" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B77" s="58" t="s">
-        <v>199</v>
-      </c>
-      <c r="C77" s="58"/>
-      <c r="D77" s="58"/>
-      <c r="E77" s="58"/>
-      <c r="F77" s="58"/>
-      <c r="G77" s="58"/>
-      <c r="H77" s="58"/>
-      <c r="I77" s="58"/>
+      <c r="B77" s="56" t="s">
+        <v>194</v>
+      </c>
+      <c r="C77" s="56"/>
+      <c r="D77" s="56"/>
+      <c r="E77" s="56"/>
+      <c r="F77" s="56"/>
+      <c r="G77" s="56"/>
+      <c r="H77" s="56"/>
+      <c r="I77" s="56"/>
     </row>
     <row r="78" spans="2:9" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B78" s="64" t="s">
+      <c r="B78" s="55" t="s">
         <v>91</v>
       </c>
-      <c r="C78" s="64"/>
-      <c r="D78" s="64"/>
-      <c r="E78" s="64"/>
-      <c r="F78" s="64"/>
-      <c r="G78" s="64"/>
-      <c r="H78" s="64"/>
-      <c r="I78" s="64"/>
+      <c r="C78" s="55"/>
+      <c r="D78" s="55"/>
+      <c r="E78" s="55"/>
+      <c r="F78" s="55"/>
+      <c r="G78" s="55"/>
+      <c r="H78" s="55"/>
+      <c r="I78" s="55"/>
     </row>
     <row r="79" spans="2:9" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B79" s="55" t="s">
+      <c r="B79" s="49" t="s">
         <v>92</v>
       </c>
-      <c r="C79" s="55"/>
-      <c r="D79" s="55"/>
-      <c r="E79" s="55"/>
-      <c r="F79" s="55"/>
-      <c r="G79" s="55"/>
-      <c r="H79" s="55"/>
-      <c r="I79" s="55"/>
+      <c r="C79" s="49"/>
+      <c r="D79" s="49"/>
+      <c r="E79" s="49"/>
+      <c r="F79" s="49"/>
+      <c r="G79" s="49"/>
+      <c r="H79" s="49"/>
+      <c r="I79" s="49"/>
     </row>
     <row r="80" spans="2:9" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B80" s="64" t="s">
+      <c r="B80" s="55" t="s">
         <v>93</v>
       </c>
-      <c r="C80" s="64"/>
-      <c r="D80" s="64"/>
-      <c r="E80" s="64"/>
-      <c r="F80" s="64"/>
-      <c r="G80" s="64"/>
-      <c r="H80" s="64"/>
-      <c r="I80" s="64"/>
+      <c r="C80" s="55"/>
+      <c r="D80" s="55"/>
+      <c r="E80" s="55"/>
+      <c r="F80" s="55"/>
+      <c r="G80" s="55"/>
+      <c r="H80" s="55"/>
+      <c r="I80" s="55"/>
     </row>
     <row r="81" spans="2:9" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B81" s="55" t="s">
+      <c r="B81" s="49" t="s">
         <v>94</v>
       </c>
-      <c r="C81" s="55"/>
-      <c r="D81" s="55"/>
-      <c r="E81" s="55"/>
-      <c r="F81" s="55"/>
-      <c r="G81" s="55"/>
-      <c r="H81" s="55"/>
-      <c r="I81" s="55"/>
+      <c r="C81" s="49"/>
+      <c r="D81" s="49"/>
+      <c r="E81" s="49"/>
+      <c r="F81" s="49"/>
+      <c r="G81" s="49"/>
+      <c r="H81" s="49"/>
+      <c r="I81" s="49"/>
     </row>
     <row r="82" spans="2:9" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B82" s="64" t="s">
+      <c r="B82" s="55" t="s">
         <v>95</v>
       </c>
-      <c r="C82" s="64"/>
-      <c r="D82" s="64"/>
-      <c r="E82" s="64"/>
-      <c r="F82" s="64"/>
-      <c r="G82" s="64"/>
-      <c r="H82" s="64"/>
-      <c r="I82" s="64"/>
+      <c r="C82" s="55"/>
+      <c r="D82" s="55"/>
+      <c r="E82" s="55"/>
+      <c r="F82" s="55"/>
+      <c r="G82" s="55"/>
+      <c r="H82" s="55"/>
+      <c r="I82" s="55"/>
     </row>
     <row r="84" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B84" s="54" t="s">
+      <c r="B84" s="48" t="s">
         <v>2</v>
       </c>
-      <c r="C84" s="54"/>
-      <c r="D84" s="54"/>
-      <c r="E84" s="54"/>
-      <c r="F84" s="54"/>
-      <c r="G84" s="54"/>
-      <c r="H84" s="54"/>
-      <c r="I84" s="54"/>
+      <c r="C84" s="48"/>
+      <c r="D84" s="48"/>
+      <c r="E84" s="48"/>
+      <c r="F84" s="48"/>
+      <c r="G84" s="48"/>
+      <c r="H84" s="48"/>
+      <c r="I84" s="48"/>
     </row>
   </sheetData>
   <mergeCells count="36">
+    <mergeCell ref="B1:I1"/>
+    <mergeCell ref="B3:F3"/>
+    <mergeCell ref="B8:F8"/>
+    <mergeCell ref="B15:F15"/>
+    <mergeCell ref="B20:I20"/>
+    <mergeCell ref="B27:F27"/>
+    <mergeCell ref="B28:F28"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="B30:F30"/>
+    <mergeCell ref="B31:F31"/>
+    <mergeCell ref="B32:I32"/>
+    <mergeCell ref="B41:F41"/>
+    <mergeCell ref="B42:F42"/>
+    <mergeCell ref="B43:F43"/>
+    <mergeCell ref="B44:F44"/>
+    <mergeCell ref="B45:F45"/>
+    <mergeCell ref="B46:I46"/>
+    <mergeCell ref="B55:F55"/>
+    <mergeCell ref="B56:F56"/>
+    <mergeCell ref="B57:F57"/>
+    <mergeCell ref="B58:F58"/>
+    <mergeCell ref="B59:F59"/>
+    <mergeCell ref="B60:I60"/>
+    <mergeCell ref="B65:I65"/>
+    <mergeCell ref="B72:I72"/>
+    <mergeCell ref="B73:I73"/>
+    <mergeCell ref="B74:I74"/>
+    <mergeCell ref="B75:I75"/>
+    <mergeCell ref="B76:I76"/>
+    <mergeCell ref="B77:I77"/>
     <mergeCell ref="B84:I84"/>
     <mergeCell ref="B78:I78"/>
     <mergeCell ref="B79:I79"/>
     <mergeCell ref="B80:I80"/>
     <mergeCell ref="B81:I81"/>
     <mergeCell ref="B82:I82"/>
-    <mergeCell ref="B73:I73"/>
-    <mergeCell ref="B74:I74"/>
-    <mergeCell ref="B75:I75"/>
-    <mergeCell ref="B76:I76"/>
-    <mergeCell ref="B77:I77"/>
-    <mergeCell ref="B58:F58"/>
-    <mergeCell ref="B59:F59"/>
-    <mergeCell ref="B60:I60"/>
-    <mergeCell ref="B65:I65"/>
-    <mergeCell ref="B72:I72"/>
-    <mergeCell ref="B45:F45"/>
-    <mergeCell ref="B46:I46"/>
-    <mergeCell ref="B55:F55"/>
-    <mergeCell ref="B56:F56"/>
-    <mergeCell ref="B57:F57"/>
-    <mergeCell ref="B32:I32"/>
-    <mergeCell ref="B41:F41"/>
-    <mergeCell ref="B42:F42"/>
-    <mergeCell ref="B43:F43"/>
-    <mergeCell ref="B44:F44"/>
-    <mergeCell ref="B27:F27"/>
-    <mergeCell ref="B28:F28"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="B30:F30"/>
-    <mergeCell ref="B31:F31"/>
-    <mergeCell ref="B1:I1"/>
-    <mergeCell ref="B3:F3"/>
-    <mergeCell ref="B8:F8"/>
-    <mergeCell ref="B15:F15"/>
-    <mergeCell ref="B20:I20"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -2791,25 +2784,25 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B1" s="57" t="s">
-        <v>202</v>
-      </c>
-      <c r="C1" s="57"/>
-      <c r="D1" s="57"/>
-      <c r="E1" s="57"/>
-      <c r="F1" s="57"/>
-      <c r="G1" s="57"/>
-      <c r="H1" s="57"/>
-      <c r="I1" s="57"/>
+      <c r="B1" s="61" t="s">
+        <v>197</v>
+      </c>
+      <c r="C1" s="61"/>
+      <c r="D1" s="61"/>
+      <c r="E1" s="61"/>
+      <c r="F1" s="61"/>
+      <c r="G1" s="61"/>
+      <c r="H1" s="61"/>
+      <c r="I1" s="61"/>
     </row>
     <row r="3" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="58" t="s">
-        <v>210</v>
-      </c>
-      <c r="C3" s="58"/>
-      <c r="D3" s="58"/>
-      <c r="E3" s="58"/>
-      <c r="F3" s="58"/>
+      <c r="B3" s="56" t="s">
+        <v>205</v>
+      </c>
+      <c r="C3" s="56"/>
+      <c r="D3" s="56"/>
+      <c r="E3" s="56"/>
+      <c r="F3" s="56"/>
     </row>
     <row r="4" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B4" s="7" t="s">
@@ -2931,16 +2924,16 @@
       </c>
     </row>
     <row r="12" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B12" s="58" t="s">
+      <c r="B12" s="56" t="s">
         <v>102</v>
       </c>
-      <c r="C12" s="58"/>
-      <c r="D12" s="58"/>
-      <c r="E12" s="58"/>
-      <c r="F12" s="58"/>
-      <c r="G12" s="58"/>
-      <c r="H12" s="58"/>
-      <c r="I12" s="58"/>
+      <c r="C12" s="56"/>
+      <c r="D12" s="56"/>
+      <c r="E12" s="56"/>
+      <c r="F12" s="56"/>
+      <c r="G12" s="56"/>
+      <c r="H12" s="56"/>
+      <c r="I12" s="56"/>
     </row>
     <row r="13" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B13" s="7" t="s">
@@ -2961,103 +2954,103 @@
     </row>
     <row r="14" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B14" s="4" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="C14" s="26">
-        <f>C6</f>
-        <v>4569.93</v>
+        <f>C7</f>
+        <v>938.17</v>
       </c>
       <c r="D14" s="26">
-        <f>D6</f>
-        <v>807.53</v>
+        <f>D7</f>
+        <v>969.3</v>
       </c>
       <c r="E14" s="26">
-        <f>E6</f>
-        <v>1027.49</v>
+        <f t="shared" ref="E14:F14" si="0">E7</f>
+        <v>1106.48</v>
       </c>
       <c r="F14" s="26">
-        <f>F6</f>
-        <v>3044.8</v>
+        <f>F7</f>
+        <v>1489.51</v>
       </c>
     </row>
     <row r="15" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B15" s="12" t="s">
-        <v>105</v>
+        <v>207</v>
       </c>
       <c r="C15" s="27">
-        <f>C8</f>
-        <v>5631.44</v>
+        <f>C10</f>
+        <v>230.5</v>
       </c>
       <c r="D15" s="27">
-        <f>D8</f>
-        <v>6479.15</v>
+        <f t="shared" ref="D15:F15" si="1">D10</f>
+        <v>626.29</v>
       </c>
       <c r="E15" s="27">
-        <f>E8</f>
-        <v>7867.28</v>
+        <f t="shared" si="1"/>
+        <v>252.4</v>
       </c>
       <c r="F15" s="27">
-        <f>F8</f>
-        <v>8623.7199999999993</v>
+        <f t="shared" si="1"/>
+        <v>344.87</v>
       </c>
     </row>
     <row r="16" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B16" s="10" t="s">
-        <v>106</v>
+        <v>208</v>
       </c>
       <c r="C16" s="16">
         <f>C14-C15</f>
-        <v>-1061.5099999999993</v>
+        <v>707.67</v>
       </c>
       <c r="D16" s="16">
         <f>D14-D15</f>
-        <v>-5671.62</v>
+        <v>343.01</v>
       </c>
       <c r="E16" s="16">
         <f>E14-E15</f>
-        <v>-6839.79</v>
+        <v>854.08</v>
       </c>
       <c r="F16" s="16">
         <f>F14-F15</f>
-        <v>-5578.9199999999992</v>
+        <v>1144.6399999999999</v>
       </c>
     </row>
     <row r="17" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B17" s="4" t="s">
-        <v>107</v>
+        <v>206</v>
       </c>
       <c r="C17" s="28">
-        <f>C14*365/19381.71</f>
-        <v>86.061779378599738</v>
+        <f>C14*365/'P&amp;L Statement'!C5</f>
+        <v>17.667793502224519</v>
       </c>
       <c r="D17" s="28">
-        <f>D14*365/20281.57</f>
-        <v>14.532822163175732</v>
+        <f>D14*365/'P&amp;L Statement'!D5</f>
+        <v>17.444137707287947</v>
       </c>
       <c r="E17" s="28">
-        <f>E14*365/21732.58</f>
-        <v>17.256756905990912</v>
+        <f>E14*365/'P&amp;L Statement'!E5</f>
+        <v>18.583398749711261</v>
       </c>
       <c r="F17" s="28">
-        <f>F14*365/19869.35</f>
-        <v>55.932982206262416</v>
+        <f>F14*365/'P&amp;L Statement'!F5</f>
+        <v>27.362301736091016</v>
       </c>
     </row>
     <row r="19" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B19" s="58" t="s">
-        <v>108</v>
-      </c>
-      <c r="C19" s="58"/>
-      <c r="D19" s="58"/>
-      <c r="E19" s="58"/>
-      <c r="F19" s="58"/>
-      <c r="G19" s="58"/>
-      <c r="H19" s="58"/>
-      <c r="I19" s="58"/>
+      <c r="B19" s="56" t="s">
+        <v>104</v>
+      </c>
+      <c r="C19" s="56"/>
+      <c r="D19" s="56"/>
+      <c r="E19" s="56"/>
+      <c r="F19" s="56"/>
+      <c r="G19" s="56"/>
+      <c r="H19" s="56"/>
+      <c r="I19" s="56"/>
     </row>
     <row r="20" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B20" s="7" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="C20" s="8" t="s">
         <v>28</v>
@@ -3074,137 +3067,137 @@
     </row>
     <row r="21" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B21" s="4" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="C21" s="29">
-        <f>C7/C6</f>
-        <v>0.20529198477876026</v>
+        <f>C9/C8</f>
+        <v>1.1214573892290427</v>
       </c>
       <c r="D21" s="29">
-        <f>D7/D6</f>
-        <v>1.2003269228387801</v>
+        <f t="shared" ref="D21:F21" si="2">D9/D8</f>
+        <v>0.9307671530987861</v>
       </c>
       <c r="E21" s="29">
-        <f>E7/E6</f>
-        <v>1.0768766606001032</v>
+        <f t="shared" si="2"/>
+        <v>0.70110254115780812</v>
       </c>
       <c r="F21" s="29">
-        <f>F7/F6</f>
-        <v>0.48919797687861266</v>
+        <f t="shared" si="2"/>
+        <v>0.56698385383569971</v>
       </c>
     </row>
     <row r="22" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B22" s="12" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="C22" s="30">
-        <f>C5/C6</f>
-        <v>4.2405660480576284</v>
+        <f>C5/C8</f>
+        <v>3.4412317275865503</v>
       </c>
       <c r="D22" s="30">
-        <f>D5/D6</f>
-        <v>21.771884635864922</v>
+        <f t="shared" ref="D22:F22" si="3">D5/D8</f>
+        <v>2.7135426714924029</v>
       </c>
       <c r="E22" s="30">
-        <f>E5/E6</f>
-        <v>18.232323428938479</v>
+        <f t="shared" si="3"/>
+        <v>2.3811952796900582</v>
       </c>
       <c r="F22" s="30">
-        <f>F5/F6</f>
-        <v>6.3992774566473987</v>
+        <f t="shared" si="3"/>
+        <v>2.2594100921644027</v>
       </c>
     </row>
     <row r="23" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B23" s="4" t="s">
-        <v>112</v>
-      </c>
-      <c r="C23" s="31" t="s">
-        <v>113</v>
-      </c>
-      <c r="D23" s="32">
+        <v>108</v>
+      </c>
+      <c r="C23" s="65">
+        <v>2.0699999999999998</v>
+      </c>
+      <c r="D23" s="31">
         <v>2.02</v>
       </c>
-      <c r="E23" s="32">
+      <c r="E23" s="31">
         <v>2.11</v>
       </c>
-      <c r="F23" s="32">
+      <c r="F23" s="31">
         <v>2.0499999999999998</v>
       </c>
     </row>
     <row r="24" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B24" s="12" t="s">
-        <v>114</v>
-      </c>
-      <c r="C24" s="33" t="s">
-        <v>113</v>
-      </c>
-      <c r="D24" s="34">
+        <v>109</v>
+      </c>
+      <c r="C24" s="66">
+        <v>1.17</v>
+      </c>
+      <c r="D24" s="32">
         <v>0.99</v>
       </c>
-      <c r="E24" s="34">
+      <c r="E24" s="32">
         <v>0.76</v>
       </c>
-      <c r="F24" s="34">
+      <c r="F24" s="32">
         <v>0.62</v>
       </c>
     </row>
     <row r="25" spans="2:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="26" spans="2:9" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B26" s="60" t="s">
+      <c r="B26" s="57" t="s">
+        <v>110</v>
+      </c>
+      <c r="C26" s="58"/>
+      <c r="D26" s="58"/>
+      <c r="E26" s="58"/>
+      <c r="F26" s="59"/>
+    </row>
+    <row r="27" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B27" s="63" t="s">
+        <v>111</v>
+      </c>
+      <c r="C27" s="63"/>
+      <c r="D27" s="63"/>
+      <c r="E27" s="63"/>
+      <c r="F27" s="63"/>
+    </row>
+    <row r="28" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B28" s="50" t="s">
+        <v>112</v>
+      </c>
+      <c r="C28" s="50"/>
+      <c r="D28" s="50"/>
+      <c r="E28" s="50"/>
+      <c r="F28" s="50"/>
+    </row>
+    <row r="29" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B29" s="49" t="s">
+        <v>113</v>
+      </c>
+      <c r="C29" s="49"/>
+      <c r="D29" s="49"/>
+      <c r="E29" s="49"/>
+      <c r="F29" s="49"/>
+    </row>
+    <row r="30" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B30" s="50" t="s">
+        <v>114</v>
+      </c>
+      <c r="C30" s="50"/>
+      <c r="D30" s="50"/>
+      <c r="E30" s="50"/>
+      <c r="F30" s="50"/>
+    </row>
+    <row r="31" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B31" s="56" t="s">
         <v>115</v>
       </c>
-      <c r="C26" s="61"/>
-      <c r="D26" s="61"/>
-      <c r="E26" s="61"/>
-      <c r="F26" s="62"/>
-    </row>
-    <row r="27" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B27" s="65" t="s">
-        <v>116</v>
-      </c>
-      <c r="C27" s="65"/>
-      <c r="D27" s="65"/>
-      <c r="E27" s="65"/>
-      <c r="F27" s="65"/>
-    </row>
-    <row r="28" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B28" s="56" t="s">
-        <v>117</v>
-      </c>
-      <c r="C28" s="56"/>
-      <c r="D28" s="56"/>
-      <c r="E28" s="56"/>
-      <c r="F28" s="56"/>
-    </row>
-    <row r="29" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B29" s="55" t="s">
-        <v>118</v>
-      </c>
-      <c r="C29" s="55"/>
-      <c r="D29" s="55"/>
-      <c r="E29" s="55"/>
-      <c r="F29" s="55"/>
-    </row>
-    <row r="30" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B30" s="56" t="s">
-        <v>119</v>
-      </c>
-      <c r="C30" s="56"/>
-      <c r="D30" s="56"/>
-      <c r="E30" s="56"/>
-      <c r="F30" s="56"/>
-    </row>
-    <row r="31" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B31" s="58" t="s">
-        <v>120</v>
-      </c>
-      <c r="C31" s="58"/>
-      <c r="D31" s="58"/>
-      <c r="E31" s="58"/>
-      <c r="F31" s="58"/>
-      <c r="G31" s="58"/>
-      <c r="H31" s="58"/>
-      <c r="I31" s="58"/>
+      <c r="C31" s="56"/>
+      <c r="D31" s="56"/>
+      <c r="E31" s="56"/>
+      <c r="F31" s="56"/>
+      <c r="G31" s="56"/>
+      <c r="H31" s="56"/>
+      <c r="I31" s="56"/>
     </row>
     <row r="32" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B32" s="7" t="s">
@@ -3222,7 +3215,7 @@
     </row>
     <row r="33" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B33" s="20" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="C33" s="21">
         <v>0.09</v>
@@ -3236,7 +3229,7 @@
     </row>
     <row r="34" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B34" s="20" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="C34" s="11">
         <v>300</v>
@@ -3250,7 +3243,7 @@
     </row>
     <row r="35" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B35" s="20" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="C35" s="21">
         <v>0.08</v>
@@ -3263,16 +3256,16 @@
       </c>
     </row>
     <row r="36" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B36" s="58" t="s">
-        <v>124</v>
-      </c>
-      <c r="C36" s="58"/>
-      <c r="D36" s="58"/>
-      <c r="E36" s="58"/>
-      <c r="F36" s="58"/>
-      <c r="G36" s="58"/>
-      <c r="H36" s="58"/>
-      <c r="I36" s="58"/>
+      <c r="B36" s="56" t="s">
+        <v>119</v>
+      </c>
+      <c r="C36" s="56"/>
+      <c r="D36" s="56"/>
+      <c r="E36" s="56"/>
+      <c r="F36" s="56"/>
+      <c r="G36" s="56"/>
+      <c r="H36" s="56"/>
+      <c r="I36" s="56"/>
     </row>
     <row r="37" spans="2:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B37" s="7" t="s">
@@ -3361,79 +3354,89 @@
       </c>
     </row>
     <row r="42" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B42" s="58" t="s">
-        <v>125</v>
-      </c>
-      <c r="C42" s="58"/>
-      <c r="D42" s="58"/>
-      <c r="E42" s="58"/>
-      <c r="F42" s="58"/>
-      <c r="G42" s="58"/>
-      <c r="H42" s="58"/>
-      <c r="I42" s="58"/>
+      <c r="B42" s="56" t="s">
+        <v>120</v>
+      </c>
+      <c r="C42" s="56"/>
+      <c r="D42" s="56"/>
+      <c r="E42" s="56"/>
+      <c r="F42" s="56"/>
+      <c r="G42" s="56"/>
+      <c r="H42" s="56"/>
+      <c r="I42" s="56"/>
     </row>
     <row r="43" spans="2:9" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B43" s="55" t="s">
-        <v>126</v>
-      </c>
-      <c r="C43" s="55"/>
-      <c r="D43" s="55"/>
-      <c r="E43" s="55"/>
-      <c r="F43" s="55"/>
-      <c r="G43" s="55"/>
-      <c r="H43" s="55"/>
-      <c r="I43" s="55"/>
+      <c r="B43" s="49" t="s">
+        <v>121</v>
+      </c>
+      <c r="C43" s="49"/>
+      <c r="D43" s="49"/>
+      <c r="E43" s="49"/>
+      <c r="F43" s="49"/>
+      <c r="G43" s="49"/>
+      <c r="H43" s="49"/>
+      <c r="I43" s="49"/>
     </row>
     <row r="44" spans="2:9" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B44" s="64" t="s">
-        <v>127</v>
-      </c>
-      <c r="C44" s="64"/>
-      <c r="D44" s="64"/>
-      <c r="E44" s="64"/>
-      <c r="F44" s="64"/>
-      <c r="G44" s="64"/>
-      <c r="H44" s="64"/>
-      <c r="I44" s="64"/>
+      <c r="B44" s="55" t="s">
+        <v>122</v>
+      </c>
+      <c r="C44" s="55"/>
+      <c r="D44" s="55"/>
+      <c r="E44" s="55"/>
+      <c r="F44" s="55"/>
+      <c r="G44" s="55"/>
+      <c r="H44" s="55"/>
+      <c r="I44" s="55"/>
     </row>
     <row r="45" spans="2:9" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B45" s="55" t="s">
-        <v>128</v>
-      </c>
-      <c r="C45" s="55"/>
-      <c r="D45" s="55"/>
-      <c r="E45" s="55"/>
-      <c r="F45" s="55"/>
-      <c r="G45" s="55"/>
-      <c r="H45" s="55"/>
-      <c r="I45" s="55"/>
+      <c r="B45" s="49" t="s">
+        <v>123</v>
+      </c>
+      <c r="C45" s="49"/>
+      <c r="D45" s="49"/>
+      <c r="E45" s="49"/>
+      <c r="F45" s="49"/>
+      <c r="G45" s="49"/>
+      <c r="H45" s="49"/>
+      <c r="I45" s="49"/>
     </row>
     <row r="46" spans="2:9" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B46" s="64" t="s">
-        <v>129</v>
-      </c>
-      <c r="C46" s="64"/>
-      <c r="D46" s="64"/>
-      <c r="E46" s="64"/>
-      <c r="F46" s="64"/>
-      <c r="G46" s="64"/>
-      <c r="H46" s="64"/>
-      <c r="I46" s="64"/>
+      <c r="B46" s="55" t="s">
+        <v>124</v>
+      </c>
+      <c r="C46" s="55"/>
+      <c r="D46" s="55"/>
+      <c r="E46" s="55"/>
+      <c r="F46" s="55"/>
+      <c r="G46" s="55"/>
+      <c r="H46" s="55"/>
+      <c r="I46" s="55"/>
     </row>
     <row r="48" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B48" s="54" t="s">
+      <c r="B48" s="48" t="s">
         <v>2</v>
       </c>
-      <c r="C48" s="54"/>
-      <c r="D48" s="54"/>
-      <c r="E48" s="54"/>
-      <c r="F48" s="54"/>
-      <c r="G48" s="54"/>
-      <c r="H48" s="54"/>
-      <c r="I48" s="54"/>
+      <c r="C48" s="48"/>
+      <c r="D48" s="48"/>
+      <c r="E48" s="48"/>
+      <c r="F48" s="48"/>
+      <c r="G48" s="48"/>
+      <c r="H48" s="48"/>
+      <c r="I48" s="48"/>
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="B1:I1"/>
+    <mergeCell ref="B3:F3"/>
+    <mergeCell ref="B12:I12"/>
+    <mergeCell ref="B19:I19"/>
+    <mergeCell ref="B26:F26"/>
+    <mergeCell ref="B27:F27"/>
+    <mergeCell ref="B28:F28"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="B30:F30"/>
+    <mergeCell ref="B31:I31"/>
     <mergeCell ref="B46:I46"/>
     <mergeCell ref="B48:I48"/>
     <mergeCell ref="B36:I36"/>
@@ -3441,19 +3444,9 @@
     <mergeCell ref="B43:I43"/>
     <mergeCell ref="B44:I44"/>
     <mergeCell ref="B45:I45"/>
-    <mergeCell ref="B27:F27"/>
-    <mergeCell ref="B28:F28"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="B30:F30"/>
-    <mergeCell ref="B31:I31"/>
-    <mergeCell ref="B1:I1"/>
-    <mergeCell ref="B3:F3"/>
-    <mergeCell ref="B12:I12"/>
-    <mergeCell ref="B19:I19"/>
-    <mergeCell ref="B26:F26"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -3471,25 +3464,25 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B1" s="57" t="s">
-        <v>130</v>
-      </c>
-      <c r="C1" s="57"/>
-      <c r="D1" s="57"/>
-      <c r="E1" s="57"/>
-      <c r="F1" s="57"/>
-      <c r="G1" s="57"/>
-      <c r="H1" s="57"/>
-      <c r="I1" s="57"/>
+      <c r="B1" s="61" t="s">
+        <v>125</v>
+      </c>
+      <c r="C1" s="61"/>
+      <c r="D1" s="61"/>
+      <c r="E1" s="61"/>
+      <c r="F1" s="61"/>
+      <c r="G1" s="61"/>
+      <c r="H1" s="61"/>
+      <c r="I1" s="61"/>
     </row>
     <row r="3" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="58" t="s">
-        <v>131</v>
-      </c>
-      <c r="C3" s="58"/>
-      <c r="D3" s="58"/>
-      <c r="E3" s="58"/>
-      <c r="F3" s="58"/>
+      <c r="B3" s="56" t="s">
+        <v>126</v>
+      </c>
+      <c r="C3" s="56"/>
+      <c r="D3" s="56"/>
+      <c r="E3" s="56"/>
+      <c r="F3" s="56"/>
     </row>
     <row r="4" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B4" s="7" t="s">
@@ -3510,7 +3503,7 @@
     </row>
     <row r="5" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B5" s="10" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="C5" s="11">
         <v>4806.17</v>
@@ -3527,7 +3520,7 @@
     </row>
     <row r="6" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B6" s="4" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="C6" s="9">
         <v>-1462.83</v>
@@ -3544,7 +3537,7 @@
     </row>
     <row r="7" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B7" s="12" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="C7" s="13">
         <v>-189.36</v>
@@ -3561,7 +3554,7 @@
     </row>
     <row r="8" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B8" s="14" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="C8" s="25">
         <f>C5+C6+C7</f>
@@ -3582,7 +3575,7 @@
     </row>
     <row r="9" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B9" s="14" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="C9" s="15">
         <v>4569.93</v>
@@ -3598,16 +3591,16 @@
       </c>
     </row>
     <row r="11" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B11" s="58" t="s">
-        <v>209</v>
-      </c>
-      <c r="C11" s="58"/>
-      <c r="D11" s="58"/>
-      <c r="E11" s="58"/>
-      <c r="F11" s="58"/>
-      <c r="G11" s="58"/>
-      <c r="H11" s="58"/>
-      <c r="I11" s="58"/>
+      <c r="B11" s="56" t="s">
+        <v>204</v>
+      </c>
+      <c r="C11" s="56"/>
+      <c r="D11" s="56"/>
+      <c r="E11" s="56"/>
+      <c r="F11" s="56"/>
+      <c r="G11" s="56"/>
+      <c r="H11" s="56"/>
+      <c r="I11" s="56"/>
     </row>
     <row r="12" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B12" s="7" t="s">
@@ -3645,7 +3638,7 @@
     </row>
     <row r="14" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B14" s="12" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="C14" s="13">
         <v>4806.17</v>
@@ -3662,7 +3655,7 @@
     </row>
     <row r="15" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B15" s="10" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="C15" s="16">
         <f>C14-C13</f>
@@ -3683,7 +3676,7 @@
     </row>
     <row r="16" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B16" s="4" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="C16" s="29">
         <f>C14/C13</f>
@@ -3704,70 +3697,70 @@
     </row>
     <row r="17" spans="2:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="18" spans="2:9" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B18" s="60" t="s">
+      <c r="B18" s="57" t="s">
+        <v>135</v>
+      </c>
+      <c r="C18" s="58"/>
+      <c r="D18" s="58"/>
+      <c r="E18" s="58"/>
+      <c r="F18" s="59"/>
+    </row>
+    <row r="19" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B19" s="63" t="s">
+        <v>136</v>
+      </c>
+      <c r="C19" s="63"/>
+      <c r="D19" s="63"/>
+      <c r="E19" s="63"/>
+      <c r="F19" s="63"/>
+    </row>
+    <row r="20" spans="2:9" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B20" s="50" t="s">
+        <v>137</v>
+      </c>
+      <c r="C20" s="50"/>
+      <c r="D20" s="50"/>
+      <c r="E20" s="50"/>
+      <c r="F20" s="50"/>
+    </row>
+    <row r="21" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B21" s="49" t="s">
+        <v>138</v>
+      </c>
+      <c r="C21" s="49"/>
+      <c r="D21" s="49"/>
+      <c r="E21" s="49"/>
+      <c r="F21" s="49"/>
+    </row>
+    <row r="22" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B22" s="50" t="s">
+        <v>139</v>
+      </c>
+      <c r="C22" s="50"/>
+      <c r="D22" s="50"/>
+      <c r="E22" s="50"/>
+      <c r="F22" s="50"/>
+    </row>
+    <row r="23" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B23" s="49" t="s">
         <v>140</v>
       </c>
-      <c r="C18" s="61"/>
-      <c r="D18" s="61"/>
-      <c r="E18" s="61"/>
-      <c r="F18" s="62"/>
-    </row>
-    <row r="19" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B19" s="65" t="s">
-        <v>141</v>
-      </c>
-      <c r="C19" s="65"/>
-      <c r="D19" s="65"/>
-      <c r="E19" s="65"/>
-      <c r="F19" s="65"/>
-    </row>
-    <row r="20" spans="2:9" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B20" s="56" t="s">
-        <v>142</v>
-      </c>
-      <c r="C20" s="56"/>
-      <c r="D20" s="56"/>
-      <c r="E20" s="56"/>
-      <c r="F20" s="56"/>
-    </row>
-    <row r="21" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B21" s="55" t="s">
-        <v>143</v>
-      </c>
-      <c r="C21" s="55"/>
-      <c r="D21" s="55"/>
-      <c r="E21" s="55"/>
-      <c r="F21" s="55"/>
-    </row>
-    <row r="22" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B22" s="56" t="s">
-        <v>144</v>
-      </c>
-      <c r="C22" s="56"/>
-      <c r="D22" s="56"/>
-      <c r="E22" s="56"/>
-      <c r="F22" s="56"/>
-    </row>
-    <row r="23" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B23" s="55" t="s">
-        <v>145</v>
-      </c>
-      <c r="C23" s="55"/>
-      <c r="D23" s="55"/>
-      <c r="E23" s="55"/>
-      <c r="F23" s="55"/>
+      <c r="C23" s="49"/>
+      <c r="D23" s="49"/>
+      <c r="E23" s="49"/>
+      <c r="F23" s="49"/>
     </row>
     <row r="24" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B24" s="58" t="s">
-        <v>207</v>
-      </c>
-      <c r="C24" s="58"/>
-      <c r="D24" s="58"/>
-      <c r="E24" s="58"/>
-      <c r="F24" s="58"/>
-      <c r="G24" s="58"/>
-      <c r="H24" s="58"/>
-      <c r="I24" s="58"/>
+      <c r="B24" s="56" t="s">
+        <v>202</v>
+      </c>
+      <c r="C24" s="56"/>
+      <c r="D24" s="56"/>
+      <c r="E24" s="56"/>
+      <c r="F24" s="56"/>
+      <c r="G24" s="56"/>
+      <c r="H24" s="56"/>
+      <c r="I24" s="56"/>
     </row>
     <row r="25" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B25" s="7" t="s">
@@ -3785,7 +3778,7 @@
     </row>
     <row r="26" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B26" s="20" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="C26" s="11">
         <v>1350</v>
@@ -3799,21 +3792,21 @@
     </row>
     <row r="27" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B27" s="20" t="s">
-        <v>147</v>
-      </c>
-      <c r="C27" s="35">
+        <v>142</v>
+      </c>
+      <c r="C27" s="33">
         <v>1.2</v>
       </c>
-      <c r="D27" s="35">
+      <c r="D27" s="33">
         <v>1.3</v>
       </c>
-      <c r="E27" s="35">
+      <c r="E27" s="33">
         <v>1.4</v>
       </c>
     </row>
     <row r="28" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B28" s="20" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="C28" s="11">
         <v>-1500</v>
@@ -3826,16 +3819,16 @@
       </c>
     </row>
     <row r="29" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B29" s="58" t="s">
-        <v>208</v>
-      </c>
-      <c r="C29" s="58"/>
-      <c r="D29" s="58"/>
-      <c r="E29" s="58"/>
-      <c r="F29" s="58"/>
-      <c r="G29" s="58"/>
-      <c r="H29" s="58"/>
-      <c r="I29" s="58"/>
+      <c r="B29" s="56" t="s">
+        <v>203</v>
+      </c>
+      <c r="C29" s="56"/>
+      <c r="D29" s="56"/>
+      <c r="E29" s="56"/>
+      <c r="F29" s="56"/>
+      <c r="G29" s="56"/>
+      <c r="H29" s="56"/>
+      <c r="I29" s="56"/>
     </row>
     <row r="30" spans="2:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B30" s="7" t="s">
@@ -3924,91 +3917,101 @@
       </c>
     </row>
     <row r="35" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B35" s="58" t="s">
+      <c r="B35" s="56" t="s">
+        <v>144</v>
+      </c>
+      <c r="C35" s="56"/>
+      <c r="D35" s="56"/>
+      <c r="E35" s="56"/>
+      <c r="F35" s="56"/>
+      <c r="G35" s="56"/>
+      <c r="H35" s="56"/>
+      <c r="I35" s="56"/>
+    </row>
+    <row r="36" spans="2:9" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B36" s="55" t="s">
+        <v>145</v>
+      </c>
+      <c r="C36" s="55"/>
+      <c r="D36" s="55"/>
+      <c r="E36" s="55"/>
+      <c r="F36" s="55"/>
+      <c r="G36" s="55"/>
+      <c r="H36" s="55"/>
+      <c r="I36" s="55"/>
+    </row>
+    <row r="37" spans="2:9" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B37" s="49" t="s">
+        <v>146</v>
+      </c>
+      <c r="C37" s="49"/>
+      <c r="D37" s="49"/>
+      <c r="E37" s="49"/>
+      <c r="F37" s="49"/>
+      <c r="G37" s="49"/>
+      <c r="H37" s="49"/>
+      <c r="I37" s="49"/>
+    </row>
+    <row r="38" spans="2:9" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B38" s="55" t="s">
+        <v>147</v>
+      </c>
+      <c r="C38" s="55"/>
+      <c r="D38" s="55"/>
+      <c r="E38" s="55"/>
+      <c r="F38" s="55"/>
+      <c r="G38" s="55"/>
+      <c r="H38" s="55"/>
+      <c r="I38" s="55"/>
+    </row>
+    <row r="39" spans="2:9" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B39" s="49" t="s">
+        <v>148</v>
+      </c>
+      <c r="C39" s="49"/>
+      <c r="D39" s="49"/>
+      <c r="E39" s="49"/>
+      <c r="F39" s="49"/>
+      <c r="G39" s="49"/>
+      <c r="H39" s="49"/>
+      <c r="I39" s="49"/>
+    </row>
+    <row r="40" spans="2:9" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B40" s="55" t="s">
         <v>149</v>
       </c>
-      <c r="C35" s="58"/>
-      <c r="D35" s="58"/>
-      <c r="E35" s="58"/>
-      <c r="F35" s="58"/>
-      <c r="G35" s="58"/>
-      <c r="H35" s="58"/>
-      <c r="I35" s="58"/>
-    </row>
-    <row r="36" spans="2:9" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B36" s="64" t="s">
-        <v>150</v>
-      </c>
-      <c r="C36" s="64"/>
-      <c r="D36" s="64"/>
-      <c r="E36" s="64"/>
-      <c r="F36" s="64"/>
-      <c r="G36" s="64"/>
-      <c r="H36" s="64"/>
-      <c r="I36" s="64"/>
-    </row>
-    <row r="37" spans="2:9" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B37" s="55" t="s">
-        <v>151</v>
-      </c>
-      <c r="C37" s="55"/>
-      <c r="D37" s="55"/>
-      <c r="E37" s="55"/>
-      <c r="F37" s="55"/>
-      <c r="G37" s="55"/>
-      <c r="H37" s="55"/>
-      <c r="I37" s="55"/>
-    </row>
-    <row r="38" spans="2:9" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B38" s="64" t="s">
-        <v>152</v>
-      </c>
-      <c r="C38" s="64"/>
-      <c r="D38" s="64"/>
-      <c r="E38" s="64"/>
-      <c r="F38" s="64"/>
-      <c r="G38" s="64"/>
-      <c r="H38" s="64"/>
-      <c r="I38" s="64"/>
-    </row>
-    <row r="39" spans="2:9" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B39" s="55" t="s">
-        <v>153</v>
-      </c>
-      <c r="C39" s="55"/>
-      <c r="D39" s="55"/>
-      <c r="E39" s="55"/>
-      <c r="F39" s="55"/>
-      <c r="G39" s="55"/>
-      <c r="H39" s="55"/>
-      <c r="I39" s="55"/>
-    </row>
-    <row r="40" spans="2:9" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B40" s="64" t="s">
-        <v>154</v>
-      </c>
-      <c r="C40" s="64"/>
-      <c r="D40" s="64"/>
-      <c r="E40" s="64"/>
-      <c r="F40" s="64"/>
-      <c r="G40" s="64"/>
-      <c r="H40" s="64"/>
-      <c r="I40" s="64"/>
+      <c r="C40" s="55"/>
+      <c r="D40" s="55"/>
+      <c r="E40" s="55"/>
+      <c r="F40" s="55"/>
+      <c r="G40" s="55"/>
+      <c r="H40" s="55"/>
+      <c r="I40" s="55"/>
     </row>
     <row r="42" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B42" s="54" t="s">
+      <c r="B42" s="48" t="s">
         <v>2</v>
       </c>
-      <c r="C42" s="54"/>
-      <c r="D42" s="54"/>
-      <c r="E42" s="54"/>
-      <c r="F42" s="54"/>
-      <c r="G42" s="54"/>
-      <c r="H42" s="54"/>
-      <c r="I42" s="54"/>
+      <c r="C42" s="48"/>
+      <c r="D42" s="48"/>
+      <c r="E42" s="48"/>
+      <c r="F42" s="48"/>
+      <c r="G42" s="48"/>
+      <c r="H42" s="48"/>
+      <c r="I42" s="48"/>
     </row>
   </sheetData>
   <mergeCells count="18">
+    <mergeCell ref="B1:I1"/>
+    <mergeCell ref="B3:F3"/>
+    <mergeCell ref="B11:I11"/>
+    <mergeCell ref="B18:F18"/>
+    <mergeCell ref="B19:F19"/>
+    <mergeCell ref="B20:F20"/>
+    <mergeCell ref="B21:F21"/>
+    <mergeCell ref="B22:F22"/>
+    <mergeCell ref="B23:F23"/>
+    <mergeCell ref="B24:I24"/>
     <mergeCell ref="B39:I39"/>
     <mergeCell ref="B40:I40"/>
     <mergeCell ref="B42:I42"/>
@@ -4017,16 +4020,6 @@
     <mergeCell ref="B36:I36"/>
     <mergeCell ref="B37:I37"/>
     <mergeCell ref="B38:I38"/>
-    <mergeCell ref="B20:F20"/>
-    <mergeCell ref="B21:F21"/>
-    <mergeCell ref="B22:F22"/>
-    <mergeCell ref="B23:F23"/>
-    <mergeCell ref="B24:I24"/>
-    <mergeCell ref="B1:I1"/>
-    <mergeCell ref="B3:F3"/>
-    <mergeCell ref="B11:I11"/>
-    <mergeCell ref="B18:F18"/>
-    <mergeCell ref="B19:F19"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -4044,26 +4037,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="57" t="s">
-        <v>206</v>
-      </c>
-      <c r="B1" s="57"/>
-      <c r="C1" s="57"/>
-      <c r="D1" s="57"/>
-      <c r="E1" s="57"/>
+      <c r="A1" s="61" t="s">
+        <v>201</v>
+      </c>
+      <c r="B1" s="61"/>
+      <c r="C1" s="61"/>
+      <c r="D1" s="61"/>
+      <c r="E1" s="61"/>
     </row>
     <row r="2" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="66" t="s">
-        <v>203</v>
-      </c>
-      <c r="B2" s="66"/>
-      <c r="C2" s="66"/>
-      <c r="D2" s="66"/>
-      <c r="E2" s="66"/>
+      <c r="A2" s="64" t="s">
+        <v>198</v>
+      </c>
+      <c r="B2" s="64"/>
+      <c r="C2" s="64"/>
+      <c r="D2" s="64"/>
+      <c r="E2" s="64"/>
     </row>
     <row r="4" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="7" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="B4" s="8" t="s">
         <v>28</v>
@@ -4079,13 +4072,13 @@
       </c>
     </row>
     <row r="5" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="36" t="s">
-        <v>156</v>
-      </c>
-      <c r="B5" s="37"/>
-      <c r="C5" s="37"/>
-      <c r="D5" s="37"/>
-      <c r="E5" s="37"/>
+      <c r="A5" s="34" t="s">
+        <v>151</v>
+      </c>
+      <c r="B5" s="35"/>
+      <c r="C5" s="35"/>
+      <c r="D5" s="35"/>
+      <c r="E5" s="35"/>
     </row>
     <row r="6" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="12" t="s">
@@ -4139,13 +4132,13 @@
       </c>
     </row>
     <row r="10" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="36" t="s">
+      <c r="A10" s="34" t="s">
         <v>35</v>
       </c>
-      <c r="B10" s="37"/>
-      <c r="C10" s="37"/>
-      <c r="D10" s="37"/>
-      <c r="E10" s="37"/>
+      <c r="B10" s="35"/>
+      <c r="C10" s="35"/>
+      <c r="D10" s="35"/>
+      <c r="E10" s="35"/>
     </row>
     <row r="11" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
@@ -4250,17 +4243,17 @@
       </c>
     </row>
     <row r="18" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="36" t="s">
+      <c r="A18" s="34" t="s">
         <v>42</v>
       </c>
-      <c r="B18" s="37"/>
-      <c r="C18" s="37"/>
-      <c r="D18" s="37"/>
-      <c r="E18" s="37"/>
+      <c r="B18" s="35"/>
+      <c r="C18" s="35"/>
+      <c r="D18" s="35"/>
+      <c r="E18" s="35"/>
     </row>
     <row r="19" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="B19" s="9">
         <v>1406.24</v>
@@ -4310,17 +4303,17 @@
       </c>
     </row>
     <row r="23" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="36" t="s">
-        <v>158</v>
-      </c>
-      <c r="B23" s="37"/>
-      <c r="C23" s="37"/>
-      <c r="D23" s="37"/>
-      <c r="E23" s="37"/>
+      <c r="A23" s="34" t="s">
+        <v>153</v>
+      </c>
+      <c r="B23" s="35"/>
+      <c r="C23" s="35"/>
+      <c r="D23" s="35"/>
+      <c r="E23" s="35"/>
     </row>
     <row r="24" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="10" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
       <c r="B24" s="11">
         <v>19379.09</v>
@@ -4421,17 +4414,17 @@
       </c>
     </row>
     <row r="31" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="36" t="s">
-        <v>160</v>
-      </c>
-      <c r="B31" s="37"/>
-      <c r="C31" s="37"/>
-      <c r="D31" s="37"/>
-      <c r="E31" s="37"/>
+      <c r="A31" s="34" t="s">
+        <v>155</v>
+      </c>
+      <c r="B31" s="35"/>
+      <c r="C31" s="35"/>
+      <c r="D31" s="35"/>
+      <c r="E31" s="35"/>
     </row>
     <row r="32" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="12" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="B32" s="13">
         <v>4806.17</v>
@@ -4448,7 +4441,7 @@
     </row>
     <row r="33" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="4" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="B33" s="9">
         <v>-1462.83</v>
@@ -4465,7 +4458,7 @@
     </row>
     <row r="34" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="12" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="B34" s="13">
         <v>-189.36</v>
@@ -4482,7 +4475,7 @@
     </row>
     <row r="35" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="4" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="B35" s="9">
         <v>4569.93</v>
@@ -4498,17 +4491,17 @@
       </c>
     </row>
     <row r="37" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="38" t="s">
-        <v>161</v>
+      <c r="A37" s="36" t="s">
+        <v>156</v>
       </c>
     </row>
     <row r="39" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B39" s="54" t="s">
+      <c r="B39" s="48" t="s">
         <v>2</v>
       </c>
-      <c r="C39" s="54"/>
-      <c r="D39" s="54"/>
-      <c r="E39" s="54"/>
+      <c r="C39" s="48"/>
+      <c r="D39" s="48"/>
+      <c r="E39" s="48"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -4532,192 +4525,192 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:2" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B1" s="39" t="s">
-        <v>204</v>
+      <c r="B1" s="37" t="s">
+        <v>199</v>
       </c>
     </row>
     <row r="2" spans="2:2" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="40" t="s">
+      <c r="B2" s="38" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="4" spans="2:2" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B4" s="39" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="5" spans="2:2" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B5" s="40" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="6" spans="2:2" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B6" s="41" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="7" spans="2:2" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B7" s="40" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="8" spans="2:2" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B8" s="41" t="s">
         <v>162</v>
       </c>
     </row>
-    <row r="4" spans="2:2" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B4" s="41" t="s">
+    <row r="10" spans="2:2" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B10" s="39" t="s">
         <v>163</v>
       </c>
     </row>
-    <row r="5" spans="2:2" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="42" t="s">
+    <row r="11" spans="2:2" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B11" s="40" t="s">
         <v>164</v>
       </c>
     </row>
-    <row r="6" spans="2:2" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="43" t="s">
+    <row r="12" spans="2:2" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B12" s="41" t="s">
         <v>165</v>
       </c>
     </row>
-    <row r="7" spans="2:2" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B7" s="42" t="s">
+    <row r="13" spans="2:2" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B13" s="40" t="s">
         <v>166</v>
       </c>
     </row>
-    <row r="8" spans="2:2" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B8" s="43" t="s">
+    <row r="14" spans="2:2" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B14" s="41" t="s">
         <v>167</v>
       </c>
     </row>
-    <row r="10" spans="2:2" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B10" s="41" t="s">
+    <row r="16" spans="2:2" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B16" s="39" t="s">
         <v>168</v>
       </c>
     </row>
-    <row r="11" spans="2:2" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B11" s="42" t="s">
+    <row r="17" spans="2:2" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B17" s="40" t="s">
         <v>169</v>
       </c>
     </row>
-    <row r="12" spans="2:2" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B12" s="43" t="s">
+    <row r="18" spans="2:2" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B18" s="41" t="s">
         <v>170</v>
       </c>
     </row>
-    <row r="13" spans="2:2" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B13" s="42" t="s">
+    <row r="19" spans="2:2" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B19" s="40" t="s">
         <v>171</v>
       </c>
     </row>
-    <row r="14" spans="2:2" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B14" s="43" t="s">
+    <row r="20" spans="2:2" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B20" s="41" t="s">
         <v>172</v>
       </c>
     </row>
-    <row r="16" spans="2:2" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B16" s="41" t="s">
+    <row r="22" spans="2:2" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B22" s="39" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="17" spans="2:2" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B17" s="42" t="s">
+    <row r="23" spans="2:2" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B23" s="40" t="s">
         <v>174</v>
       </c>
     </row>
-    <row r="18" spans="2:2" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B18" s="43" t="s">
+    <row r="24" spans="2:2" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B24" s="41" t="s">
         <v>175</v>
       </c>
     </row>
-    <row r="19" spans="2:2" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B19" s="42" t="s">
+    <row r="25" spans="2:2" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B25" s="40" t="s">
         <v>176</v>
       </c>
     </row>
-    <row r="20" spans="2:2" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B20" s="43" t="s">
+    <row r="27" spans="2:2" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B27" s="39" t="s">
         <v>177</v>
       </c>
     </row>
-    <row r="22" spans="2:2" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B22" s="41" t="s">
+    <row r="28" spans="2:2" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B28" s="41" t="s">
         <v>178</v>
       </c>
     </row>
-    <row r="23" spans="2:2" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B23" s="42" t="s">
+    <row r="29" spans="2:2" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B29" s="40" t="s">
         <v>179</v>
       </c>
     </row>
-    <row r="24" spans="2:2" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B24" s="43" t="s">
+    <row r="30" spans="2:2" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B30" s="41" t="s">
         <v>180</v>
       </c>
     </row>
-    <row r="25" spans="2:2" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B25" s="42" t="s">
+    <row r="31" spans="2:2" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B31" s="40" t="s">
         <v>181</v>
       </c>
     </row>
-    <row r="27" spans="2:2" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B27" s="41" t="s">
+    <row r="33" spans="2:2" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B33" s="39" t="s">
         <v>182</v>
       </c>
     </row>
-    <row r="28" spans="2:2" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B28" s="43" t="s">
+    <row r="34" spans="2:2" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B34" s="41" t="s">
         <v>183</v>
       </c>
     </row>
-    <row r="29" spans="2:2" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B29" s="42" t="s">
+    <row r="35" spans="2:2" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B35" s="40" t="s">
         <v>184</v>
       </c>
     </row>
-    <row r="30" spans="2:2" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B30" s="43" t="s">
+    <row r="36" spans="2:2" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B36" s="41" t="s">
         <v>185</v>
       </c>
     </row>
-    <row r="31" spans="2:2" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B31" s="42" t="s">
+    <row r="37" spans="2:2" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B37" s="40" t="s">
         <v>186</v>
       </c>
     </row>
-    <row r="33" spans="2:2" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B33" s="41" t="s">
+    <row r="39" spans="2:2" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B39" s="42" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="40" spans="2:2" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B40" s="43" t="s">
         <v>187</v>
       </c>
     </row>
-    <row r="34" spans="2:2" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B34" s="43" t="s">
+    <row r="41" spans="2:2" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B41" s="44" t="s">
         <v>188</v>
       </c>
     </row>
-    <row r="35" spans="2:2" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B35" s="42" t="s">
+    <row r="42" spans="2:2" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B42" s="43" t="s">
         <v>189</v>
       </c>
     </row>
-    <row r="36" spans="2:2" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B36" s="43" t="s">
+    <row r="43" spans="2:2" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B43" s="44" t="s">
         <v>190</v>
       </c>
     </row>
-    <row r="37" spans="2:2" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B37" s="42" t="s">
+    <row r="44" spans="2:2" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B44" s="43" t="s">
         <v>191</v>
       </c>
     </row>
-    <row r="39" spans="2:2" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B39" s="44" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="40" spans="2:2" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B40" s="45" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="41" spans="2:2" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B41" s="46" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="42" spans="2:2" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B42" s="45" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="43" spans="2:2" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B43" s="46" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="44" spans="2:2" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B44" s="45" t="s">
-        <v>196</v>
-      </c>
-    </row>
     <row r="46" spans="2:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B46" s="47" t="s">
+      <c r="B46" s="45" t="s">
         <v>2</v>
       </c>
     </row>

--- a/myprojects/RVNL/RVNL_Business_Performance.xlsx
+++ b/myprojects/RVNL/RVNL_Business_Performance.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dell\Documents\GitHub\inakm.github.io\myprojects\RVNL\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\inanj\Documents\GitHub\inakm.github.io\myprojects\RVNL\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D19A34B9-F374-406B-A12C-35FD706E185E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="1350" windowWidth="28800" windowHeight="13860" tabRatio="500" activeTab="2"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="HOME" sheetId="1" r:id="rId1"/>
@@ -19,8 +20,19 @@
     <sheet name="Raw Data" sheetId="5" r:id="rId5"/>
     <sheet name="Key Insights" sheetId="6" r:id="rId6"/>
   </sheets>
-  <calcPr calcId="152511" iterateDelta="1E-4"/>
+  <calcPr calcId="191029" iterateDelta="1E-4"/>
   <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
       <loext:extCalcPr stringRefSyntax="ExcelA1"/>
     </ext>
@@ -106,9 +118,6 @@
     <t>Final summary, business story, suggestions for improvement</t>
   </si>
   <si>
-    <t>Colour guide:  Blue text = numbers directly from annual reports  |  Black text = formulas that auto-calculate  |  Green text = values linked from another sheet</t>
-  </si>
-  <si>
     <t>A.  INCOME STATEMENT  (Rs. in Crore)  |  Blue numbers are from Annual Reports</t>
   </si>
   <si>
@@ -656,12 +665,15 @@
   </si>
   <si>
     <t>Net Working Capital  (Receivables - Payables)</t>
+  </si>
+  <si>
+    <t>Blue text = numbers directly from annual reports  |  Black text = formulas that auto-calculate  |  Green text = values linked from another sheet</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
     <numFmt numFmtId="164" formatCode="0.0%"/>
     <numFmt numFmtId="165" formatCode="0.0"/>
@@ -1091,9 +1103,27 @@
     <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="20" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -1106,53 +1136,35 @@
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="10" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="10" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="10" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="10" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="10" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="10" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1417,95 +1429,95 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:E23"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="2" style="1" customWidth="1"/>
     <col min="2" max="2" width="42" style="1" customWidth="1"/>
-    <col min="3" max="3" width="57.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="64.5703125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="57.81640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="64.54296875" style="1" customWidth="1"/>
     <col min="5" max="5" width="2" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:4" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B1" s="51" t="s">
+    <row r="1" spans="2:4" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B1" s="48" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="51"/>
-      <c r="D1" s="51"/>
-    </row>
-    <row r="2" spans="2:4" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="52" t="s">
+      <c r="C1" s="48"/>
+      <c r="D1" s="48"/>
+    </row>
+    <row r="2" spans="2:4" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B2" s="49" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="52"/>
-      <c r="D2" s="52"/>
-    </row>
-    <row r="3" spans="2:4" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="53" t="s">
+      <c r="C2" s="49"/>
+      <c r="D2" s="49"/>
+    </row>
+    <row r="3" spans="2:4" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B3" s="50" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="53"/>
-      <c r="D3" s="53"/>
-    </row>
-    <row r="5" spans="2:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="46" t="s">
+      <c r="C3" s="50"/>
+      <c r="D3" s="50"/>
+    </row>
+    <row r="5" spans="2:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B5" s="51" t="s">
         <v>3</v>
       </c>
-      <c r="C5" s="46"/>
-      <c r="D5" s="46"/>
-    </row>
-    <row r="6" spans="2:4" ht="54.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="54" t="s">
+      <c r="C5" s="51"/>
+      <c r="D5" s="51"/>
+    </row>
+    <row r="6" spans="2:4" ht="54.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B6" s="52" t="s">
         <v>4</v>
       </c>
-      <c r="C6" s="54"/>
-      <c r="D6" s="54"/>
-    </row>
-    <row r="8" spans="2:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B8" s="46" t="s">
+      <c r="C6" s="52"/>
+      <c r="D6" s="52"/>
+    </row>
+    <row r="8" spans="2:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B8" s="51" t="s">
         <v>5</v>
       </c>
-      <c r="C8" s="46"/>
-      <c r="D8" s="46"/>
-    </row>
-    <row r="9" spans="2:4" ht="48" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B9" s="49" t="s">
+      <c r="C8" s="51"/>
+      <c r="D8" s="51"/>
+    </row>
+    <row r="9" spans="2:4" ht="48" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B9" s="55" t="s">
         <v>6</v>
       </c>
-      <c r="C9" s="49"/>
-      <c r="D9" s="49"/>
-    </row>
-    <row r="10" spans="2:4" ht="48" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B10" s="50" t="s">
+      <c r="C9" s="55"/>
+      <c r="D9" s="55"/>
+    </row>
+    <row r="10" spans="2:4" ht="48" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B10" s="56" t="s">
         <v>7</v>
       </c>
-      <c r="C10" s="50"/>
-      <c r="D10" s="50"/>
-    </row>
-    <row r="11" spans="2:4" ht="48" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B11" s="49" t="s">
+      <c r="C10" s="56"/>
+      <c r="D10" s="56"/>
+    </row>
+    <row r="11" spans="2:4" ht="48" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B11" s="55" t="s">
         <v>8</v>
       </c>
-      <c r="C11" s="49"/>
-      <c r="D11" s="49"/>
-    </row>
-    <row r="12" spans="2:4" ht="48" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B12" s="50" t="s">
+      <c r="C11" s="55"/>
+      <c r="D11" s="55"/>
+    </row>
+    <row r="12" spans="2:4" ht="48" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B12" s="56" t="s">
         <v>9</v>
       </c>
-      <c r="C12" s="50"/>
-      <c r="D12" s="50"/>
-    </row>
-    <row r="13" spans="2:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B13" s="46" t="s">
+      <c r="C12" s="56"/>
+      <c r="D12" s="56"/>
+    </row>
+    <row r="13" spans="2:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B13" s="51" t="s">
         <v>10</v>
       </c>
-      <c r="C13" s="46"/>
-      <c r="D13" s="46"/>
-    </row>
-    <row r="14" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C13" s="51"/>
+      <c r="D13" s="51"/>
+    </row>
+    <row r="14" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B14" s="2" t="s">
         <v>11</v>
       </c>
@@ -1513,7 +1525,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="15" spans="2:4" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:4" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B15" s="3" t="s">
         <v>13</v>
       </c>
@@ -1521,7 +1533,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="16" spans="2:4" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:4" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B16" s="5" t="s">
         <v>15</v>
       </c>
@@ -1529,7 +1541,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="17" spans="2:4" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:4" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B17" s="3" t="s">
         <v>17</v>
       </c>
@@ -1537,7 +1549,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="18" spans="2:4" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:4" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B18" s="5" t="s">
         <v>19</v>
       </c>
@@ -1545,7 +1557,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="19" spans="2:4" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:4" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B19" s="3" t="s">
         <v>21</v>
       </c>
@@ -1553,7 +1565,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="20" spans="2:4" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:4" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B20" s="5" t="s">
         <v>23</v>
       </c>
@@ -1561,27 +1573,22 @@
         <v>24</v>
       </c>
     </row>
-    <row r="21" spans="2:4" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B21" s="47" t="s">
-        <v>25</v>
-      </c>
-      <c r="C21" s="47"/>
-      <c r="D21" s="47"/>
-    </row>
-    <row r="23" spans="2:4" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B23" s="48" t="s">
+    <row r="21" spans="2:4" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B21" s="53" t="s">
+        <v>208</v>
+      </c>
+      <c r="C21" s="53"/>
+      <c r="D21" s="53"/>
+    </row>
+    <row r="23" spans="2:4" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B23" s="54" t="s">
         <v>2</v>
       </c>
-      <c r="C23" s="48"/>
-      <c r="D23" s="48"/>
+      <c r="C23" s="54"/>
+      <c r="D23" s="54"/>
     </row>
   </sheetData>
   <mergeCells count="13">
-    <mergeCell ref="B1:D1"/>
-    <mergeCell ref="B2:D2"/>
-    <mergeCell ref="B3:D3"/>
-    <mergeCell ref="B5:D5"/>
-    <mergeCell ref="B6:D6"/>
     <mergeCell ref="B13:D13"/>
     <mergeCell ref="B21:D21"/>
     <mergeCell ref="B23:D23"/>
@@ -1590,6 +1597,11 @@
     <mergeCell ref="B10:D10"/>
     <mergeCell ref="B11:D11"/>
     <mergeCell ref="B12:D12"/>
+    <mergeCell ref="B1:D1"/>
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="B3:D3"/>
+    <mergeCell ref="B5:D5"/>
+    <mergeCell ref="B6:D6"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -1597,58 +1609,59 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:J84"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="2" style="1" customWidth="1"/>
     <col min="2" max="2" width="41" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="6" width="13" style="1" customWidth="1"/>
+    <col min="3" max="5" width="13" style="1" customWidth="1"/>
+    <col min="6" max="6" width="9.453125" style="1" bestFit="1" customWidth="1"/>
     <col min="7" max="9" width="14" style="1" customWidth="1"/>
-    <col min="10" max="10" width="9.42578125" style="1" customWidth="1"/>
+    <col min="10" max="10" width="9.453125" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B1" s="61" t="s">
-        <v>192</v>
-      </c>
-      <c r="C1" s="61"/>
-      <c r="D1" s="61"/>
-      <c r="E1" s="61"/>
-      <c r="F1" s="61"/>
-      <c r="G1" s="61"/>
-      <c r="H1" s="61"/>
-      <c r="I1" s="61"/>
-    </row>
-    <row r="3" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="56" t="s">
+    <row r="1" spans="2:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B1" s="57" t="s">
+        <v>191</v>
+      </c>
+      <c r="C1" s="57"/>
+      <c r="D1" s="57"/>
+      <c r="E1" s="57"/>
+      <c r="F1" s="57"/>
+      <c r="G1" s="57"/>
+      <c r="H1" s="57"/>
+      <c r="I1" s="57"/>
+    </row>
+    <row r="3" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B3" s="58" t="s">
+        <v>25</v>
+      </c>
+      <c r="C3" s="58"/>
+      <c r="D3" s="58"/>
+      <c r="E3" s="58"/>
+      <c r="F3" s="58"/>
+    </row>
+    <row r="4" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B4" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="C3" s="56"/>
-      <c r="D3" s="56"/>
-      <c r="E3" s="56"/>
-      <c r="F3" s="56"/>
-    </row>
-    <row r="4" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B4" s="7" t="s">
+      <c r="C4" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="C4" s="8" t="s">
+      <c r="D4" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="D4" s="8" t="s">
+      <c r="E4" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="E4" s="8" t="s">
+      <c r="F4" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="F4" s="8" t="s">
+    </row>
+    <row r="5" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B5" s="4" t="s">
         <v>31</v>
-      </c>
-    </row>
-    <row r="5" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="4" t="s">
-        <v>32</v>
       </c>
       <c r="C5" s="9">
         <v>19381.71</v>
@@ -1663,9 +1676,9 @@
         <v>19869.349999999999</v>
       </c>
     </row>
-    <row r="6" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B6" s="4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C6" s="9">
         <v>809.26</v>
@@ -1680,9 +1693,9 @@
         <v>1018.89</v>
       </c>
     </row>
-    <row r="7" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B7" s="10" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C7" s="11">
         <f>SUM(C5:C6)</f>
@@ -1701,18 +1714,18 @@
         <v>20888.239999999998</v>
       </c>
     </row>
-    <row r="8" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B8" s="62" t="s">
+    <row r="8" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B8" s="59" t="s">
+        <v>34</v>
+      </c>
+      <c r="C8" s="59"/>
+      <c r="D8" s="59"/>
+      <c r="E8" s="59"/>
+      <c r="F8" s="59"/>
+    </row>
+    <row r="9" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B9" s="4" t="s">
         <v>35</v>
-      </c>
-      <c r="C8" s="62"/>
-      <c r="D8" s="62"/>
-      <c r="E8" s="62"/>
-      <c r="F8" s="62"/>
-    </row>
-    <row r="9" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B9" s="4" t="s">
-        <v>36</v>
       </c>
       <c r="C9" s="9">
         <v>17905.57</v>
@@ -1727,9 +1740,9 @@
         <v>18385.2</v>
       </c>
     </row>
-    <row r="10" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B10" s="12" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C10" s="13">
         <v>203.05</v>
@@ -1744,9 +1757,9 @@
         <v>182.98</v>
       </c>
     </row>
-    <row r="11" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B11" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C11" s="9">
         <v>563.71</v>
@@ -1761,9 +1774,9 @@
         <v>539.51</v>
       </c>
     </row>
-    <row r="12" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B12" s="12" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C12" s="13">
         <v>20.9</v>
@@ -1778,9 +1791,9 @@
         <v>30.6</v>
       </c>
     </row>
-    <row r="13" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B13" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C13" s="9">
         <v>91.5</v>
@@ -1795,9 +1808,9 @@
         <v>199.78</v>
       </c>
     </row>
-    <row r="14" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B14" s="10" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C14" s="11">
         <f>SUM(C9:C13)</f>
@@ -1816,18 +1829,18 @@
         <v>19338.069999999996</v>
       </c>
     </row>
-    <row r="15" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B15" s="62" t="s">
+    <row r="15" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B15" s="59" t="s">
+        <v>41</v>
+      </c>
+      <c r="C15" s="59"/>
+      <c r="D15" s="59"/>
+      <c r="E15" s="59"/>
+      <c r="F15" s="59"/>
+    </row>
+    <row r="16" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B16" s="14" t="s">
         <v>42</v>
-      </c>
-      <c r="C15" s="62"/>
-      <c r="D15" s="62"/>
-      <c r="E15" s="62"/>
-      <c r="F15" s="62"/>
-    </row>
-    <row r="16" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B16" s="14" t="s">
-        <v>43</v>
       </c>
       <c r="C16" s="15">
         <f>C7-C14</f>
@@ -1846,9 +1859,9 @@
         <v>1550.1700000000019</v>
       </c>
     </row>
-    <row r="17" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B17" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C17" s="9">
         <v>318.89</v>
@@ -1863,9 +1876,9 @@
         <v>361.55</v>
       </c>
     </row>
-    <row r="18" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B18" s="14" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C18" s="15">
         <f>C16-C17</f>
@@ -1884,35 +1897,35 @@
         <v>1188.6200000000019</v>
       </c>
     </row>
-    <row r="20" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B20" s="56" t="s">
+    <row r="20" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B20" s="58" t="s">
+        <v>45</v>
+      </c>
+      <c r="C20" s="58"/>
+      <c r="D20" s="58"/>
+      <c r="E20" s="58"/>
+      <c r="F20" s="58"/>
+      <c r="G20" s="58"/>
+      <c r="H20" s="58"/>
+      <c r="I20" s="58"/>
+    </row>
+    <row r="21" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B21" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="C20" s="56"/>
-      <c r="D20" s="56"/>
-      <c r="E20" s="56"/>
-      <c r="F20" s="56"/>
-      <c r="G20" s="56"/>
-      <c r="H20" s="56"/>
-      <c r="I20" s="56"/>
-    </row>
-    <row r="21" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B21" s="7" t="s">
+      <c r="C21" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="D21" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="E21" s="8" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="22" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B22" s="4" t="s">
         <v>47</v>
-      </c>
-      <c r="C21" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="D21" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="E21" s="8" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="22" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B22" s="4" t="s">
-        <v>48</v>
       </c>
       <c r="C22" s="9">
         <f>D5</f>
@@ -1927,9 +1940,9 @@
         <v>19869.349999999999</v>
       </c>
     </row>
-    <row r="23" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B23" s="12" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C23" s="13">
         <f>C5</f>
@@ -1944,9 +1957,9 @@
         <v>21732.58</v>
       </c>
     </row>
-    <row r="24" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B24" s="10" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C24" s="16">
         <f>C22-C23</f>
@@ -1961,9 +1974,9 @@
         <v>-1863.2300000000032</v>
       </c>
     </row>
-    <row r="25" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B25" s="4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C25" s="17">
         <f>C24/C23</f>
@@ -1978,81 +1991,81 @@
         <v>-8.5734413493473993E-2</v>
       </c>
     </row>
-    <row r="26" spans="2:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="27" spans="2:9" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B27" s="57" t="s">
+    <row r="26" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="27" spans="2:9" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B27" s="60" t="s">
+        <v>51</v>
+      </c>
+      <c r="C27" s="61"/>
+      <c r="D27" s="61"/>
+      <c r="E27" s="61"/>
+      <c r="F27" s="62"/>
+    </row>
+    <row r="28" spans="2:9" ht="28" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B28" s="63" t="s">
         <v>52</v>
       </c>
-      <c r="C27" s="58"/>
-      <c r="D27" s="58"/>
-      <c r="E27" s="58"/>
-      <c r="F27" s="59"/>
-    </row>
-    <row r="28" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B28" s="60" t="s">
+      <c r="C28" s="63"/>
+      <c r="D28" s="63"/>
+      <c r="E28" s="63"/>
+      <c r="F28" s="63"/>
+    </row>
+    <row r="29" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B29" s="55" t="s">
         <v>53</v>
       </c>
-      <c r="C28" s="60"/>
-      <c r="D28" s="60"/>
-      <c r="E28" s="60"/>
-      <c r="F28" s="60"/>
-    </row>
-    <row r="29" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B29" s="49" t="s">
+      <c r="C29" s="55"/>
+      <c r="D29" s="55"/>
+      <c r="E29" s="55"/>
+      <c r="F29" s="55"/>
+    </row>
+    <row r="30" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B30" s="56" t="s">
         <v>54</v>
       </c>
-      <c r="C29" s="49"/>
-      <c r="D29" s="49"/>
-      <c r="E29" s="49"/>
-      <c r="F29" s="49"/>
-    </row>
-    <row r="30" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B30" s="50" t="s">
+      <c r="C30" s="56"/>
+      <c r="D30" s="56"/>
+      <c r="E30" s="56"/>
+      <c r="F30" s="56"/>
+    </row>
+    <row r="31" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B31" s="55" t="s">
         <v>55</v>
       </c>
-      <c r="C30" s="50"/>
-      <c r="D30" s="50"/>
-      <c r="E30" s="50"/>
-      <c r="F30" s="50"/>
-    </row>
-    <row r="31" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B31" s="49" t="s">
+      <c r="C31" s="55"/>
+      <c r="D31" s="55"/>
+      <c r="E31" s="55"/>
+      <c r="F31" s="55"/>
+    </row>
+    <row r="32" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B32" s="58" t="s">
         <v>56</v>
       </c>
-      <c r="C31" s="49"/>
-      <c r="D31" s="49"/>
-      <c r="E31" s="49"/>
-      <c r="F31" s="49"/>
-    </row>
-    <row r="32" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B32" s="56" t="s">
+      <c r="C32" s="58"/>
+      <c r="D32" s="58"/>
+      <c r="E32" s="58"/>
+      <c r="F32" s="58"/>
+      <c r="G32" s="58"/>
+      <c r="H32" s="58"/>
+      <c r="I32" s="58"/>
+    </row>
+    <row r="33" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B33" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="C33" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="D33" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="E33" s="8" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="34" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B34" s="4" t="s">
         <v>57</v>
-      </c>
-      <c r="C32" s="56"/>
-      <c r="D32" s="56"/>
-      <c r="E32" s="56"/>
-      <c r="F32" s="56"/>
-      <c r="G32" s="56"/>
-      <c r="H32" s="56"/>
-      <c r="I32" s="56"/>
-    </row>
-    <row r="33" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B33" s="7" t="s">
-        <v>47</v>
-      </c>
-      <c r="C33" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="D33" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="E33" s="8" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="34" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B34" s="4" t="s">
-        <v>58</v>
       </c>
       <c r="C34" s="9">
         <f>D16</f>
@@ -2067,9 +2080,9 @@
         <v>1550.1700000000019</v>
       </c>
     </row>
-    <row r="35" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B35" s="12" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C35" s="13">
         <f>D18</f>
@@ -2084,9 +2097,9 @@
         <v>1188.6200000000019</v>
       </c>
     </row>
-    <row r="36" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B36" s="4" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C36" s="17">
         <f>(D16-C16)/C16</f>
@@ -2101,9 +2114,9 @@
         <v>-0.20069609157471197</v>
       </c>
     </row>
-    <row r="37" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B37" s="12" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C37" s="18">
         <f>(D18-C18)/C18</f>
@@ -2118,9 +2131,9 @@
         <v>-0.18751837041593783</v>
       </c>
     </row>
-    <row r="38" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B38" s="10" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C38" s="19">
         <f>D18/D5</f>
@@ -2135,9 +2148,9 @@
         <v>5.9821785815842091E-2</v>
       </c>
     </row>
-    <row r="39" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B39" s="4" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C39" s="17">
         <f>D16/D5</f>
@@ -2152,84 +2165,84 @@
         <v>7.8018153588315778E-2</v>
       </c>
     </row>
-    <row r="40" spans="2:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="41" spans="2:9" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B41" s="57" t="s">
+    <row r="40" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="41" spans="2:9" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B41" s="60" t="s">
+        <v>63</v>
+      </c>
+      <c r="C41" s="61"/>
+      <c r="D41" s="61"/>
+      <c r="E41" s="61"/>
+      <c r="F41" s="62"/>
+    </row>
+    <row r="42" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B42" s="63" t="s">
         <v>64</v>
       </c>
-      <c r="C41" s="58"/>
-      <c r="D41" s="58"/>
-      <c r="E41" s="58"/>
-      <c r="F41" s="59"/>
-    </row>
-    <row r="42" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B42" s="60" t="s">
+      <c r="C42" s="63"/>
+      <c r="D42" s="63"/>
+      <c r="E42" s="63"/>
+      <c r="F42" s="63"/>
+    </row>
+    <row r="43" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B43" s="55" t="s">
         <v>65</v>
       </c>
-      <c r="C42" s="60"/>
-      <c r="D42" s="60"/>
-      <c r="E42" s="60"/>
-      <c r="F42" s="60"/>
-    </row>
-    <row r="43" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B43" s="49" t="s">
+      <c r="C43" s="55"/>
+      <c r="D43" s="55"/>
+      <c r="E43" s="55"/>
+      <c r="F43" s="55"/>
+    </row>
+    <row r="44" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B44" s="56" t="s">
         <v>66</v>
       </c>
-      <c r="C43" s="49"/>
-      <c r="D43" s="49"/>
-      <c r="E43" s="49"/>
-      <c r="F43" s="49"/>
-    </row>
-    <row r="44" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B44" s="50" t="s">
+      <c r="C44" s="56"/>
+      <c r="D44" s="56"/>
+      <c r="E44" s="56"/>
+      <c r="F44" s="56"/>
+    </row>
+    <row r="45" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B45" s="55" t="s">
         <v>67</v>
       </c>
-      <c r="C44" s="50"/>
-      <c r="D44" s="50"/>
-      <c r="E44" s="50"/>
-      <c r="F44" s="50"/>
-    </row>
-    <row r="45" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B45" s="49" t="s">
+      <c r="C45" s="55"/>
+      <c r="D45" s="55"/>
+      <c r="E45" s="55"/>
+      <c r="F45" s="55"/>
+    </row>
+    <row r="46" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B46" s="58" t="s">
         <v>68</v>
       </c>
-      <c r="C45" s="49"/>
-      <c r="D45" s="49"/>
-      <c r="E45" s="49"/>
-      <c r="F45" s="49"/>
-    </row>
-    <row r="46" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B46" s="56" t="s">
+      <c r="C46" s="58"/>
+      <c r="D46" s="58"/>
+      <c r="E46" s="58"/>
+      <c r="F46" s="58"/>
+      <c r="G46" s="58"/>
+      <c r="H46" s="58"/>
+      <c r="I46" s="58"/>
+    </row>
+    <row r="47" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B47" s="7" t="s">
         <v>69</v>
       </c>
-      <c r="C46" s="56"/>
-      <c r="D46" s="56"/>
-      <c r="E46" s="56"/>
-      <c r="F46" s="56"/>
-      <c r="G46" s="56"/>
-      <c r="H46" s="56"/>
-      <c r="I46" s="56"/>
-    </row>
-    <row r="47" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B47" s="7" t="s">
-        <v>70</v>
-      </c>
       <c r="C47" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="D47" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="D47" s="8" t="s">
+      <c r="E47" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="E47" s="8" t="s">
+      <c r="F47" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="F47" s="8" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="48" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="48" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B48" s="12" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C48" s="18">
         <f>C9/C5</f>
@@ -2248,9 +2261,9 @@
         <v>0.9253045519858476</v>
       </c>
     </row>
-    <row r="49" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B49" s="4" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C49" s="17">
         <f>C10/C5</f>
@@ -2269,9 +2282,9 @@
         <v>9.2091588300573495E-3</v>
       </c>
     </row>
-    <row r="50" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B50" s="12" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C50" s="18">
         <f>C11/C5</f>
@@ -2290,9 +2303,9 @@
         <v>2.7152876163538314E-2</v>
       </c>
     </row>
-    <row r="51" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B51" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C51" s="17">
         <f>C12/C5</f>
@@ -2311,9 +2324,9 @@
         <v>1.5400604448560222E-3</v>
       </c>
     </row>
-    <row r="52" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B52" s="12" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C52" s="18">
         <f>C13/C5</f>
@@ -2332,9 +2345,9 @@
         <v>1.0054682211546932E-2</v>
       </c>
     </row>
-    <row r="53" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B53" s="10" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C53" s="19">
         <f>C14/C5</f>
@@ -2353,81 +2366,81 @@
         <v>0.973261329635846</v>
       </c>
     </row>
-    <row r="54" spans="2:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="55" spans="2:9" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B55" s="57" t="s">
+    <row r="54" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="55" spans="2:9" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B55" s="60" t="s">
+        <v>70</v>
+      </c>
+      <c r="C55" s="61"/>
+      <c r="D55" s="61"/>
+      <c r="E55" s="61"/>
+      <c r="F55" s="62"/>
+    </row>
+    <row r="56" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B56" s="63" t="s">
         <v>71</v>
       </c>
-      <c r="C55" s="58"/>
-      <c r="D55" s="58"/>
-      <c r="E55" s="58"/>
-      <c r="F55" s="59"/>
-    </row>
-    <row r="56" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B56" s="60" t="s">
+      <c r="C56" s="63"/>
+      <c r="D56" s="63"/>
+      <c r="E56" s="63"/>
+      <c r="F56" s="63"/>
+    </row>
+    <row r="57" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B57" s="55" t="s">
         <v>72</v>
       </c>
-      <c r="C56" s="60"/>
-      <c r="D56" s="60"/>
-      <c r="E56" s="60"/>
-      <c r="F56" s="60"/>
-    </row>
-    <row r="57" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B57" s="49" t="s">
+      <c r="C57" s="55"/>
+      <c r="D57" s="55"/>
+      <c r="E57" s="55"/>
+      <c r="F57" s="55"/>
+    </row>
+    <row r="58" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B58" s="56" t="s">
         <v>73</v>
       </c>
-      <c r="C57" s="49"/>
-      <c r="D57" s="49"/>
-      <c r="E57" s="49"/>
-      <c r="F57" s="49"/>
-    </row>
-    <row r="58" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B58" s="50" t="s">
+      <c r="C58" s="56"/>
+      <c r="D58" s="56"/>
+      <c r="E58" s="56"/>
+      <c r="F58" s="56"/>
+    </row>
+    <row r="59" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B59" s="55" t="s">
         <v>74</v>
       </c>
-      <c r="C58" s="50"/>
-      <c r="D58" s="50"/>
-      <c r="E58" s="50"/>
-      <c r="F58" s="50"/>
-    </row>
-    <row r="59" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B59" s="49" t="s">
+      <c r="C59" s="55"/>
+      <c r="D59" s="55"/>
+      <c r="E59" s="55"/>
+      <c r="F59" s="55"/>
+    </row>
+    <row r="60" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B60" s="58" t="s">
+        <v>194</v>
+      </c>
+      <c r="C60" s="58"/>
+      <c r="D60" s="58"/>
+      <c r="E60" s="58"/>
+      <c r="F60" s="58"/>
+      <c r="G60" s="58"/>
+      <c r="H60" s="58"/>
+      <c r="I60" s="58"/>
+    </row>
+    <row r="61" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B61" s="7" t="s">
         <v>75</v>
       </c>
-      <c r="C59" s="49"/>
-      <c r="D59" s="49"/>
-      <c r="E59" s="49"/>
-      <c r="F59" s="49"/>
-    </row>
-    <row r="60" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B60" s="56" t="s">
-        <v>195</v>
-      </c>
-      <c r="C60" s="56"/>
-      <c r="D60" s="56"/>
-      <c r="E60" s="56"/>
-      <c r="F60" s="56"/>
-      <c r="G60" s="56"/>
-      <c r="H60" s="56"/>
-      <c r="I60" s="56"/>
-    </row>
-    <row r="61" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B61" s="7" t="s">
+      <c r="C61" s="8" t="s">
         <v>76</v>
       </c>
-      <c r="C61" s="8" t="s">
+      <c r="D61" s="8" t="s">
         <v>77</v>
       </c>
-      <c r="D61" s="8" t="s">
+      <c r="E61" s="8" t="s">
         <v>78</v>
       </c>
-      <c r="E61" s="8" t="s">
+    </row>
+    <row r="62" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B62" s="20" t="s">
         <v>79</v>
-      </c>
-    </row>
-    <row r="62" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B62" s="20" t="s">
-        <v>80</v>
       </c>
       <c r="C62" s="21">
         <v>0.08</v>
@@ -2439,9 +2452,9 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="63" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B63" s="20" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C63" s="21">
         <v>0.06</v>
@@ -2453,9 +2466,9 @@
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
-    <row r="64" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B64" s="20" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C64" s="21">
         <v>0.05</v>
@@ -2467,33 +2480,33 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="65" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B65" s="56" t="s">
-        <v>196</v>
-      </c>
-      <c r="C65" s="56"/>
-      <c r="D65" s="56"/>
-      <c r="E65" s="56"/>
-      <c r="F65" s="56"/>
-      <c r="G65" s="56"/>
-      <c r="H65" s="56"/>
-      <c r="I65" s="56"/>
-    </row>
-    <row r="66" spans="2:9" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B65" s="58" t="s">
+        <v>195</v>
+      </c>
+      <c r="C65" s="58"/>
+      <c r="D65" s="58"/>
+      <c r="E65" s="58"/>
+      <c r="F65" s="58"/>
+      <c r="G65" s="58"/>
+      <c r="H65" s="58"/>
+      <c r="I65" s="58"/>
+    </row>
+    <row r="66" spans="2:9" ht="29.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B66" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="C66" s="22" t="s">
         <v>83</v>
       </c>
-      <c r="C66" s="22" t="s">
+      <c r="D66" s="22" t="s">
         <v>84</v>
       </c>
-      <c r="D66" s="22" t="s">
+      <c r="E66" s="22" t="s">
         <v>85</v>
       </c>
-      <c r="E66" s="22" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="67" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="67" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B67" s="23">
         <f>F5</f>
         <v>19869.349999999999</v>
@@ -2511,7 +2524,7 @@
         <v>26437.362336000006</v>
       </c>
     </row>
-    <row r="68" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B68" s="24">
         <f>F6</f>
         <v>1018.89</v>
@@ -2529,7 +2542,7 @@
         <v>1179.4925362500001</v>
       </c>
     </row>
-    <row r="69" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B69" s="16">
         <f>F7</f>
         <v>20888.239999999998</v>
@@ -2547,7 +2560,7 @@
         <v>27616.854872250005</v>
       </c>
     </row>
-    <row r="70" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B70" s="25">
         <f>F18</f>
         <v>1188.6200000000019</v>
@@ -2565,7 +2578,7 @@
         <v>1718.4285518400004</v>
       </c>
     </row>
-    <row r="71" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B71" s="17">
         <f>E38</f>
         <v>5.9821785815842091E-2</v>
@@ -2583,188 +2596,188 @@
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
-    <row r="72" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B72" s="56" t="s">
+    <row r="72" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B72" s="58" t="s">
+        <v>192</v>
+      </c>
+      <c r="C72" s="58"/>
+      <c r="D72" s="58"/>
+      <c r="E72" s="58"/>
+      <c r="F72" s="58"/>
+      <c r="G72" s="58"/>
+      <c r="H72" s="58"/>
+      <c r="I72" s="58"/>
+    </row>
+    <row r="73" spans="2:9" ht="39.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B73" s="55" t="s">
+        <v>86</v>
+      </c>
+      <c r="C73" s="55"/>
+      <c r="D73" s="55"/>
+      <c r="E73" s="55"/>
+      <c r="F73" s="55"/>
+      <c r="G73" s="55"/>
+      <c r="H73" s="55"/>
+      <c r="I73" s="55"/>
+    </row>
+    <row r="74" spans="2:9" ht="39.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B74" s="56" t="s">
+        <v>87</v>
+      </c>
+      <c r="C74" s="56"/>
+      <c r="D74" s="56"/>
+      <c r="E74" s="56"/>
+      <c r="F74" s="56"/>
+      <c r="G74" s="56"/>
+      <c r="H74" s="56"/>
+      <c r="I74" s="56"/>
+    </row>
+    <row r="75" spans="2:9" ht="39.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B75" s="55" t="s">
+        <v>88</v>
+      </c>
+      <c r="C75" s="55"/>
+      <c r="D75" s="55"/>
+      <c r="E75" s="55"/>
+      <c r="F75" s="55"/>
+      <c r="G75" s="55"/>
+      <c r="H75" s="55"/>
+      <c r="I75" s="55"/>
+    </row>
+    <row r="76" spans="2:9" ht="39.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B76" s="56" t="s">
+        <v>89</v>
+      </c>
+      <c r="C76" s="56"/>
+      <c r="D76" s="56"/>
+      <c r="E76" s="56"/>
+      <c r="F76" s="56"/>
+      <c r="G76" s="56"/>
+      <c r="H76" s="56"/>
+      <c r="I76" s="56"/>
+    </row>
+    <row r="77" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B77" s="58" t="s">
         <v>193</v>
       </c>
-      <c r="C72" s="56"/>
-      <c r="D72" s="56"/>
-      <c r="E72" s="56"/>
-      <c r="F72" s="56"/>
-      <c r="G72" s="56"/>
-      <c r="H72" s="56"/>
-      <c r="I72" s="56"/>
-    </row>
-    <row r="73" spans="2:9" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B73" s="49" t="s">
-        <v>87</v>
-      </c>
-      <c r="C73" s="49"/>
-      <c r="D73" s="49"/>
-      <c r="E73" s="49"/>
-      <c r="F73" s="49"/>
-      <c r="G73" s="49"/>
-      <c r="H73" s="49"/>
-      <c r="I73" s="49"/>
-    </row>
-    <row r="74" spans="2:9" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B74" s="50" t="s">
-        <v>88</v>
-      </c>
-      <c r="C74" s="50"/>
-      <c r="D74" s="50"/>
-      <c r="E74" s="50"/>
-      <c r="F74" s="50"/>
-      <c r="G74" s="50"/>
-      <c r="H74" s="50"/>
-      <c r="I74" s="50"/>
-    </row>
-    <row r="75" spans="2:9" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B75" s="49" t="s">
-        <v>89</v>
-      </c>
-      <c r="C75" s="49"/>
-      <c r="D75" s="49"/>
-      <c r="E75" s="49"/>
-      <c r="F75" s="49"/>
-      <c r="G75" s="49"/>
-      <c r="H75" s="49"/>
-      <c r="I75" s="49"/>
-    </row>
-    <row r="76" spans="2:9" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B76" s="50" t="s">
+      <c r="C77" s="58"/>
+      <c r="D77" s="58"/>
+      <c r="E77" s="58"/>
+      <c r="F77" s="58"/>
+      <c r="G77" s="58"/>
+      <c r="H77" s="58"/>
+      <c r="I77" s="58"/>
+    </row>
+    <row r="78" spans="2:9" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B78" s="64" t="s">
         <v>90</v>
       </c>
-      <c r="C76" s="50"/>
-      <c r="D76" s="50"/>
-      <c r="E76" s="50"/>
-      <c r="F76" s="50"/>
-      <c r="G76" s="50"/>
-      <c r="H76" s="50"/>
-      <c r="I76" s="50"/>
-    </row>
-    <row r="77" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B77" s="56" t="s">
-        <v>194</v>
-      </c>
-      <c r="C77" s="56"/>
-      <c r="D77" s="56"/>
-      <c r="E77" s="56"/>
-      <c r="F77" s="56"/>
-      <c r="G77" s="56"/>
-      <c r="H77" s="56"/>
-      <c r="I77" s="56"/>
-    </row>
-    <row r="78" spans="2:9" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B78" s="55" t="s">
+      <c r="C78" s="64"/>
+      <c r="D78" s="64"/>
+      <c r="E78" s="64"/>
+      <c r="F78" s="64"/>
+      <c r="G78" s="64"/>
+      <c r="H78" s="64"/>
+      <c r="I78" s="64"/>
+    </row>
+    <row r="79" spans="2:9" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B79" s="55" t="s">
         <v>91</v>
       </c>
-      <c r="C78" s="55"/>
-      <c r="D78" s="55"/>
-      <c r="E78" s="55"/>
-      <c r="F78" s="55"/>
-      <c r="G78" s="55"/>
-      <c r="H78" s="55"/>
-      <c r="I78" s="55"/>
-    </row>
-    <row r="79" spans="2:9" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B79" s="49" t="s">
+      <c r="C79" s="55"/>
+      <c r="D79" s="55"/>
+      <c r="E79" s="55"/>
+      <c r="F79" s="55"/>
+      <c r="G79" s="55"/>
+      <c r="H79" s="55"/>
+      <c r="I79" s="55"/>
+    </row>
+    <row r="80" spans="2:9" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B80" s="64" t="s">
         <v>92</v>
       </c>
-      <c r="C79" s="49"/>
-      <c r="D79" s="49"/>
-      <c r="E79" s="49"/>
-      <c r="F79" s="49"/>
-      <c r="G79" s="49"/>
-      <c r="H79" s="49"/>
-      <c r="I79" s="49"/>
-    </row>
-    <row r="80" spans="2:9" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B80" s="55" t="s">
+      <c r="C80" s="64"/>
+      <c r="D80" s="64"/>
+      <c r="E80" s="64"/>
+      <c r="F80" s="64"/>
+      <c r="G80" s="64"/>
+      <c r="H80" s="64"/>
+      <c r="I80" s="64"/>
+    </row>
+    <row r="81" spans="2:9" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B81" s="55" t="s">
         <v>93</v>
       </c>
-      <c r="C80" s="55"/>
-      <c r="D80" s="55"/>
-      <c r="E80" s="55"/>
-      <c r="F80" s="55"/>
-      <c r="G80" s="55"/>
-      <c r="H80" s="55"/>
-      <c r="I80" s="55"/>
-    </row>
-    <row r="81" spans="2:9" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B81" s="49" t="s">
+      <c r="C81" s="55"/>
+      <c r="D81" s="55"/>
+      <c r="E81" s="55"/>
+      <c r="F81" s="55"/>
+      <c r="G81" s="55"/>
+      <c r="H81" s="55"/>
+      <c r="I81" s="55"/>
+    </row>
+    <row r="82" spans="2:9" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B82" s="64" t="s">
         <v>94</v>
       </c>
-      <c r="C81" s="49"/>
-      <c r="D81" s="49"/>
-      <c r="E81" s="49"/>
-      <c r="F81" s="49"/>
-      <c r="G81" s="49"/>
-      <c r="H81" s="49"/>
-      <c r="I81" s="49"/>
-    </row>
-    <row r="82" spans="2:9" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B82" s="55" t="s">
-        <v>95</v>
-      </c>
-      <c r="C82" s="55"/>
-      <c r="D82" s="55"/>
-      <c r="E82" s="55"/>
-      <c r="F82" s="55"/>
-      <c r="G82" s="55"/>
-      <c r="H82" s="55"/>
-      <c r="I82" s="55"/>
-    </row>
-    <row r="84" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B84" s="48" t="s">
+      <c r="C82" s="64"/>
+      <c r="D82" s="64"/>
+      <c r="E82" s="64"/>
+      <c r="F82" s="64"/>
+      <c r="G82" s="64"/>
+      <c r="H82" s="64"/>
+      <c r="I82" s="64"/>
+    </row>
+    <row r="84" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B84" s="54" t="s">
         <v>2</v>
       </c>
-      <c r="C84" s="48"/>
-      <c r="D84" s="48"/>
-      <c r="E84" s="48"/>
-      <c r="F84" s="48"/>
-      <c r="G84" s="48"/>
-      <c r="H84" s="48"/>
-      <c r="I84" s="48"/>
+      <c r="C84" s="54"/>
+      <c r="D84" s="54"/>
+      <c r="E84" s="54"/>
+      <c r="F84" s="54"/>
+      <c r="G84" s="54"/>
+      <c r="H84" s="54"/>
+      <c r="I84" s="54"/>
     </row>
   </sheetData>
   <mergeCells count="36">
-    <mergeCell ref="B1:I1"/>
-    <mergeCell ref="B3:F3"/>
-    <mergeCell ref="B8:F8"/>
-    <mergeCell ref="B15:F15"/>
-    <mergeCell ref="B20:I20"/>
-    <mergeCell ref="B27:F27"/>
-    <mergeCell ref="B28:F28"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="B30:F30"/>
-    <mergeCell ref="B31:F31"/>
-    <mergeCell ref="B32:I32"/>
-    <mergeCell ref="B41:F41"/>
-    <mergeCell ref="B42:F42"/>
-    <mergeCell ref="B43:F43"/>
-    <mergeCell ref="B44:F44"/>
-    <mergeCell ref="B45:F45"/>
-    <mergeCell ref="B46:I46"/>
-    <mergeCell ref="B55:F55"/>
-    <mergeCell ref="B56:F56"/>
-    <mergeCell ref="B57:F57"/>
-    <mergeCell ref="B58:F58"/>
-    <mergeCell ref="B59:F59"/>
-    <mergeCell ref="B60:I60"/>
-    <mergeCell ref="B65:I65"/>
-    <mergeCell ref="B72:I72"/>
-    <mergeCell ref="B73:I73"/>
-    <mergeCell ref="B74:I74"/>
-    <mergeCell ref="B75:I75"/>
-    <mergeCell ref="B76:I76"/>
-    <mergeCell ref="B77:I77"/>
     <mergeCell ref="B84:I84"/>
     <mergeCell ref="B78:I78"/>
     <mergeCell ref="B79:I79"/>
     <mergeCell ref="B80:I80"/>
     <mergeCell ref="B81:I81"/>
     <mergeCell ref="B82:I82"/>
+    <mergeCell ref="B73:I73"/>
+    <mergeCell ref="B74:I74"/>
+    <mergeCell ref="B75:I75"/>
+    <mergeCell ref="B76:I76"/>
+    <mergeCell ref="B77:I77"/>
+    <mergeCell ref="B58:F58"/>
+    <mergeCell ref="B59:F59"/>
+    <mergeCell ref="B60:I60"/>
+    <mergeCell ref="B65:I65"/>
+    <mergeCell ref="B72:I72"/>
+    <mergeCell ref="B45:F45"/>
+    <mergeCell ref="B46:I46"/>
+    <mergeCell ref="B55:F55"/>
+    <mergeCell ref="B56:F56"/>
+    <mergeCell ref="B57:F57"/>
+    <mergeCell ref="B32:I32"/>
+    <mergeCell ref="B41:F41"/>
+    <mergeCell ref="B42:F42"/>
+    <mergeCell ref="B43:F43"/>
+    <mergeCell ref="B44:F44"/>
+    <mergeCell ref="B27:F27"/>
+    <mergeCell ref="B28:F28"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="B30:F30"/>
+    <mergeCell ref="B31:F31"/>
+    <mergeCell ref="B1:I1"/>
+    <mergeCell ref="B3:F3"/>
+    <mergeCell ref="B8:F8"/>
+    <mergeCell ref="B15:F15"/>
+    <mergeCell ref="B20:I20"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -2772,58 +2785,58 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:J48"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="2" style="1" customWidth="1"/>
-    <col min="2" max="2" width="51.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="51.1796875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="6" width="13" style="1" customWidth="1"/>
     <col min="7" max="9" width="14" style="1" customWidth="1"/>
     <col min="10" max="10" width="2" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B1" s="61" t="s">
-        <v>197</v>
-      </c>
-      <c r="C1" s="61"/>
-      <c r="D1" s="61"/>
-      <c r="E1" s="61"/>
-      <c r="F1" s="61"/>
-      <c r="G1" s="61"/>
-      <c r="H1" s="61"/>
-      <c r="I1" s="61"/>
-    </row>
-    <row r="3" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="56" t="s">
-        <v>205</v>
-      </c>
-      <c r="C3" s="56"/>
-      <c r="D3" s="56"/>
-      <c r="E3" s="56"/>
-      <c r="F3" s="56"/>
-    </row>
-    <row r="4" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="2:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B1" s="57" t="s">
+        <v>196</v>
+      </c>
+      <c r="C1" s="57"/>
+      <c r="D1" s="57"/>
+      <c r="E1" s="57"/>
+      <c r="F1" s="57"/>
+      <c r="G1" s="57"/>
+      <c r="H1" s="57"/>
+      <c r="I1" s="57"/>
+    </row>
+    <row r="3" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B3" s="58" t="s">
+        <v>204</v>
+      </c>
+      <c r="C3" s="58"/>
+      <c r="D3" s="58"/>
+      <c r="E3" s="58"/>
+      <c r="F3" s="58"/>
+    </row>
+    <row r="4" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B4" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="C4" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="C4" s="8" t="s">
+      <c r="D4" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="D4" s="8" t="s">
+      <c r="E4" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="E4" s="8" t="s">
+      <c r="F4" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="F4" s="8" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="5" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="5" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B5" s="10" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C5" s="11">
         <v>19379.09</v>
@@ -2838,9 +2851,9 @@
         <v>19484.52</v>
       </c>
     </row>
-    <row r="6" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B6" s="4" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C6" s="9">
         <v>4569.93</v>
@@ -2855,9 +2868,9 @@
         <v>3044.8</v>
       </c>
     </row>
-    <row r="7" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B7" s="12" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C7" s="13">
         <v>938.17</v>
@@ -2872,9 +2885,9 @@
         <v>1489.51</v>
       </c>
     </row>
-    <row r="8" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B8" s="14" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C8" s="15">
         <v>5631.44</v>
@@ -2889,9 +2902,9 @@
         <v>8623.7199999999993</v>
       </c>
     </row>
-    <row r="9" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B9" s="4" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C9" s="9">
         <v>6315.42</v>
@@ -2906,9 +2919,9 @@
         <v>4889.51</v>
       </c>
     </row>
-    <row r="10" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B10" s="12" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C10" s="13">
         <v>230.5</v>
@@ -2923,38 +2936,38 @@
         <v>344.87</v>
       </c>
     </row>
-    <row r="12" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B12" s="56" t="s">
+    <row r="12" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B12" s="58" t="s">
+        <v>101</v>
+      </c>
+      <c r="C12" s="58"/>
+      <c r="D12" s="58"/>
+      <c r="E12" s="58"/>
+      <c r="F12" s="58"/>
+      <c r="G12" s="58"/>
+      <c r="H12" s="58"/>
+      <c r="I12" s="58"/>
+    </row>
+    <row r="13" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B13" s="7" t="s">
         <v>102</v>
       </c>
-      <c r="C12" s="56"/>
-      <c r="D12" s="56"/>
-      <c r="E12" s="56"/>
-      <c r="F12" s="56"/>
-      <c r="G12" s="56"/>
-      <c r="H12" s="56"/>
-      <c r="I12" s="56"/>
-    </row>
-    <row r="13" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B13" s="7" t="s">
-        <v>103</v>
-      </c>
       <c r="C13" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="D13" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="D13" s="8" t="s">
+      <c r="E13" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="E13" s="8" t="s">
+      <c r="F13" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="F13" s="8" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="14" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="14" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B14" s="4" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C14" s="26">
         <f>C7</f>
@@ -2965,7 +2978,7 @@
         <v>969.3</v>
       </c>
       <c r="E14" s="26">
-        <f t="shared" ref="E14:F14" si="0">E7</f>
+        <f t="shared" ref="E14" si="0">E7</f>
         <v>1106.48</v>
       </c>
       <c r="F14" s="26">
@@ -2973,9 +2986,9 @@
         <v>1489.51</v>
       </c>
     </row>
-    <row r="15" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B15" s="12" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="C15" s="27">
         <f>C10</f>
@@ -2994,9 +3007,9 @@
         <v>344.87</v>
       </c>
     </row>
-    <row r="16" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B16" s="10" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="C16" s="16">
         <f>C14-C15</f>
@@ -3015,9 +3028,9 @@
         <v>1144.6399999999999</v>
       </c>
     </row>
-    <row r="17" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B17" s="4" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="C17" s="28">
         <f>C14*365/'P&amp;L Statement'!C5</f>
@@ -3036,38 +3049,38 @@
         <v>27.362301736091016</v>
       </c>
     </row>
-    <row r="19" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B19" s="56" t="s">
+    <row r="19" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B19" s="58" t="s">
+        <v>103</v>
+      </c>
+      <c r="C19" s="58"/>
+      <c r="D19" s="58"/>
+      <c r="E19" s="58"/>
+      <c r="F19" s="58"/>
+      <c r="G19" s="58"/>
+      <c r="H19" s="58"/>
+      <c r="I19" s="58"/>
+    </row>
+    <row r="20" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B20" s="7" t="s">
         <v>104</v>
       </c>
-      <c r="C19" s="56"/>
-      <c r="D19" s="56"/>
-      <c r="E19" s="56"/>
-      <c r="F19" s="56"/>
-      <c r="G19" s="56"/>
-      <c r="H19" s="56"/>
-      <c r="I19" s="56"/>
-    </row>
-    <row r="20" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B20" s="7" t="s">
+      <c r="C20" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="D20" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="E20" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="F20" s="8" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="21" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B21" s="4" t="s">
         <v>105</v>
-      </c>
-      <c r="C20" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="D20" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="E20" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="F20" s="8" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="21" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B21" s="4" t="s">
-        <v>106</v>
       </c>
       <c r="C21" s="29">
         <f>C9/C8</f>
@@ -3086,9 +3099,9 @@
         <v>0.56698385383569971</v>
       </c>
     </row>
-    <row r="22" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B22" s="12" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C22" s="30">
         <f>C5/C8</f>
@@ -3107,11 +3120,11 @@
         <v>2.2594100921644027</v>
       </c>
     </row>
-    <row r="23" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B23" s="4" t="s">
-        <v>108</v>
-      </c>
-      <c r="C23" s="65">
+        <v>107</v>
+      </c>
+      <c r="C23" s="46">
         <v>2.0699999999999998</v>
       </c>
       <c r="D23" s="31">
@@ -3124,11 +3137,11 @@
         <v>2.0499999999999998</v>
       </c>
     </row>
-    <row r="24" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B24" s="12" t="s">
-        <v>109</v>
-      </c>
-      <c r="C24" s="66">
+        <v>108</v>
+      </c>
+      <c r="C24" s="47">
         <v>1.17</v>
       </c>
       <c r="D24" s="32">
@@ -3141,81 +3154,81 @@
         <v>0.62</v>
       </c>
     </row>
-    <row r="25" spans="2:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="26" spans="2:9" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B26" s="57" t="s">
+    <row r="25" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="26" spans="2:9" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B26" s="60" t="s">
+        <v>109</v>
+      </c>
+      <c r="C26" s="61"/>
+      <c r="D26" s="61"/>
+      <c r="E26" s="61"/>
+      <c r="F26" s="62"/>
+    </row>
+    <row r="27" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B27" s="65" t="s">
         <v>110</v>
       </c>
-      <c r="C26" s="58"/>
-      <c r="D26" s="58"/>
-      <c r="E26" s="58"/>
-      <c r="F26" s="59"/>
-    </row>
-    <row r="27" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B27" s="63" t="s">
+      <c r="C27" s="65"/>
+      <c r="D27" s="65"/>
+      <c r="E27" s="65"/>
+      <c r="F27" s="65"/>
+    </row>
+    <row r="28" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B28" s="56" t="s">
         <v>111</v>
       </c>
-      <c r="C27" s="63"/>
-      <c r="D27" s="63"/>
-      <c r="E27" s="63"/>
-      <c r="F27" s="63"/>
-    </row>
-    <row r="28" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B28" s="50" t="s">
+      <c r="C28" s="56"/>
+      <c r="D28" s="56"/>
+      <c r="E28" s="56"/>
+      <c r="F28" s="56"/>
+    </row>
+    <row r="29" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B29" s="55" t="s">
         <v>112</v>
       </c>
-      <c r="C28" s="50"/>
-      <c r="D28" s="50"/>
-      <c r="E28" s="50"/>
-      <c r="F28" s="50"/>
-    </row>
-    <row r="29" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B29" s="49" t="s">
+      <c r="C29" s="55"/>
+      <c r="D29" s="55"/>
+      <c r="E29" s="55"/>
+      <c r="F29" s="55"/>
+    </row>
+    <row r="30" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B30" s="56" t="s">
         <v>113</v>
       </c>
-      <c r="C29" s="49"/>
-      <c r="D29" s="49"/>
-      <c r="E29" s="49"/>
-      <c r="F29" s="49"/>
-    </row>
-    <row r="30" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B30" s="50" t="s">
+      <c r="C30" s="56"/>
+      <c r="D30" s="56"/>
+      <c r="E30" s="56"/>
+      <c r="F30" s="56"/>
+    </row>
+    <row r="31" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B31" s="58" t="s">
         <v>114</v>
       </c>
-      <c r="C30" s="50"/>
-      <c r="D30" s="50"/>
-      <c r="E30" s="50"/>
-      <c r="F30" s="50"/>
-    </row>
-    <row r="31" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B31" s="56" t="s">
+      <c r="C31" s="58"/>
+      <c r="D31" s="58"/>
+      <c r="E31" s="58"/>
+      <c r="F31" s="58"/>
+      <c r="G31" s="58"/>
+      <c r="H31" s="58"/>
+      <c r="I31" s="58"/>
+    </row>
+    <row r="32" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B32" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="C32" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="D32" s="8" t="s">
+        <v>77</v>
+      </c>
+      <c r="E32" s="8" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="33" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B33" s="20" t="s">
         <v>115</v>
-      </c>
-      <c r="C31" s="56"/>
-      <c r="D31" s="56"/>
-      <c r="E31" s="56"/>
-      <c r="F31" s="56"/>
-      <c r="G31" s="56"/>
-      <c r="H31" s="56"/>
-      <c r="I31" s="56"/>
-    </row>
-    <row r="32" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B32" s="7" t="s">
-        <v>76</v>
-      </c>
-      <c r="C32" s="8" t="s">
-        <v>77</v>
-      </c>
-      <c r="D32" s="8" t="s">
-        <v>78</v>
-      </c>
-      <c r="E32" s="8" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="33" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B33" s="20" t="s">
-        <v>116</v>
       </c>
       <c r="C33" s="21">
         <v>0.09</v>
@@ -3227,9 +3240,9 @@
         <v>0.11</v>
       </c>
     </row>
-    <row r="34" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B34" s="20" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C34" s="11">
         <v>300</v>
@@ -3241,9 +3254,9 @@
         <v>300</v>
       </c>
     </row>
-    <row r="35" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B35" s="20" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C35" s="21">
         <v>0.08</v>
@@ -3255,33 +3268,33 @@
         <v>0.08</v>
       </c>
     </row>
-    <row r="36" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B36" s="56" t="s">
-        <v>119</v>
-      </c>
-      <c r="C36" s="56"/>
-      <c r="D36" s="56"/>
-      <c r="E36" s="56"/>
-      <c r="F36" s="56"/>
-      <c r="G36" s="56"/>
-      <c r="H36" s="56"/>
-      <c r="I36" s="56"/>
-    </row>
-    <row r="37" spans="2:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B36" s="58" t="s">
+        <v>118</v>
+      </c>
+      <c r="C36" s="58"/>
+      <c r="D36" s="58"/>
+      <c r="E36" s="58"/>
+      <c r="F36" s="58"/>
+      <c r="G36" s="58"/>
+      <c r="H36" s="58"/>
+      <c r="I36" s="58"/>
+    </row>
+    <row r="37" spans="2:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B37" s="7" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C37" s="22" t="s">
+        <v>76</v>
+      </c>
+      <c r="D37" s="22" t="s">
         <v>77</v>
       </c>
-      <c r="D37" s="22" t="s">
+      <c r="E37" s="22" t="s">
         <v>78</v>
       </c>
-      <c r="E37" s="22" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="38" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="38" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B38" s="25">
         <f>8623.72</f>
         <v>8623.7199999999993</v>
@@ -3299,7 +3312,7 @@
         <v>11477.222710800001</v>
       </c>
     </row>
-    <row r="39" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B39" s="24">
         <f>4889.51</f>
         <v>4889.51</v>
@@ -3317,7 +3330,7 @@
         <v>3989.51</v>
       </c>
     </row>
-    <row r="40" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B40" s="23">
         <f>1489.51</f>
         <v>1489.51</v>
@@ -3335,7 +3348,7 @@
         <v>1876.3536211200003</v>
       </c>
     </row>
-    <row r="41" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B41" s="29">
         <f>4889.51/8623.72</f>
         <v>0.56698385383569971</v>
@@ -3353,90 +3366,80 @@
         <v>0.34760238609344873</v>
       </c>
     </row>
-    <row r="42" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B42" s="56" t="s">
+    <row r="42" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B42" s="58" t="s">
+        <v>119</v>
+      </c>
+      <c r="C42" s="58"/>
+      <c r="D42" s="58"/>
+      <c r="E42" s="58"/>
+      <c r="F42" s="58"/>
+      <c r="G42" s="58"/>
+      <c r="H42" s="58"/>
+      <c r="I42" s="58"/>
+    </row>
+    <row r="43" spans="2:9" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B43" s="55" t="s">
         <v>120</v>
       </c>
-      <c r="C42" s="56"/>
-      <c r="D42" s="56"/>
-      <c r="E42" s="56"/>
-      <c r="F42" s="56"/>
-      <c r="G42" s="56"/>
-      <c r="H42" s="56"/>
-      <c r="I42" s="56"/>
-    </row>
-    <row r="43" spans="2:9" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B43" s="49" t="s">
+      <c r="C43" s="55"/>
+      <c r="D43" s="55"/>
+      <c r="E43" s="55"/>
+      <c r="F43" s="55"/>
+      <c r="G43" s="55"/>
+      <c r="H43" s="55"/>
+      <c r="I43" s="55"/>
+    </row>
+    <row r="44" spans="2:9" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B44" s="64" t="s">
         <v>121</v>
       </c>
-      <c r="C43" s="49"/>
-      <c r="D43" s="49"/>
-      <c r="E43" s="49"/>
-      <c r="F43" s="49"/>
-      <c r="G43" s="49"/>
-      <c r="H43" s="49"/>
-      <c r="I43" s="49"/>
-    </row>
-    <row r="44" spans="2:9" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B44" s="55" t="s">
+      <c r="C44" s="64"/>
+      <c r="D44" s="64"/>
+      <c r="E44" s="64"/>
+      <c r="F44" s="64"/>
+      <c r="G44" s="64"/>
+      <c r="H44" s="64"/>
+      <c r="I44" s="64"/>
+    </row>
+    <row r="45" spans="2:9" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B45" s="55" t="s">
         <v>122</v>
       </c>
-      <c r="C44" s="55"/>
-      <c r="D44" s="55"/>
-      <c r="E44" s="55"/>
-      <c r="F44" s="55"/>
-      <c r="G44" s="55"/>
-      <c r="H44" s="55"/>
-      <c r="I44" s="55"/>
-    </row>
-    <row r="45" spans="2:9" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B45" s="49" t="s">
+      <c r="C45" s="55"/>
+      <c r="D45" s="55"/>
+      <c r="E45" s="55"/>
+      <c r="F45" s="55"/>
+      <c r="G45" s="55"/>
+      <c r="H45" s="55"/>
+      <c r="I45" s="55"/>
+    </row>
+    <row r="46" spans="2:9" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B46" s="64" t="s">
         <v>123</v>
       </c>
-      <c r="C45" s="49"/>
-      <c r="D45" s="49"/>
-      <c r="E45" s="49"/>
-      <c r="F45" s="49"/>
-      <c r="G45" s="49"/>
-      <c r="H45" s="49"/>
-      <c r="I45" s="49"/>
-    </row>
-    <row r="46" spans="2:9" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B46" s="55" t="s">
-        <v>124</v>
-      </c>
-      <c r="C46" s="55"/>
-      <c r="D46" s="55"/>
-      <c r="E46" s="55"/>
-      <c r="F46" s="55"/>
-      <c r="G46" s="55"/>
-      <c r="H46" s="55"/>
-      <c r="I46" s="55"/>
-    </row>
-    <row r="48" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B48" s="48" t="s">
+      <c r="C46" s="64"/>
+      <c r="D46" s="64"/>
+      <c r="E46" s="64"/>
+      <c r="F46" s="64"/>
+      <c r="G46" s="64"/>
+      <c r="H46" s="64"/>
+      <c r="I46" s="64"/>
+    </row>
+    <row r="48" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B48" s="54" t="s">
         <v>2</v>
       </c>
-      <c r="C48" s="48"/>
-      <c r="D48" s="48"/>
-      <c r="E48" s="48"/>
-      <c r="F48" s="48"/>
-      <c r="G48" s="48"/>
-      <c r="H48" s="48"/>
-      <c r="I48" s="48"/>
+      <c r="C48" s="54"/>
+      <c r="D48" s="54"/>
+      <c r="E48" s="54"/>
+      <c r="F48" s="54"/>
+      <c r="G48" s="54"/>
+      <c r="H48" s="54"/>
+      <c r="I48" s="54"/>
     </row>
   </sheetData>
   <mergeCells count="17">
-    <mergeCell ref="B1:I1"/>
-    <mergeCell ref="B3:F3"/>
-    <mergeCell ref="B12:I12"/>
-    <mergeCell ref="B19:I19"/>
-    <mergeCell ref="B26:F26"/>
-    <mergeCell ref="B27:F27"/>
-    <mergeCell ref="B28:F28"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="B30:F30"/>
-    <mergeCell ref="B31:I31"/>
     <mergeCell ref="B46:I46"/>
     <mergeCell ref="B48:I48"/>
     <mergeCell ref="B36:I36"/>
@@ -3444,6 +3447,16 @@
     <mergeCell ref="B43:I43"/>
     <mergeCell ref="B44:I44"/>
     <mergeCell ref="B45:I45"/>
+    <mergeCell ref="B27:F27"/>
+    <mergeCell ref="B28:F28"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="B30:F30"/>
+    <mergeCell ref="B31:I31"/>
+    <mergeCell ref="B1:I1"/>
+    <mergeCell ref="B3:F3"/>
+    <mergeCell ref="B12:I12"/>
+    <mergeCell ref="B19:I19"/>
+    <mergeCell ref="B26:F26"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
@@ -3451,59 +3464,59 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:J42"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="2" style="1" customWidth="1"/>
-    <col min="2" max="2" width="46.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="46.81640625" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="5" width="13" style="1" customWidth="1"/>
-    <col min="6" max="6" width="9.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.81640625" style="1" bestFit="1" customWidth="1"/>
     <col min="7" max="9" width="14" style="1" customWidth="1"/>
     <col min="10" max="10" width="2" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B1" s="61" t="s">
+    <row r="1" spans="2:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B1" s="57" t="s">
+        <v>124</v>
+      </c>
+      <c r="C1" s="57"/>
+      <c r="D1" s="57"/>
+      <c r="E1" s="57"/>
+      <c r="F1" s="57"/>
+      <c r="G1" s="57"/>
+      <c r="H1" s="57"/>
+      <c r="I1" s="57"/>
+    </row>
+    <row r="3" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B3" s="58" t="s">
         <v>125</v>
       </c>
-      <c r="C1" s="61"/>
-      <c r="D1" s="61"/>
-      <c r="E1" s="61"/>
-      <c r="F1" s="61"/>
-      <c r="G1" s="61"/>
-      <c r="H1" s="61"/>
-      <c r="I1" s="61"/>
-    </row>
-    <row r="3" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="56" t="s">
+      <c r="C3" s="58"/>
+      <c r="D3" s="58"/>
+      <c r="E3" s="58"/>
+      <c r="F3" s="58"/>
+    </row>
+    <row r="4" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B4" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="C4" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="D4" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="E4" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="F4" s="8" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="5" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B5" s="10" t="s">
         <v>126</v>
-      </c>
-      <c r="C3" s="56"/>
-      <c r="D3" s="56"/>
-      <c r="E3" s="56"/>
-      <c r="F3" s="56"/>
-    </row>
-    <row r="4" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B4" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="C4" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="D4" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="E4" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="F4" s="8" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="5" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="10" t="s">
-        <v>127</v>
       </c>
       <c r="C5" s="11">
         <v>4806.17</v>
@@ -3518,9 +3531,9 @@
         <v>1919.9</v>
       </c>
     </row>
-    <row r="6" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B6" s="4" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C6" s="9">
         <v>-1462.83</v>
@@ -3535,9 +3548,9 @@
         <v>1581.62</v>
       </c>
     </row>
-    <row r="7" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B7" s="12" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C7" s="13">
         <v>-189.36</v>
@@ -3552,9 +3565,9 @@
         <v>-1484.17</v>
       </c>
     </row>
-    <row r="8" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B8" s="14" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C8" s="25">
         <f>C5+C6+C7</f>
@@ -3573,9 +3586,9 @@
         <v>2017.35</v>
       </c>
     </row>
-    <row r="9" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B9" s="14" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C9" s="15">
         <v>4569.93</v>
@@ -3590,38 +3603,38 @@
         <v>3044.8</v>
       </c>
     </row>
-    <row r="11" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B11" s="56" t="s">
-        <v>204</v>
-      </c>
-      <c r="C11" s="56"/>
-      <c r="D11" s="56"/>
-      <c r="E11" s="56"/>
-      <c r="F11" s="56"/>
-      <c r="G11" s="56"/>
-      <c r="H11" s="56"/>
-      <c r="I11" s="56"/>
-    </row>
-    <row r="12" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B11" s="58" t="s">
+        <v>203</v>
+      </c>
+      <c r="C11" s="58"/>
+      <c r="D11" s="58"/>
+      <c r="E11" s="58"/>
+      <c r="F11" s="58"/>
+      <c r="G11" s="58"/>
+      <c r="H11" s="58"/>
+      <c r="I11" s="58"/>
+    </row>
+    <row r="12" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B12" s="7" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C12" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="D12" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="D12" s="8" t="s">
+      <c r="E12" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="E12" s="8" t="s">
+      <c r="F12" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="F12" s="8" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="13" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="13" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B13" s="4" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C13" s="9">
         <v>1087.3499999999999</v>
@@ -3636,9 +3649,9 @@
         <v>1188.6199999999999</v>
       </c>
     </row>
-    <row r="14" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B14" s="12" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C14" s="13">
         <v>4806.17</v>
@@ -3653,9 +3666,9 @@
         <v>1919.9</v>
       </c>
     </row>
-    <row r="15" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B15" s="10" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C15" s="16">
         <f>C14-C13</f>
@@ -3674,9 +3687,9 @@
         <v>731.2800000000002</v>
       </c>
     </row>
-    <row r="16" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B16" s="4" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C16" s="29">
         <f>C14/C13</f>
@@ -3695,90 +3708,90 @@
         <v>1.6152344735912236</v>
       </c>
     </row>
-    <row r="17" spans="2:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="18" spans="2:9" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B18" s="57" t="s">
+    <row r="17" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="18" spans="2:9" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B18" s="60" t="s">
+        <v>134</v>
+      </c>
+      <c r="C18" s="61"/>
+      <c r="D18" s="61"/>
+      <c r="E18" s="61"/>
+      <c r="F18" s="62"/>
+    </row>
+    <row r="19" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B19" s="65" t="s">
         <v>135</v>
       </c>
-      <c r="C18" s="58"/>
-      <c r="D18" s="58"/>
-      <c r="E18" s="58"/>
-      <c r="F18" s="59"/>
-    </row>
-    <row r="19" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B19" s="63" t="s">
+      <c r="C19" s="65"/>
+      <c r="D19" s="65"/>
+      <c r="E19" s="65"/>
+      <c r="F19" s="65"/>
+    </row>
+    <row r="20" spans="2:9" ht="36" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B20" s="56" t="s">
         <v>136</v>
       </c>
-      <c r="C19" s="63"/>
-      <c r="D19" s="63"/>
-      <c r="E19" s="63"/>
-      <c r="F19" s="63"/>
-    </row>
-    <row r="20" spans="2:9" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B20" s="50" t="s">
+      <c r="C20" s="56"/>
+      <c r="D20" s="56"/>
+      <c r="E20" s="56"/>
+      <c r="F20" s="56"/>
+    </row>
+    <row r="21" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B21" s="55" t="s">
         <v>137</v>
       </c>
-      <c r="C20" s="50"/>
-      <c r="D20" s="50"/>
-      <c r="E20" s="50"/>
-      <c r="F20" s="50"/>
-    </row>
-    <row r="21" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B21" s="49" t="s">
+      <c r="C21" s="55"/>
+      <c r="D21" s="55"/>
+      <c r="E21" s="55"/>
+      <c r="F21" s="55"/>
+    </row>
+    <row r="22" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B22" s="56" t="s">
         <v>138</v>
       </c>
-      <c r="C21" s="49"/>
-      <c r="D21" s="49"/>
-      <c r="E21" s="49"/>
-      <c r="F21" s="49"/>
-    </row>
-    <row r="22" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B22" s="50" t="s">
+      <c r="C22" s="56"/>
+      <c r="D22" s="56"/>
+      <c r="E22" s="56"/>
+      <c r="F22" s="56"/>
+    </row>
+    <row r="23" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B23" s="55" t="s">
         <v>139</v>
       </c>
-      <c r="C22" s="50"/>
-      <c r="D22" s="50"/>
-      <c r="E22" s="50"/>
-      <c r="F22" s="50"/>
-    </row>
-    <row r="23" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B23" s="49" t="s">
+      <c r="C23" s="55"/>
+      <c r="D23" s="55"/>
+      <c r="E23" s="55"/>
+      <c r="F23" s="55"/>
+    </row>
+    <row r="24" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B24" s="58" t="s">
+        <v>201</v>
+      </c>
+      <c r="C24" s="58"/>
+      <c r="D24" s="58"/>
+      <c r="E24" s="58"/>
+      <c r="F24" s="58"/>
+      <c r="G24" s="58"/>
+      <c r="H24" s="58"/>
+      <c r="I24" s="58"/>
+    </row>
+    <row r="25" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B25" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="C25" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="D25" s="8" t="s">
+        <v>77</v>
+      </c>
+      <c r="E25" s="8" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="26" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B26" s="20" t="s">
         <v>140</v>
-      </c>
-      <c r="C23" s="49"/>
-      <c r="D23" s="49"/>
-      <c r="E23" s="49"/>
-      <c r="F23" s="49"/>
-    </row>
-    <row r="24" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B24" s="56" t="s">
-        <v>202</v>
-      </c>
-      <c r="C24" s="56"/>
-      <c r="D24" s="56"/>
-      <c r="E24" s="56"/>
-      <c r="F24" s="56"/>
-      <c r="G24" s="56"/>
-      <c r="H24" s="56"/>
-      <c r="I24" s="56"/>
-    </row>
-    <row r="25" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B25" s="7" t="s">
-        <v>76</v>
-      </c>
-      <c r="C25" s="8" t="s">
-        <v>77</v>
-      </c>
-      <c r="D25" s="8" t="s">
-        <v>78</v>
-      </c>
-      <c r="E25" s="8" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="26" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B26" s="20" t="s">
-        <v>141</v>
       </c>
       <c r="C26" s="11">
         <v>1350</v>
@@ -3790,9 +3803,9 @@
         <v>1700</v>
       </c>
     </row>
-    <row r="27" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B27" s="20" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C27" s="33">
         <v>1.2</v>
@@ -3804,9 +3817,9 @@
         <v>1.4</v>
       </c>
     </row>
-    <row r="28" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B28" s="20" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C28" s="11">
         <v>-1500</v>
@@ -3818,33 +3831,33 @@
         <v>-1500</v>
       </c>
     </row>
-    <row r="29" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B29" s="56" t="s">
-        <v>203</v>
-      </c>
-      <c r="C29" s="56"/>
-      <c r="D29" s="56"/>
-      <c r="E29" s="56"/>
-      <c r="F29" s="56"/>
-      <c r="G29" s="56"/>
-      <c r="H29" s="56"/>
-      <c r="I29" s="56"/>
-    </row>
-    <row r="30" spans="2:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B29" s="58" t="s">
+        <v>202</v>
+      </c>
+      <c r="C29" s="58"/>
+      <c r="D29" s="58"/>
+      <c r="E29" s="58"/>
+      <c r="F29" s="58"/>
+      <c r="G29" s="58"/>
+      <c r="H29" s="58"/>
+      <c r="I29" s="58"/>
+    </row>
+    <row r="30" spans="2:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B30" s="7" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C30" s="22" t="s">
+        <v>76</v>
+      </c>
+      <c r="D30" s="22" t="s">
         <v>77</v>
       </c>
-      <c r="D30" s="22" t="s">
+      <c r="E30" s="22" t="s">
         <v>78</v>
       </c>
-      <c r="E30" s="22" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="31" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="31" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B31" s="16">
         <f>1919.9</f>
         <v>1919.9</v>
@@ -3862,7 +3875,7 @@
         <v>2380</v>
       </c>
     </row>
-    <row r="32" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B32" s="24">
         <f>-1484.17</f>
         <v>-1484.17</v>
@@ -3880,7 +3893,7 @@
         <v>-1500</v>
       </c>
     </row>
-    <row r="33" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B33" s="25">
         <f>B31+B32</f>
         <v>435.73</v>
@@ -3898,7 +3911,7 @@
         <v>880</v>
       </c>
     </row>
-    <row r="34" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B34" s="25">
         <f>3044.8</f>
         <v>3044.8</v>
@@ -3916,102 +3929,92 @@
         <v>4494.8</v>
       </c>
     </row>
-    <row r="35" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B35" s="56" t="s">
+    <row r="35" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B35" s="58" t="s">
+        <v>143</v>
+      </c>
+      <c r="C35" s="58"/>
+      <c r="D35" s="58"/>
+      <c r="E35" s="58"/>
+      <c r="F35" s="58"/>
+      <c r="G35" s="58"/>
+      <c r="H35" s="58"/>
+      <c r="I35" s="58"/>
+    </row>
+    <row r="36" spans="2:9" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B36" s="64" t="s">
         <v>144</v>
       </c>
-      <c r="C35" s="56"/>
-      <c r="D35" s="56"/>
-      <c r="E35" s="56"/>
-      <c r="F35" s="56"/>
-      <c r="G35" s="56"/>
-      <c r="H35" s="56"/>
-      <c r="I35" s="56"/>
-    </row>
-    <row r="36" spans="2:9" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B36" s="55" t="s">
+      <c r="C36" s="64"/>
+      <c r="D36" s="64"/>
+      <c r="E36" s="64"/>
+      <c r="F36" s="64"/>
+      <c r="G36" s="64"/>
+      <c r="H36" s="64"/>
+      <c r="I36" s="64"/>
+    </row>
+    <row r="37" spans="2:9" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B37" s="55" t="s">
         <v>145</v>
       </c>
-      <c r="C36" s="55"/>
-      <c r="D36" s="55"/>
-      <c r="E36" s="55"/>
-      <c r="F36" s="55"/>
-      <c r="G36" s="55"/>
-      <c r="H36" s="55"/>
-      <c r="I36" s="55"/>
-    </row>
-    <row r="37" spans="2:9" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B37" s="49" t="s">
+      <c r="C37" s="55"/>
+      <c r="D37" s="55"/>
+      <c r="E37" s="55"/>
+      <c r="F37" s="55"/>
+      <c r="G37" s="55"/>
+      <c r="H37" s="55"/>
+      <c r="I37" s="55"/>
+    </row>
+    <row r="38" spans="2:9" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B38" s="64" t="s">
         <v>146</v>
       </c>
-      <c r="C37" s="49"/>
-      <c r="D37" s="49"/>
-      <c r="E37" s="49"/>
-      <c r="F37" s="49"/>
-      <c r="G37" s="49"/>
-      <c r="H37" s="49"/>
-      <c r="I37" s="49"/>
-    </row>
-    <row r="38" spans="2:9" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B38" s="55" t="s">
+      <c r="C38" s="64"/>
+      <c r="D38" s="64"/>
+      <c r="E38" s="64"/>
+      <c r="F38" s="64"/>
+      <c r="G38" s="64"/>
+      <c r="H38" s="64"/>
+      <c r="I38" s="64"/>
+    </row>
+    <row r="39" spans="2:9" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B39" s="55" t="s">
         <v>147</v>
       </c>
-      <c r="C38" s="55"/>
-      <c r="D38" s="55"/>
-      <c r="E38" s="55"/>
-      <c r="F38" s="55"/>
-      <c r="G38" s="55"/>
-      <c r="H38" s="55"/>
-      <c r="I38" s="55"/>
-    </row>
-    <row r="39" spans="2:9" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B39" s="49" t="s">
+      <c r="C39" s="55"/>
+      <c r="D39" s="55"/>
+      <c r="E39" s="55"/>
+      <c r="F39" s="55"/>
+      <c r="G39" s="55"/>
+      <c r="H39" s="55"/>
+      <c r="I39" s="55"/>
+    </row>
+    <row r="40" spans="2:9" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B40" s="64" t="s">
         <v>148</v>
       </c>
-      <c r="C39" s="49"/>
-      <c r="D39" s="49"/>
-      <c r="E39" s="49"/>
-      <c r="F39" s="49"/>
-      <c r="G39" s="49"/>
-      <c r="H39" s="49"/>
-      <c r="I39" s="49"/>
-    </row>
-    <row r="40" spans="2:9" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B40" s="55" t="s">
-        <v>149</v>
-      </c>
-      <c r="C40" s="55"/>
-      <c r="D40" s="55"/>
-      <c r="E40" s="55"/>
-      <c r="F40" s="55"/>
-      <c r="G40" s="55"/>
-      <c r="H40" s="55"/>
-      <c r="I40" s="55"/>
-    </row>
-    <row r="42" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B42" s="48" t="s">
+      <c r="C40" s="64"/>
+      <c r="D40" s="64"/>
+      <c r="E40" s="64"/>
+      <c r="F40" s="64"/>
+      <c r="G40" s="64"/>
+      <c r="H40" s="64"/>
+      <c r="I40" s="64"/>
+    </row>
+    <row r="42" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B42" s="54" t="s">
         <v>2</v>
       </c>
-      <c r="C42" s="48"/>
-      <c r="D42" s="48"/>
-      <c r="E42" s="48"/>
-      <c r="F42" s="48"/>
-      <c r="G42" s="48"/>
-      <c r="H42" s="48"/>
-      <c r="I42" s="48"/>
+      <c r="C42" s="54"/>
+      <c r="D42" s="54"/>
+      <c r="E42" s="54"/>
+      <c r="F42" s="54"/>
+      <c r="G42" s="54"/>
+      <c r="H42" s="54"/>
+      <c r="I42" s="54"/>
     </row>
   </sheetData>
   <mergeCells count="18">
-    <mergeCell ref="B1:I1"/>
-    <mergeCell ref="B3:F3"/>
-    <mergeCell ref="B11:I11"/>
-    <mergeCell ref="B18:F18"/>
-    <mergeCell ref="B19:F19"/>
-    <mergeCell ref="B20:F20"/>
-    <mergeCell ref="B21:F21"/>
-    <mergeCell ref="B22:F22"/>
-    <mergeCell ref="B23:F23"/>
-    <mergeCell ref="B24:I24"/>
     <mergeCell ref="B39:I39"/>
     <mergeCell ref="B40:I40"/>
     <mergeCell ref="B42:I42"/>
@@ -4020,6 +4023,16 @@
     <mergeCell ref="B36:I36"/>
     <mergeCell ref="B37:I37"/>
     <mergeCell ref="B38:I38"/>
+    <mergeCell ref="B20:F20"/>
+    <mergeCell ref="B21:F21"/>
+    <mergeCell ref="B22:F22"/>
+    <mergeCell ref="B23:F23"/>
+    <mergeCell ref="B24:I24"/>
+    <mergeCell ref="B1:I1"/>
+    <mergeCell ref="B3:F3"/>
+    <mergeCell ref="B11:I11"/>
+    <mergeCell ref="B18:F18"/>
+    <mergeCell ref="B19:F19"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -4027,62 +4040,62 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:F39"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="68.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="68.81640625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="5" width="14" style="1" customWidth="1"/>
     <col min="6" max="6" width="4" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="61" t="s">
-        <v>201</v>
-      </c>
-      <c r="B1" s="61"/>
-      <c r="C1" s="61"/>
-      <c r="D1" s="61"/>
-      <c r="E1" s="61"/>
-    </row>
-    <row r="2" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="64" t="s">
-        <v>198</v>
-      </c>
-      <c r="B2" s="64"/>
-      <c r="C2" s="64"/>
-      <c r="D2" s="64"/>
-      <c r="E2" s="64"/>
-    </row>
-    <row r="4" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="57" t="s">
+        <v>200</v>
+      </c>
+      <c r="B1" s="57"/>
+      <c r="C1" s="57"/>
+      <c r="D1" s="57"/>
+      <c r="E1" s="57"/>
+    </row>
+    <row r="2" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="66" t="s">
+        <v>197</v>
+      </c>
+      <c r="B2" s="66"/>
+      <c r="C2" s="66"/>
+      <c r="D2" s="66"/>
+      <c r="E2" s="66"/>
+    </row>
+    <row r="4" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="B4" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="C4" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="D4" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="E4" s="8" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="34" t="s">
         <v>150</v>
-      </c>
-      <c r="B4" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="C4" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="D4" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="E4" s="8" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="34" t="s">
-        <v>151</v>
       </c>
       <c r="B5" s="35"/>
       <c r="C5" s="35"/>
       <c r="D5" s="35"/>
       <c r="E5" s="35"/>
     </row>
-    <row r="6" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="12" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B6" s="13">
         <v>19381.71</v>
@@ -4097,9 +4110,9 @@
         <v>19869.349999999999</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B7" s="9">
         <v>809.26</v>
@@ -4114,9 +4127,9 @@
         <v>1018.89</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="10" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B8" s="11">
         <v>20190.97</v>
@@ -4131,18 +4144,18 @@
         <v>20888.240000000002</v>
       </c>
     </row>
-    <row r="10" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="34" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B10" s="35"/>
       <c r="C10" s="35"/>
       <c r="D10" s="35"/>
       <c r="E10" s="35"/>
     </row>
-    <row r="11" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B11" s="9">
         <v>17905.57</v>
@@ -4157,9 +4170,9 @@
         <v>18385.2</v>
       </c>
     </row>
-    <row r="12" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="12" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B12" s="13">
         <v>203.05</v>
@@ -4174,9 +4187,9 @@
         <v>182.98</v>
       </c>
     </row>
-    <row r="13" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B13" s="9">
         <v>563.71</v>
@@ -4191,9 +4204,9 @@
         <v>539.51</v>
       </c>
     </row>
-    <row r="14" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="12" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B14" s="13">
         <v>20.9</v>
@@ -4208,9 +4221,9 @@
         <v>30.6</v>
       </c>
     </row>
-    <row r="15" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B15" s="9">
         <v>91.5</v>
@@ -4225,9 +4238,9 @@
         <v>199.78</v>
       </c>
     </row>
-    <row r="16" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="10" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B16" s="11">
         <v>18784.73</v>
@@ -4242,18 +4255,18 @@
         <v>19338.07</v>
       </c>
     </row>
-    <row r="18" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="34" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B18" s="35"/>
       <c r="C18" s="35"/>
       <c r="D18" s="35"/>
       <c r="E18" s="35"/>
     </row>
-    <row r="19" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="4" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B19" s="9">
         <v>1406.24</v>
@@ -4268,9 +4281,9 @@
         <v>1550.17</v>
       </c>
     </row>
-    <row r="20" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A20" s="10" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B20" s="11">
         <v>318.89</v>
@@ -4285,9 +4298,9 @@
         <v>361.55</v>
       </c>
     </row>
-    <row r="21" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A21" s="14" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B21" s="15">
         <v>1087.3499999999999</v>
@@ -4302,18 +4315,18 @@
         <v>1188.6199999999999</v>
       </c>
     </row>
-    <row r="23" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A23" s="34" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B23" s="35"/>
       <c r="C23" s="35"/>
       <c r="D23" s="35"/>
       <c r="E23" s="35"/>
     </row>
-    <row r="24" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A24" s="10" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B24" s="11">
         <v>19379.09</v>
@@ -4328,9 +4341,9 @@
         <v>19484.52</v>
       </c>
     </row>
-    <row r="25" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A25" s="10" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B25" s="11">
         <v>5631.44</v>
@@ -4345,9 +4358,9 @@
         <v>8623.7199999999993</v>
       </c>
     </row>
-    <row r="26" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A26" s="12" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B26" s="13">
         <v>938.17</v>
@@ -4362,9 +4375,9 @@
         <v>1489.51</v>
       </c>
     </row>
-    <row r="27" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A27" s="4" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B27" s="9">
         <v>4569.93</v>
@@ -4379,9 +4392,9 @@
         <v>3044.8</v>
       </c>
     </row>
-    <row r="28" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A28" s="12" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B28" s="13">
         <v>6315.42</v>
@@ -4396,9 +4409,9 @@
         <v>4889.51</v>
       </c>
     </row>
-    <row r="29" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A29" s="4" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B29" s="9">
         <v>230.5</v>
@@ -4413,18 +4426,18 @@
         <v>344.87</v>
       </c>
     </row>
-    <row r="31" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A31" s="34" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B31" s="35"/>
       <c r="C31" s="35"/>
       <c r="D31" s="35"/>
       <c r="E31" s="35"/>
     </row>
-    <row r="32" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A32" s="12" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B32" s="13">
         <v>4806.17</v>
@@ -4439,9 +4452,9 @@
         <v>1919.9</v>
       </c>
     </row>
-    <row r="33" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A33" s="4" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B33" s="9">
         <v>-1462.83</v>
@@ -4456,9 +4469,9 @@
         <v>1581.62</v>
       </c>
     </row>
-    <row r="34" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A34" s="12" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B34" s="13">
         <v>-189.36</v>
@@ -4473,9 +4486,9 @@
         <v>-1484.17</v>
       </c>
     </row>
-    <row r="35" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A35" s="4" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B35" s="9">
         <v>4569.93</v>
@@ -4490,18 +4503,18 @@
         <v>3044.8</v>
       </c>
     </row>
-    <row r="37" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A37" s="36" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B39" s="48" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B39" s="54" t="s">
         <v>2</v>
       </c>
-      <c r="C39" s="48"/>
-      <c r="D39" s="48"/>
-      <c r="E39" s="48"/>
+      <c r="C39" s="54"/>
+      <c r="D39" s="54"/>
+      <c r="E39" s="54"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -4515,201 +4528,201 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:C46"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="2" style="1" customWidth="1"/>
-    <col min="2" max="2" width="141.28515625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="141.26953125" style="1" customWidth="1"/>
     <col min="3" max="3" width="2" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:2" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="2:2" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B1" s="37" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="2" spans="2:2" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B2" s="38" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="4" spans="2:2" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B4" s="39" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="5" spans="2:2" ht="34.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B5" s="40" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="6" spans="2:2" ht="34.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B6" s="41" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="7" spans="2:2" ht="34.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B7" s="40" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="8" spans="2:2" ht="34.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B8" s="41" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="10" spans="2:2" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B10" s="39" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="11" spans="2:2" ht="34.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B11" s="40" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="12" spans="2:2" ht="34.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B12" s="41" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="13" spans="2:2" ht="34.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B13" s="40" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="14" spans="2:2" ht="34.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B14" s="41" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="16" spans="2:2" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B16" s="39" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="17" spans="2:2" ht="34.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B17" s="40" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="18" spans="2:2" ht="34.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B18" s="41" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="19" spans="2:2" ht="34.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B19" s="40" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="20" spans="2:2" ht="34.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B20" s="41" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="22" spans="2:2" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B22" s="39" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="23" spans="2:2" ht="34.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B23" s="40" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="24" spans="2:2" ht="34.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B24" s="41" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="25" spans="2:2" ht="34.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B25" s="40" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="27" spans="2:2" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B27" s="39" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="28" spans="2:2" ht="34.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B28" s="41" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="29" spans="2:2" ht="34.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B29" s="40" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="30" spans="2:2" ht="34.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B30" s="41" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="31" spans="2:2" ht="34.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B31" s="40" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="33" spans="2:2" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B33" s="39" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="34" spans="2:2" ht="34.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B34" s="41" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="35" spans="2:2" ht="34.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B35" s="40" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="36" spans="2:2" ht="34.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B36" s="41" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="37" spans="2:2" ht="34.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B37" s="40" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="39" spans="2:2" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B39" s="42" t="s">
         <v>199</v>
       </c>
     </row>
-    <row r="2" spans="2:2" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="38" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="4" spans="2:2" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B4" s="39" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="5" spans="2:2" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="40" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="6" spans="2:2" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="41" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="7" spans="2:2" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B7" s="40" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="8" spans="2:2" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B8" s="41" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="10" spans="2:2" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B10" s="39" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="11" spans="2:2" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B11" s="40" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="12" spans="2:2" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B12" s="41" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="13" spans="2:2" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B13" s="40" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="14" spans="2:2" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B14" s="41" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="16" spans="2:2" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B16" s="39" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="17" spans="2:2" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B17" s="40" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="18" spans="2:2" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B18" s="41" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="19" spans="2:2" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B19" s="40" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="20" spans="2:2" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B20" s="41" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="22" spans="2:2" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B22" s="39" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="23" spans="2:2" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B23" s="40" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="24" spans="2:2" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B24" s="41" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="25" spans="2:2" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B25" s="40" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="27" spans="2:2" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B27" s="39" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="28" spans="2:2" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B28" s="41" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="29" spans="2:2" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B29" s="40" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="30" spans="2:2" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B30" s="41" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="31" spans="2:2" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B31" s="40" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="33" spans="2:2" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B33" s="39" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="34" spans="2:2" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B34" s="41" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="35" spans="2:2" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B35" s="40" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="36" spans="2:2" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B36" s="41" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="37" spans="2:2" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B37" s="40" t="s">
+    <row r="40" spans="2:2" ht="34.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B40" s="43" t="s">
         <v>186</v>
       </c>
     </row>
-    <row r="39" spans="2:2" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B39" s="42" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="40" spans="2:2" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B40" s="43" t="s">
+    <row r="41" spans="2:2" ht="34.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B41" s="44" t="s">
         <v>187</v>
       </c>
     </row>
-    <row r="41" spans="2:2" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B41" s="44" t="s">
+    <row r="42" spans="2:2" ht="34.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B42" s="43" t="s">
         <v>188</v>
       </c>
     </row>
-    <row r="42" spans="2:2" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B42" s="43" t="s">
+    <row r="43" spans="2:2" ht="34.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B43" s="44" t="s">
         <v>189</v>
       </c>
     </row>
-    <row r="43" spans="2:2" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B43" s="44" t="s">
+    <row r="44" spans="2:2" ht="34.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B44" s="43" t="s">
         <v>190</v>
       </c>
     </row>
-    <row r="44" spans="2:2" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B44" s="43" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="46" spans="2:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="2:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B46" s="45" t="s">
         <v>2</v>
       </c>
